--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -3081,9 +3081,14 @@
           <t xml:space="preserve">TODDY CACAO ORIGINAL 180GR</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5">
+        <v>17690.88</v>
+      </c>
       <c r="E4" s="5">
+        <f>IF(C4&gt;0,D4/C4,"")</f>
         <v>1474.24</v>
       </c>
     </row>
@@ -3096,10 +3101,15 @@
           <t xml:space="preserve">TODDY CACAO EXTREMO 360GR</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5">
+        <v>41113.72</v>
+      </c>
       <c r="E5" s="5">
-        <v>2936.69</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>2936.6942857142858</v>
       </c>
     </row>
     <row r="6">
@@ -3111,9 +3121,14 @@
           <t xml:space="preserve">TODDY CACAO EXTREMO 8X800GR</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5">
+        <v>48149.68</v>
+      </c>
       <c r="E6" s="5">
+        <f>IF(C6&gt;0,D6/C6,"")</f>
         <v>6018.71</v>
       </c>
     </row>
@@ -3206,10 +3221,15 @@
           <t xml:space="preserve">GRANOLA NUTRIFOODS 20X320GR</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="4">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5">
+        <v>36310.41</v>
+      </c>
       <c r="E12" s="5">
-        <v>1815.52</v>
+        <f>IF(C12&gt;0,D12/C12,"")</f>
+        <v>1815.5205</v>
       </c>
     </row>
     <row r="13">
@@ -3236,10 +3256,15 @@
           <t xml:space="preserve">FLYNN PAFF EST BANANA 12X8GR</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="4">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5">
+        <v>78408.44</v>
+      </c>
       <c r="E14" s="5">
-        <v>6534.04</v>
+        <f>IF(C14&gt;0,D14/C14,"")</f>
+        <v>6534.0366666666669</v>
       </c>
     </row>
     <row r="15">
@@ -3251,10 +3276,15 @@
           <t xml:space="preserve">FLYNN PAFF EST UVA 12X8GR</t>
         </is>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="4">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5">
+        <v>78408.44</v>
+      </c>
       <c r="E15" s="5">
-        <v>6534.04</v>
+        <f>IF(C15&gt;0,D15/C15,"")</f>
+        <v>6534.0366666666669</v>
       </c>
     </row>
     <row r="16">
@@ -3266,10 +3296,15 @@
           <t xml:space="preserve">FLYNN PAFF EST TUTTI FRUTTI 12X8GR</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="4">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5">
+        <v>78408.44</v>
+      </c>
       <c r="E16" s="5">
-        <v>6534.04</v>
+        <f>IF(C16&gt;0,D16/C16,"")</f>
+        <v>6534.0366666666669</v>
       </c>
     </row>
     <row r="17">
@@ -3281,10 +3316,15 @@
           <t xml:space="preserve">FLYNN PAFF CONFITADOS 1X50GR</t>
         </is>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="4">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5">
+        <v>26848.93</v>
+      </c>
       <c r="E17" s="5">
-        <v>894.96</v>
+        <f>IF(C17&gt;0,D17/C17,"")</f>
+        <v>894.96433333333334</v>
       </c>
     </row>
     <row r="18">
@@ -3296,10 +3336,15 @@
           <t xml:space="preserve">FLYNN PAFF EST MANZANA 12X8GR</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="4">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5">
+        <v>78408.44</v>
+      </c>
       <c r="E18" s="5">
-        <v>6534.04</v>
+        <f>IF(C18&gt;0,D18/C18,"")</f>
+        <v>6534.0366666666669</v>
       </c>
     </row>
     <row r="19">
@@ -3311,10 +3356,15 @@
           <t xml:space="preserve">FLYNN PAFF EST FRUTILLA 12X8GR</t>
         </is>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="4">
+        <v>12</v>
+      </c>
+      <c r="D19" s="5">
+        <v>6534.04</v>
+      </c>
       <c r="E19" s="5">
-        <v>6534.04</v>
+        <f>IF(C19&gt;0,D19/C19,"")</f>
+        <v>544.50333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3386,10 +3436,15 @@
           <t xml:space="preserve">CHOCOLATÍN BLANCO 8GR</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4">
+        <v>12</v>
+      </c>
+      <c r="D24" s="5">
+        <v>105771.09</v>
+      </c>
       <c r="E24" s="5">
-        <v>8814.26</v>
+        <f>IF(C24&gt;0,D24/C24,"")</f>
+        <v>8814.2575</v>
       </c>
     </row>
     <row r="25">
@@ -3401,10 +3456,15 @@
           <t xml:space="preserve">CHOCOLATÍN CON LECHE 8 GR</t>
         </is>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4">
+        <v>12</v>
+      </c>
+      <c r="D25" s="5">
+        <v>105771.09</v>
+      </c>
       <c r="E25" s="5">
-        <v>8814.26</v>
+        <f>IF(C25&gt;0,D25/C25,"")</f>
+        <v>8814.2575</v>
       </c>
     </row>
     <row r="26">
@@ -3446,9 +3506,14 @@
           <t xml:space="preserve">SIN AZUC CHOCOLATE CON LECHE 30GR</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4">
+        <v>12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>231161.16</v>
+      </c>
       <c r="E28" s="5">
+        <f>IF(C28&gt;0,D28/C28,"")</f>
         <v>19263.43</v>
       </c>
     </row>
@@ -3521,10 +3586,15 @@
           <t xml:space="preserve">ALMENDRAS CON CHOCOLATE 24x100gr</t>
         </is>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
+      <c r="C33" s="4">
+        <v>24</v>
+      </c>
+      <c r="D33" s="5">
+        <v>109914.66</v>
+      </c>
       <c r="E33" s="5">
-        <v>4579.78</v>
+        <f>IF(C33&gt;0,D33/C33,"")</f>
+        <v>4579.7775</v>
       </c>
     </row>
     <row r="34">
@@ -3581,10 +3651,15 @@
           <t xml:space="preserve">TURRÓN SEMIBLANDO DE MANÍ Y ALMENDRAS</t>
         </is>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
+      <c r="C37" s="4">
+        <v>36</v>
+      </c>
+      <c r="D37" s="5">
+        <v>52677.98</v>
+      </c>
       <c r="E37" s="5">
-        <v>1463.28</v>
+        <f>IF(C37&gt;0,D37/C37,"")</f>
+        <v>1463.2772222222222</v>
       </c>
     </row>
     <row r="38">
@@ -3596,10 +3671,15 @@
           <t xml:space="preserve">TURRÓN DE MANÍ CON FRUTAS</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
+      <c r="C38" s="4">
+        <v>24</v>
+      </c>
+      <c r="D38" s="5">
+        <v>47902.06</v>
+      </c>
       <c r="E38" s="5">
-        <v>1995.92</v>
+        <f>IF(C38&gt;0,D38/C38,"")</f>
+        <v>1995.9191666666666</v>
       </c>
     </row>
     <row r="39">
@@ -3611,10 +3691,15 @@
           <t xml:space="preserve">TABLETA CROCANTE DE MANÍ 24x150gr</t>
         </is>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
+      <c r="C39" s="4">
+        <v>24</v>
+      </c>
+      <c r="D39" s="5">
+        <v>55303.78</v>
+      </c>
       <c r="E39" s="5">
-        <v>2304.32</v>
+        <f>IF(C39&gt;0,D39/C39,"")</f>
+        <v>2304.3241666666668</v>
       </c>
     </row>
     <row r="40">
@@ -3626,10 +3711,15 @@
           <t xml:space="preserve">TURRON DE MANI CON MIEL 24X120GR</t>
         </is>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
+      <c r="C40" s="4">
+        <v>24</v>
+      </c>
+      <c r="D40" s="5">
+        <v>35184.86</v>
+      </c>
       <c r="E40" s="5">
-        <v>1466.04</v>
+        <f>IF(C40&gt;0,D40/C40,"")</f>
+        <v>1466.0358333333334</v>
       </c>
     </row>
     <row r="41">
@@ -3641,10 +3731,15 @@
           <t xml:space="preserve">TURRÓN DE MANÍ CON MIEL 1X36X80G</t>
         </is>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="4">
+        <v>36</v>
+      </c>
+      <c r="D41" s="5">
+        <v>36412.24</v>
+      </c>
       <c r="E41" s="5">
-        <v>1011.45</v>
+        <f>IF(C41&gt;0,D41/C41,"")</f>
+        <v>1011.451111111111</v>
       </c>
     </row>
     <row r="42">
@@ -3656,10 +3751,15 @@
           <t xml:space="preserve">TABLETA CROCANTE DE MANÍ 36x80gr</t>
         </is>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="4">
+        <v>36</v>
+      </c>
+      <c r="D42" s="5">
+        <v>42660.05</v>
+      </c>
       <c r="E42" s="5">
-        <v>1185</v>
+        <f>IF(C42&gt;0,D42/C42,"")</f>
+        <v>1185.0013888888889</v>
       </c>
     </row>
     <row r="43">
@@ -3671,10 +3771,15 @@
           <t xml:space="preserve">POCHOCLOS DULCE BIGGYS 20X100GR</t>
         </is>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
+      <c r="C43" s="4">
+        <v>20</v>
+      </c>
+      <c r="D43" s="5">
+        <v>34589.3</v>
+      </c>
       <c r="E43" s="5">
-        <v>1729.47</v>
+        <f>IF(C43&gt;0,D43/C43,"")</f>
+        <v>1729.4650000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3716,10 +3821,15 @@
           <t xml:space="preserve">TURRÓN BLANDO DE MANÍ CON YEMA 20x120gr</t>
         </is>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
+      <c r="C46" s="4">
+        <v>20</v>
+      </c>
+      <c r="D46" s="5">
+        <v>41386.36</v>
+      </c>
       <c r="E46" s="5">
-        <v>2069.32</v>
+        <f>IF(C46&gt;0,D46/C46,"")</f>
+        <v>2069.318</v>
       </c>
     </row>
     <row r="47">
@@ -3731,10 +3841,15 @@
           <t xml:space="preserve">TURRÓN BLANDO DE MANÍ CON YEMA Y FRUTAS 20x120gr</t>
         </is>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="5"/>
+      <c r="C47" s="4">
+        <v>20</v>
+      </c>
+      <c r="D47" s="5">
+        <v>40079.56</v>
+      </c>
       <c r="E47" s="5">
-        <v>2003.98</v>
+        <f>IF(C47&gt;0,D47/C47,"")</f>
+        <v>2003.9779999999998</v>
       </c>
     </row>
     <row r="48">
@@ -3791,9 +3906,14 @@
           <t xml:space="preserve">TURRÓN DE MANÍ BLANDO</t>
         </is>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
+      <c r="C51" s="4">
+        <v>36</v>
+      </c>
+      <c r="D51" s="5">
+        <v>47480.4</v>
+      </c>
       <c r="E51" s="5">
+        <f>IF(C51&gt;0,D51/C51,"")</f>
         <v>1318.9</v>
       </c>
     </row>
@@ -3806,10 +3926,15 @@
           <t xml:space="preserve">TABLETA DE CHOCOLATE RELLENA NOUGAT DE ALMENDRAS 24x100gr</t>
         </is>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
+      <c r="C52" s="4">
+        <v>24</v>
+      </c>
+      <c r="D52" s="5">
+        <v>76490.49</v>
+      </c>
       <c r="E52" s="5">
-        <v>3187.1</v>
+        <f>IF(C52&gt;0,D52/C52,"")</f>
+        <v>3187.10375</v>
       </c>
     </row>
     <row r="53">
@@ -3836,10 +3961,15 @@
           <t xml:space="preserve">GARAPIÑADA DE MANI NAMUR 36X60GR</t>
         </is>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
+      <c r="C54" s="4">
+        <v>36</v>
+      </c>
+      <c r="D54" s="5">
+        <v>21750.38</v>
+      </c>
       <c r="E54" s="5">
-        <v>604.18</v>
+        <f>IF(C54&gt;0,D54/C54,"")</f>
+        <v>604.17722222222221</v>
       </c>
     </row>
     <row r="55">
@@ -3851,9 +3981,14 @@
           <t xml:space="preserve">SIN AZUC CHOCO RELL YOG FRUT 30GR</t>
         </is>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
+      <c r="C55" s="4">
+        <v>12</v>
+      </c>
+      <c r="D55" s="5">
+        <v>231161.16</v>
+      </c>
       <c r="E55" s="5">
+        <f>IF(C55&gt;0,D55/C55,"")</f>
         <v>19263.43</v>
       </c>
     </row>
@@ -3926,10 +4061,15 @@
           <t xml:space="preserve">FLYNN PAFF BOLSA TUTTI FRUTTI  8X8GR</t>
         </is>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
+      <c r="C60" s="4">
+        <v>8</v>
+      </c>
+      <c r="D60" s="5">
+        <v>59696.95</v>
+      </c>
       <c r="E60" s="5">
-        <v>7462.12</v>
+        <f>IF(C60&gt;0,D60/C60,"")</f>
+        <v>7462.11875</v>
       </c>
     </row>
     <row r="61">
@@ -3941,10 +4081,15 @@
           <t xml:space="preserve">FLYNN PAFF BOLSA TUTTI FRUT  36X8GR</t>
         </is>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
+      <c r="C61" s="4">
+        <v>36</v>
+      </c>
+      <c r="D61" s="5">
+        <v>69747.4</v>
+      </c>
       <c r="E61" s="5">
-        <v>1937.43</v>
+        <f>IF(C61&gt;0,D61/C61,"")</f>
+        <v>1937.4277777777777</v>
       </c>
     </row>
     <row r="62">
@@ -3956,9 +4101,14 @@
           <t xml:space="preserve">TABLETA DE CHOCOLATE RELLENA CREMA CATALANA 24x100gr</t>
         </is>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
+      <c r="C62" s="4">
+        <v>24</v>
+      </c>
+      <c r="D62" s="5">
+        <v>83141.52</v>
+      </c>
       <c r="E62" s="5">
+        <f>IF(C62&gt;0,D62/C62,"")</f>
         <v>3464.23</v>
       </c>
     </row>
@@ -4061,10 +4211,15 @@
           <t xml:space="preserve">TURRON DE MANI NAMUR 36X70GR</t>
         </is>
       </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="5"/>
+      <c r="C69" s="4">
+        <v>36</v>
+      </c>
+      <c r="D69" s="5">
+        <v>25062.25</v>
+      </c>
       <c r="E69" s="5">
-        <v>696.17</v>
+        <f>IF(C69&gt;0,D69/C69,"")</f>
+        <v>696.17361111111109</v>
       </c>
     </row>
     <row r="70">
@@ -4136,10 +4291,15 @@
           <t xml:space="preserve">COPOS AZUCARADOS 21 x 400 grs</t>
         </is>
       </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="5"/>
+      <c r="C74" s="4">
+        <v>21</v>
+      </c>
+      <c r="D74" s="5">
+        <v>31851.44</v>
+      </c>
       <c r="E74" s="5">
-        <v>1516.74</v>
+        <f>IF(C74&gt;0,D74/C74,"")</f>
+        <v>1516.7352380952379</v>
       </c>
     </row>
     <row r="75">
@@ -4211,10 +4371,15 @@
           <t xml:space="preserve">TODDY CRUN EXTBOL DE CHOCO 200GR</t>
         </is>
       </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="5"/>
+      <c r="C79" s="4">
+        <v>16</v>
+      </c>
+      <c r="D79" s="5">
+        <v>43947.59</v>
+      </c>
       <c r="E79" s="5">
-        <v>2746.72</v>
+        <f>IF(C79&gt;0,D79/C79,"")</f>
+        <v>2746.724375</v>
       </c>
     </row>
     <row r="80">
@@ -4226,10 +4391,15 @@
           <t xml:space="preserve">CEREAL  FLYNN PAFF CARAM 200GR</t>
         </is>
       </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="5"/>
+      <c r="C80" s="4">
+        <v>16</v>
+      </c>
+      <c r="D80" s="5">
+        <v>41137.68</v>
+      </c>
       <c r="E80" s="5">
-        <v>2571.1</v>
+        <f>IF(C80&gt;0,D80/C80,"")</f>
+        <v>2571.105</v>
       </c>
     </row>
     <row r="81">
@@ -4241,10 +4411,15 @@
           <t xml:space="preserve">FLOW GRANOLA CHOCO 20X320GR</t>
         </is>
       </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="5"/>
+      <c r="C81" s="4">
+        <v>20</v>
+      </c>
+      <c r="D81" s="5">
+        <v>76463.77</v>
+      </c>
       <c r="E81" s="5">
-        <v>3823.19</v>
+        <f>IF(C81&gt;0,D81/C81,"")</f>
+        <v>3823.1885</v>
       </c>
     </row>
     <row r="82">
@@ -4256,10 +4431,15 @@
           <t xml:space="preserve">MANTECOL ALMOHADITAS 16X180GR</t>
         </is>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="5"/>
+      <c r="C82" s="4">
+        <v>16</v>
+      </c>
+      <c r="D82" s="5">
+        <v>43947.59</v>
+      </c>
       <c r="E82" s="5">
-        <v>2746.72</v>
+        <f>IF(C82&gt;0,D82/C82,"")</f>
+        <v>2746.724375</v>
       </c>
     </row>
     <row r="83">
@@ -4271,10 +4451,15 @@
           <t xml:space="preserve">TODDY ALMOHADITAS RELLENAS CHOCOLATE 16X180GR</t>
         </is>
       </c>
-      <c r="C83" s="4"/>
-      <c r="D83" s="5"/>
+      <c r="C83" s="4">
+        <v>16</v>
+      </c>
+      <c r="D83" s="5">
+        <v>43947.59</v>
+      </c>
       <c r="E83" s="5">
-        <v>2746.72</v>
+        <f>IF(C83&gt;0,D83/C83,"")</f>
+        <v>2746.724375</v>
       </c>
     </row>
     <row r="84">
@@ -4286,10 +4471,15 @@
           <t xml:space="preserve">FLOW CEREAL HONEY CRUNCH 16X180G</t>
         </is>
       </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="5"/>
+      <c r="C84" s="4">
+        <v>16</v>
+      </c>
+      <c r="D84" s="5">
+        <v>31946.52</v>
+      </c>
       <c r="E84" s="5">
-        <v>1996.66</v>
+        <f>IF(C84&gt;0,D84/C84,"")</f>
+        <v>1996.6575</v>
       </c>
     </row>
     <row r="85">
@@ -4301,10 +4491,15 @@
           <t xml:space="preserve">FLOW BARR GRAN C/CHIPS CHO 20X23GR</t>
         </is>
       </c>
-      <c r="C85" s="4"/>
-      <c r="D85" s="5"/>
+      <c r="C85" s="4">
+        <v>6</v>
+      </c>
+      <c r="D85" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E85" s="5">
-        <v>13165.34</v>
+        <f>IF(C85&gt;0,D85/C85,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="86">
@@ -4331,10 +4526,15 @@
           <t xml:space="preserve">FLOW BARR GRA/FRUT D/BOS 20X23GR</t>
         </is>
       </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="5"/>
+      <c r="C87" s="4">
+        <v>6</v>
+      </c>
+      <c r="D87" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E87" s="5">
-        <v>13165.34</v>
+        <f>IF(C87&gt;0,D87/C87,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="88">
@@ -4346,10 +4546,15 @@
           <t xml:space="preserve">FLOW BARR FRU D/ BOS C/YOG 20X27GR</t>
         </is>
       </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="5"/>
+      <c r="C88" s="4">
+        <v>6</v>
+      </c>
+      <c r="D88" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E88" s="5">
-        <v>13165.34</v>
+        <f>IF(C88&gt;0,D88/C88,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="89">
@@ -4361,10 +4566,15 @@
           <t xml:space="preserve">FLOW BARRA MANZANA LIGHT 20X21GR</t>
         </is>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="5"/>
+      <c r="C89" s="4">
+        <v>6</v>
+      </c>
+      <c r="D89" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E89" s="5">
-        <v>13165.34</v>
+        <f>IF(C89&gt;0,D89/C89,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="90">
@@ -4376,10 +4586,15 @@
           <t xml:space="preserve">FLOW BARRA CON FRUTAS 20X23GR</t>
         </is>
       </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="5"/>
+      <c r="C90" s="4">
+        <v>6</v>
+      </c>
+      <c r="D90" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E90" s="5">
-        <v>13165.34</v>
+        <f>IF(C90&gt;0,D90/C90,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="91">
@@ -4391,10 +4606,15 @@
           <t xml:space="preserve">FLOW BARRA YOGHURT LIGHT 24GR</t>
         </is>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="5"/>
+      <c r="C91" s="4">
+        <v>6</v>
+      </c>
+      <c r="D91" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E91" s="5">
-        <v>13165.34</v>
+        <f>IF(C91&gt;0,D91/C91,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="92">
@@ -4406,10 +4626,15 @@
           <t xml:space="preserve">FLOW BARRA ALMEN ENTERAS 30GR</t>
         </is>
       </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="5"/>
+      <c r="C92" s="4">
+        <v>6</v>
+      </c>
+      <c r="D92" s="5">
+        <v>93418.99</v>
+      </c>
       <c r="E92" s="5">
-        <v>15569.83</v>
+        <f>IF(C92&gt;0,D92/C92,"")</f>
+        <v>15569.831666666667</v>
       </c>
     </row>
     <row r="93">
@@ -4571,10 +4796,15 @@
           <t xml:space="preserve">TODDY BARRA DE CEREAL 21GR</t>
         </is>
       </c>
-      <c r="C103" s="4"/>
-      <c r="D103" s="5"/>
+      <c r="C103" s="4">
+        <v>6</v>
+      </c>
+      <c r="D103" s="5">
+        <v>78992.07</v>
+      </c>
       <c r="E103" s="5">
-        <v>13165.34</v>
+        <f>IF(C103&gt;0,D103/C103,"")</f>
+        <v>13165.345000000001</v>
       </c>
     </row>
     <row r="104">
@@ -4736,10 +4966,15 @@
           <t xml:space="preserve">TODDY MINI GALLE CHI CHOCO 50GR</t>
         </is>
       </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="5"/>
+      <c r="C114" s="4">
+        <v>36</v>
+      </c>
+      <c r="D114" s="5">
+        <v>30742.03</v>
+      </c>
       <c r="E114" s="5">
-        <v>853.95</v>
+        <f>IF(C114&gt;0,D114/C114,"")</f>
+        <v>853.94527777777773</v>
       </c>
     </row>
     <row r="115">
@@ -4751,10 +4986,15 @@
           <t xml:space="preserve">TODDY ALFAJOR MOUSSE 24X 50GR</t>
         </is>
       </c>
-      <c r="C115" s="4"/>
-      <c r="D115" s="5"/>
+      <c r="C115" s="4">
+        <v>24</v>
+      </c>
+      <c r="D115" s="5">
+        <v>20766.79</v>
+      </c>
       <c r="E115" s="5">
-        <v>865.28</v>
+        <f>IF(C115&gt;0,D115/C115,"")</f>
+        <v>865.28291666666667</v>
       </c>
     </row>
     <row r="116">
@@ -4766,10 +5006,15 @@
           <t xml:space="preserve">TODDY  POLVO S/ AZÚCAR 1X12 X150gr</t>
         </is>
       </c>
-      <c r="C116" s="4"/>
-      <c r="D116" s="5"/>
+      <c r="C116" s="4">
+        <v>12</v>
+      </c>
+      <c r="D116" s="5">
+        <v>9495.21</v>
+      </c>
       <c r="E116" s="5">
-        <v>791.27</v>
+        <f>IF(C116&gt;0,D116/C116,"")</f>
+        <v>791.26749999999993</v>
       </c>
     </row>
     <row r="117">
@@ -4781,9 +5026,14 @@
           <t xml:space="preserve">TODDY CACAO AVELLANAS 12X150G</t>
         </is>
       </c>
-      <c r="C117" s="4"/>
-      <c r="D117" s="5"/>
+      <c r="C117" s="4">
+        <v>12</v>
+      </c>
+      <c r="D117" s="5">
+        <v>17690.88</v>
+      </c>
       <c r="E117" s="5">
+        <f>IF(C117&gt;0,D117/C117,"")</f>
         <v>1474.24</v>
       </c>
     </row>
@@ -4796,10 +5046,15 @@
           <t xml:space="preserve">TODDY ALFAJOR MOUSE BLANCO 24X50G</t>
         </is>
       </c>
-      <c r="C118" s="4"/>
-      <c r="D118" s="5"/>
+      <c r="C118" s="4">
+        <v>24</v>
+      </c>
+      <c r="D118" s="5">
+        <v>20766.79</v>
+      </c>
       <c r="E118" s="5">
-        <v>865.28</v>
+        <f>IF(C118&gt;0,D118/C118,"")</f>
+        <v>865.28291666666667</v>
       </c>
     </row>
     <row r="119">
@@ -4811,10 +5066,15 @@
           <t xml:space="preserve">TODDY ALFAJOR TRIPLE MOUSSE</t>
         </is>
       </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="5"/>
+      <c r="C119" s="4">
+        <v>20</v>
+      </c>
+      <c r="D119" s="5">
+        <v>25402.5</v>
+      </c>
       <c r="E119" s="5">
-        <v>1270.12</v>
+        <f>IF(C119&gt;0,D119/C119,"")</f>
+        <v>1270.125</v>
       </c>
     </row>
     <row r="120">
@@ -4826,10 +5086,15 @@
           <t xml:space="preserve">TODDY GALLETAS OBLEAS 40ux85gr</t>
         </is>
       </c>
-      <c r="C120" s="4"/>
-      <c r="D120" s="5"/>
+      <c r="C120" s="4">
+        <v>40</v>
+      </c>
+      <c r="D120" s="5">
+        <v>45280.62</v>
+      </c>
       <c r="E120" s="5">
-        <v>1132.02</v>
+        <f>IF(C120&gt;0,D120/C120,"")</f>
+        <v>1132.0155</v>
       </c>
     </row>
     <row r="121">
@@ -4871,10 +5136,15 @@
           <t xml:space="preserve">COLMENITA CHOCO  C/LECH 25GR</t>
         </is>
       </c>
-      <c r="C123" s="4"/>
-      <c r="D123" s="5"/>
+      <c r="C123" s="4">
+        <v>12</v>
+      </c>
+      <c r="D123" s="5">
+        <v>196267.42</v>
+      </c>
       <c r="E123" s="5">
-        <v>16355.62</v>
+        <f>IF(C123&gt;0,D123/C123,"")</f>
+        <v>16355.618333333334</v>
       </c>
     </row>
     <row r="124">
@@ -4886,10 +5156,15 @@
           <t xml:space="preserve">COLMENITA CHOCO BLANCO  25GR</t>
         </is>
       </c>
-      <c r="C124" s="4"/>
-      <c r="D124" s="5"/>
+      <c r="C124" s="4">
+        <v>12</v>
+      </c>
+      <c r="D124" s="5">
+        <v>196267.42</v>
+      </c>
       <c r="E124" s="5">
-        <v>16355.62</v>
+        <f>IF(C124&gt;0,D124/C124,"")</f>
+        <v>16355.618333333334</v>
       </c>
     </row>
     <row r="125">
@@ -4976,10 +5251,15 @@
           <t xml:space="preserve">SIN AZUC CHOCOLATE CON LECHE 70GR</t>
         </is>
       </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="5"/>
+      <c r="C130" s="4">
+        <v>4</v>
+      </c>
+      <c r="D130" s="5">
+        <v>149431.71</v>
+      </c>
       <c r="E130" s="5">
-        <v>37357.93</v>
+        <f>IF(C130&gt;0,D130/C130,"")</f>
+        <v>37357.9275</v>
       </c>
     </row>
     <row r="131">
@@ -5036,10 +5316,15 @@
           <t xml:space="preserve">FULL MANI RELLENO 6X10X110g</t>
         </is>
       </c>
-      <c r="C134" s="4"/>
-      <c r="D134" s="5"/>
+      <c r="C134" s="4">
+        <v>10</v>
+      </c>
+      <c r="D134" s="5">
+        <v>215332.33</v>
+      </c>
       <c r="E134" s="5">
-        <v>21533.23</v>
+        <f>IF(C134&gt;0,D134/C134,"")</f>
+        <v>21533.233</v>
       </c>
     </row>
     <row r="135">
@@ -5066,10 +5351,15 @@
           <t xml:space="preserve">FULL MANI CHOCOLATE 20UX150G</t>
         </is>
       </c>
-      <c r="C136" s="4"/>
-      <c r="D136" s="5"/>
+      <c r="C136" s="4">
+        <v>20</v>
+      </c>
+      <c r="D136" s="5">
+        <v>68579.9</v>
+      </c>
       <c r="E136" s="5">
-        <v>3428.99</v>
+        <f>IF(C136&gt;0,D136/C136,"")</f>
+        <v>3428.995</v>
       </c>
     </row>
     <row r="137">
@@ -5081,10 +5371,15 @@
           <t xml:space="preserve">TODDY CHOCOLATE LECHE RELLENO DE MOUSE 6X10X60GR</t>
         </is>
       </c>
-      <c r="C137" s="4"/>
-      <c r="D137" s="5"/>
+      <c r="C137" s="4">
+        <v>10</v>
+      </c>
+      <c r="D137" s="5">
+        <v>20740.61</v>
+      </c>
       <c r="E137" s="5">
-        <v>2074.06</v>
+        <f>IF(C137&gt;0,D137/C137,"")</f>
+        <v>2074.061</v>
       </c>
     </row>
     <row r="138">
@@ -5096,10 +5391,15 @@
           <t xml:space="preserve">TODDY CHOCOLATE RELLENO MILK 6X10X60GR</t>
         </is>
       </c>
-      <c r="C138" s="4"/>
-      <c r="D138" s="5"/>
+      <c r="C138" s="4">
+        <v>10</v>
+      </c>
+      <c r="D138" s="5">
+        <v>20740.61</v>
+      </c>
       <c r="E138" s="5">
-        <v>2074.06</v>
+        <f>IF(C138&gt;0,D138/C138,"")</f>
+        <v>2074.061</v>
       </c>
     </row>
     <row r="139">
@@ -5111,10 +5411,15 @@
           <t xml:space="preserve">TODDY CHOCOLATE BLANCO CON COOKIES 6X10X50GR</t>
         </is>
       </c>
-      <c r="C139" s="4"/>
-      <c r="D139" s="5"/>
+      <c r="C139" s="4">
+        <v>10</v>
+      </c>
+      <c r="D139" s="5">
+        <v>20740.61</v>
+      </c>
       <c r="E139" s="5">
-        <v>2074.06</v>
+        <f>IF(C139&gt;0,D139/C139,"")</f>
+        <v>2074.061</v>
       </c>
     </row>
     <row r="140">
@@ -5126,10 +5431,15 @@
           <t xml:space="preserve">FULL MANI CHOCOLATE 12DX24UX13GR</t>
         </is>
       </c>
-      <c r="C140" s="4"/>
-      <c r="D140" s="5"/>
+      <c r="C140" s="4">
+        <v>12</v>
+      </c>
+      <c r="D140" s="5">
+        <v>132980.69</v>
+      </c>
       <c r="E140" s="5">
-        <v>11081.72</v>
+        <f>IF(C140&gt;0,D140/C140,"")</f>
+        <v>11081.724166666667</v>
       </c>
     </row>
     <row r="141">
@@ -5141,10 +5451,15 @@
           <t xml:space="preserve">FULL MANI CHOCOLATE 8DX15UX30G</t>
         </is>
       </c>
-      <c r="C141" s="4"/>
-      <c r="D141" s="5"/>
+      <c r="C141" s="4">
+        <v>8</v>
+      </c>
+      <c r="D141" s="5">
+        <v>115059.87</v>
+      </c>
       <c r="E141" s="5">
-        <v>14382.48</v>
+        <f>IF(C141&gt;0,D141/C141,"")</f>
+        <v>14382.48375</v>
       </c>
     </row>
     <row r="142">
@@ -5171,10 +5486,15 @@
           <t xml:space="preserve">ALFAJOR FULL MANI PASTA DE MANI 24UX40GR</t>
         </is>
       </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="5"/>
+      <c r="C143" s="4">
+        <v>24</v>
+      </c>
+      <c r="D143" s="5">
+        <v>15587.8</v>
+      </c>
       <c r="E143" s="5">
-        <v>649.49</v>
+        <f>IF(C143&gt;0,D143/C143,"")</f>
+        <v>649.49166666666667</v>
       </c>
     </row>
     <row r="144">
@@ -5186,9 +5506,14 @@
           <t xml:space="preserve">TODDY CUBANITO 12DX40UX10G</t>
         </is>
       </c>
-      <c r="C144" s="4"/>
-      <c r="D144" s="5"/>
+      <c r="C144" s="4">
+        <v>12</v>
+      </c>
+      <c r="D144" s="5">
+        <v>125447.28</v>
+      </c>
       <c r="E144" s="5">
+        <f>IF(C144&gt;0,D144/C144,"")</f>
         <v>10453.94</v>
       </c>
     </row>
@@ -5201,9 +5526,14 @@
           <t xml:space="preserve">FULL MANI RELLENO 8DX15UX35GR</t>
         </is>
       </c>
-      <c r="C145" s="4"/>
-      <c r="D145" s="5"/>
+      <c r="C145" s="4">
+        <v>8</v>
+      </c>
+      <c r="D145" s="5">
+        <v>121115.68</v>
+      </c>
       <c r="E145" s="5">
+        <f>IF(C145&gt;0,D145/C145,"")</f>
         <v>15139.46</v>
       </c>
     </row>
@@ -5216,10 +5546,15 @@
           <t xml:space="preserve">FULL MANI CHOCOLATE 8UX500GR</t>
         </is>
       </c>
-      <c r="C146" s="4"/>
-      <c r="D146" s="5"/>
+      <c r="C146" s="4">
+        <v>8</v>
+      </c>
+      <c r="D146" s="5">
+        <v>74209.88</v>
+      </c>
       <c r="E146" s="5">
-        <v>9276.24</v>
+        <f>IF(C146&gt;0,D146/C146,"")</f>
+        <v>9276.235</v>
       </c>
     </row>
     <row r="147">
@@ -5231,10 +5566,15 @@
           <t xml:space="preserve">MANTECOL LINGOTE 500GR</t>
         </is>
       </c>
-      <c r="C147" s="4"/>
-      <c r="D147" s="5"/>
+      <c r="C147" s="4">
+        <v>8</v>
+      </c>
+      <c r="D147" s="5">
+        <v>89400.41</v>
+      </c>
       <c r="E147" s="5">
-        <v>11175.05</v>
+        <f>IF(C147&gt;0,D147/C147,"")</f>
+        <v>11175.05125</v>
       </c>
     </row>
     <row r="148">
@@ -5246,10 +5586,15 @@
           <t xml:space="preserve">MANTECOL BAÑADO C/CHOCO 20GR</t>
         </is>
       </c>
-      <c r="C148" s="4"/>
-      <c r="D148" s="5"/>
+      <c r="C148" s="4">
+        <v>12</v>
+      </c>
+      <c r="D148" s="5">
+        <v>169898.81</v>
+      </c>
       <c r="E148" s="5">
-        <v>14158.23</v>
+        <f>IF(C148&gt;0,D148/C148,"")</f>
+        <v>14158.234166666667</v>
       </c>
     </row>
     <row r="149">
@@ -5276,10 +5621,15 @@
           <t xml:space="preserve">Mantecol Untable 1x16x250gr</t>
         </is>
       </c>
-      <c r="C150" s="4"/>
-      <c r="D150" s="5"/>
+      <c r="C150" s="4">
+        <v>16</v>
+      </c>
+      <c r="D150" s="5">
+        <v>34112.71</v>
+      </c>
       <c r="E150" s="5">
-        <v>2132.04</v>
+        <f>IF(C150&gt;0,D150/C150,"")</f>
+        <v>2132.044375</v>
       </c>
     </row>
     <row r="151">
@@ -5291,10 +5641,15 @@
           <t xml:space="preserve">MANTECOL OBLEA 8x18x27gr</t>
         </is>
       </c>
-      <c r="C151" s="4"/>
-      <c r="D151" s="5"/>
+      <c r="C151" s="4">
+        <v>8</v>
+      </c>
+      <c r="D151" s="5">
+        <v>96957.01</v>
+      </c>
       <c r="E151" s="5">
-        <v>12119.63</v>
+        <f>IF(C151&gt;0,D151/C151,"")</f>
+        <v>12119.62625</v>
       </c>
     </row>
     <row r="152">
@@ -5306,9 +5661,14 @@
           <t xml:space="preserve">MANTECOL CUBANITO 12X40X10GR</t>
         </is>
       </c>
-      <c r="C152" s="4"/>
-      <c r="D152" s="5"/>
+      <c r="C152" s="4">
+        <v>12</v>
+      </c>
+      <c r="D152" s="5">
+        <v>125447.28</v>
+      </c>
       <c r="E152" s="5">
+        <f>IF(C152&gt;0,D152/C152,"")</f>
         <v>10453.94</v>
       </c>
     </row>
@@ -5321,10 +5681,15 @@
           <t xml:space="preserve">MANTECOL ALFAJOR RELLENO PASTA MANTECOL 24UX40G</t>
         </is>
       </c>
-      <c r="C153" s="4"/>
-      <c r="D153" s="5"/>
+      <c r="C153" s="4">
+        <v>24</v>
+      </c>
+      <c r="D153" s="5">
+        <v>18202.85</v>
+      </c>
       <c r="E153" s="5">
-        <v>758.45</v>
+        <f>IF(C153&gt;0,D153/C153,"")</f>
+        <v>758.45208333333323</v>
       </c>
     </row>
     <row r="154">
@@ -5336,10 +5701,15 @@
           <t xml:space="preserve">MANTECOL GALLETAS OBLEAS 40UX85GR</t>
         </is>
       </c>
-      <c r="C154" s="4"/>
-      <c r="D154" s="5"/>
+      <c r="C154" s="4">
+        <v>40</v>
+      </c>
+      <c r="D154" s="5">
+        <v>45280.62</v>
+      </c>
       <c r="E154" s="5">
-        <v>1132.02</v>
+        <f>IF(C154&gt;0,D154/C154,"")</f>
+        <v>1132.0155</v>
       </c>
     </row>
     <row r="155">
@@ -5351,10 +5721,15 @@
           <t xml:space="preserve">MANTECOL ALFAJOR TRIPLE 20UX60G</t>
         </is>
       </c>
-      <c r="C155" s="4"/>
-      <c r="D155" s="5"/>
+      <c r="C155" s="4">
+        <v>20</v>
+      </c>
+      <c r="D155" s="5">
+        <v>25402.5</v>
+      </c>
       <c r="E155" s="5">
-        <v>1270.12</v>
+        <f>IF(C155&gt;0,D155/C155,"")</f>
+        <v>1270.125</v>
       </c>
     </row>
     <row r="156">
@@ -5366,10 +5741,15 @@
           <t xml:space="preserve">FLYNN PAFF XXL 12X24X30GR</t>
         </is>
       </c>
-      <c r="C156" s="4"/>
-      <c r="D156" s="5"/>
+      <c r="C156" s="4">
+        <v>12</v>
+      </c>
+      <c r="D156" s="5">
+        <v>102930.54</v>
+      </c>
       <c r="E156" s="5">
-        <v>8577.54</v>
+        <f>IF(C156&gt;0,D156/C156,"")</f>
+        <v>8577.545</v>
       </c>
     </row>
     <row r="157">
@@ -5411,10 +5791,15 @@
           <t xml:space="preserve">FLYNN PAFF EST YOG FRUT BAN 12X8GR</t>
         </is>
       </c>
-      <c r="C159" s="4"/>
-      <c r="D159" s="5"/>
+      <c r="C159" s="4">
+        <v>12</v>
+      </c>
+      <c r="D159" s="5">
+        <v>73196.19</v>
+      </c>
       <c r="E159" s="5">
-        <v>6099.68</v>
+        <f>IF(C159&gt;0,D159/C159,"")</f>
+        <v>6099.6825</v>
       </c>
     </row>
     <row r="160">
@@ -5426,10 +5811,15 @@
           <t xml:space="preserve">FLYNN PAFF EST LIMONA BERRY 12X8GR</t>
         </is>
       </c>
-      <c r="C160" s="4"/>
-      <c r="D160" s="5"/>
+      <c r="C160" s="4">
+        <v>12</v>
+      </c>
+      <c r="D160" s="5">
+        <v>76124.44</v>
+      </c>
       <c r="E160" s="5">
-        <v>6343.7</v>
+        <f>IF(C160&gt;0,D160/C160,"")</f>
+        <v>6343.7033333333338</v>
       </c>
     </row>
     <row r="161">
@@ -5441,10 +5831,15 @@
           <t xml:space="preserve">FLYNN PAFF XXL LIMO-BERRY 12X24X30GR</t>
         </is>
       </c>
-      <c r="C161" s="4"/>
-      <c r="D161" s="5"/>
+      <c r="C161" s="4">
+        <v>12</v>
+      </c>
+      <c r="D161" s="5">
+        <v>102930.54</v>
+      </c>
       <c r="E161" s="5">
-        <v>8577.54</v>
+        <f>IF(C161&gt;0,D161/C161,"")</f>
+        <v>8577.545</v>
       </c>
     </row>
     <row r="162">
@@ -5486,10 +5881,15 @@
           <t xml:space="preserve">FLYNN PAFF JELLY BEANS ACIDO XTREMO 12DX12UX40GR</t>
         </is>
       </c>
-      <c r="C164" s="4"/>
-      <c r="D164" s="5"/>
+      <c r="C164" s="4">
+        <v>12</v>
+      </c>
+      <c r="D164" s="5">
+        <v>112388.72</v>
+      </c>
       <c r="E164" s="5">
-        <v>9365.73</v>
+        <f>IF(C164&gt;0,D164/C164,"")</f>
+        <v>9365.7266666666674</v>
       </c>
     </row>
     <row r="165">
@@ -5501,10 +5901,15 @@
           <t xml:space="preserve">FLYNN PAFF BOLSA UVA 36X8GR</t>
         </is>
       </c>
-      <c r="C165" s="4"/>
-      <c r="D165" s="5"/>
+      <c r="C165" s="4">
+        <v>36</v>
+      </c>
+      <c r="D165" s="5">
+        <v>72430.26</v>
+      </c>
       <c r="E165" s="5">
-        <v>2011.95</v>
+        <f>IF(C165&gt;0,D165/C165,"")</f>
+        <v>2011.9516666666666</v>
       </c>
     </row>
     <row r="166">
@@ -5516,10 +5921,15 @@
           <t xml:space="preserve">FLYNN PAFF BOLSA FRUTILLA 36X8GR</t>
         </is>
       </c>
-      <c r="C166" s="4"/>
-      <c r="D166" s="5"/>
+      <c r="C166" s="4">
+        <v>36</v>
+      </c>
+      <c r="D166" s="5">
+        <v>72430.26</v>
+      </c>
       <c r="E166" s="5">
-        <v>2011.95</v>
+        <f>IF(C166&gt;0,D166/C166,"")</f>
+        <v>2011.9516666666666</v>
       </c>
     </row>
     <row r="167">
@@ -5531,10 +5941,15 @@
           <t xml:space="preserve">FLYNN PAFF BOLSA SURTIDA 36X8GR</t>
         </is>
       </c>
-      <c r="C167" s="4"/>
-      <c r="D167" s="5"/>
+      <c r="C167" s="4">
+        <v>36</v>
+      </c>
+      <c r="D167" s="5">
+        <v>54091.94</v>
+      </c>
       <c r="E167" s="5">
-        <v>1502.55</v>
+        <f>IF(C167&gt;0,D167/C167,"")</f>
+        <v>1502.5538888888889</v>
       </c>
     </row>
     <row r="168">
@@ -5561,10 +5976,15 @@
           <t xml:space="preserve">FLYNN PAFF CHUPETÍN CEREZA 18X18GR</t>
         </is>
       </c>
-      <c r="C169" s="4"/>
-      <c r="D169" s="5"/>
+      <c r="C169" s="4">
+        <v>18</v>
+      </c>
+      <c r="D169" s="5">
+        <v>89558.27</v>
+      </c>
       <c r="E169" s="5">
-        <v>4975.46</v>
+        <f>IF(C169&gt;0,D169/C169,"")</f>
+        <v>4975.4594444444447</v>
       </c>
     </row>
     <row r="170">
@@ -5576,10 +5996,15 @@
           <t xml:space="preserve">FLYNN PAFF CHUP SAND-MELON 18X18GR</t>
         </is>
       </c>
-      <c r="C170" s="4"/>
-      <c r="D170" s="5"/>
+      <c r="C170" s="4">
+        <v>18</v>
+      </c>
+      <c r="D170" s="5">
+        <v>99509.12</v>
+      </c>
       <c r="E170" s="5">
-        <v>5528.28</v>
+        <f>IF(C170&gt;0,D170/C170,"")</f>
+        <v>5528.2844444444445</v>
       </c>
     </row>
     <row r="171">
@@ -5636,10 +6061,15 @@
           <t xml:space="preserve">FLYNN PAFF CHUPETÍN UVA 18X18GR</t>
         </is>
       </c>
-      <c r="C174" s="4"/>
-      <c r="D174" s="5"/>
+      <c r="C174" s="4">
+        <v>18</v>
+      </c>
+      <c r="D174" s="5">
+        <v>99509.12</v>
+      </c>
       <c r="E174" s="5">
-        <v>5528.28</v>
+        <f>IF(C174&gt;0,D174/C174,"")</f>
+        <v>5528.2844444444445</v>
       </c>
     </row>
     <row r="175">
@@ -5651,10 +6081,15 @@
           <t xml:space="preserve">FLYNN PAFF CHUPETÍN MANZ 18X18GR</t>
         </is>
       </c>
-      <c r="C175" s="4"/>
-      <c r="D175" s="5"/>
+      <c r="C175" s="4">
+        <v>18</v>
+      </c>
+      <c r="D175" s="5">
+        <v>99509.12</v>
+      </c>
       <c r="E175" s="5">
-        <v>5528.28</v>
+        <f>IF(C175&gt;0,D175/C175,"")</f>
+        <v>5528.2844444444445</v>
       </c>
     </row>
     <row r="176">
@@ -5726,10 +6161,15 @@
           <t xml:space="preserve">FLYNN PAFF GOMI SURT AZU 16X220GR</t>
         </is>
       </c>
-      <c r="C180" s="4"/>
-      <c r="D180" s="5"/>
+      <c r="C180" s="4">
+        <v>16</v>
+      </c>
+      <c r="D180" s="5">
+        <v>34047.66</v>
+      </c>
       <c r="E180" s="5">
-        <v>2127.98</v>
+        <f>IF(C180&gt;0,D180/C180,"")</f>
+        <v>2127.97875</v>
       </c>
     </row>
     <row r="181">
@@ -5801,10 +6241,15 @@
           <t xml:space="preserve">HP MANTECOL CON BOCADITO SEMIAMARGO 15X200 GRS</t>
         </is>
       </c>
-      <c r="C185" s="4"/>
-      <c r="D185" s="5"/>
+      <c r="C185" s="4">
+        <v>15</v>
+      </c>
+      <c r="D185" s="5">
+        <v>200461.12</v>
+      </c>
       <c r="E185" s="5">
-        <v>13364.07</v>
+        <f>IF(C185&gt;0,D185/C185,"")</f>
+        <v>13364.074666666666</v>
       </c>
     </row>
     <row r="186">
@@ -5846,10 +6291,15 @@
           <t xml:space="preserve">HP TODDY  LECHE CON MINI COOKIES CON CHIPS 18X126</t>
         </is>
       </c>
-      <c r="C188" s="4"/>
-      <c r="D188" s="5"/>
+      <c r="C188" s="4">
+        <v>18</v>
+      </c>
+      <c r="D188" s="5">
+        <v>142450.13</v>
+      </c>
       <c r="E188" s="5">
-        <v>7913.9</v>
+        <f>IF(C188&gt;0,D188/C188,"")</f>
+        <v>7913.8961111111112</v>
       </c>
     </row>
     <row r="189">
@@ -5876,10 +6326,15 @@
           <t xml:space="preserve">HP TODDY CON CONFITES DE CHOCOLATE 12X22 GRS</t>
         </is>
       </c>
-      <c r="C190" s="4"/>
-      <c r="D190" s="5"/>
+      <c r="C190" s="4">
+        <v>6</v>
+      </c>
+      <c r="D190" s="5">
+        <v>72942.16</v>
+      </c>
       <c r="E190" s="5">
-        <v>12157.03</v>
+        <f>IF(C190&gt;0,D190/C190,"")</f>
+        <v>12157.026666666667</v>
       </c>
     </row>
     <row r="191">
@@ -5891,10 +6346,15 @@
           <t xml:space="preserve">HP TODDY CRUNCH EXTREMO 24X75 GRS</t>
         </is>
       </c>
-      <c r="C191" s="4"/>
-      <c r="D191" s="5"/>
+      <c r="C191" s="4">
+        <v>24</v>
+      </c>
+      <c r="D191" s="5">
+        <v>81027.99</v>
+      </c>
       <c r="E191" s="5">
-        <v>3376.17</v>
+        <f>IF(C191&gt;0,D191/C191,"")</f>
+        <v>3376.16625</v>
       </c>
     </row>
     <row r="192">
@@ -5906,10 +6366,15 @@
           <t xml:space="preserve">HP FULL MANI C/ MANI C/ CHOCOLATE 18X100 GRS</t>
         </is>
       </c>
-      <c r="C192" s="4"/>
-      <c r="D192" s="5"/>
+      <c r="C192" s="4">
+        <v>18</v>
+      </c>
+      <c r="D192" s="5">
+        <v>102624.09</v>
+      </c>
       <c r="E192" s="5">
-        <v>5701.34</v>
+        <f>IF(C192&gt;0,D192/C192,"")</f>
+        <v>5701.3383333333331</v>
       </c>
     </row>
     <row r="193">
@@ -5921,10 +6386,15 @@
           <t xml:space="preserve">TURRÓN DE MANÍ CON YEMA TOSTADA 24x100gr</t>
         </is>
       </c>
-      <c r="C193" s="4"/>
-      <c r="D193" s="5"/>
+      <c r="C193" s="4">
+        <v>24</v>
+      </c>
+      <c r="D193" s="5">
+        <v>77589.94</v>
+      </c>
       <c r="E193" s="5">
-        <v>3232.91</v>
+        <f>IF(C193&gt;0,D193/C193,"")</f>
+        <v>3232.9141666666669</v>
       </c>
     </row>
     <row r="194">
@@ -5966,10 +6436,15 @@
           <t xml:space="preserve">TURRÓN DE FRUTOS SECOS 24x95gr</t>
         </is>
       </c>
-      <c r="C196" s="4"/>
-      <c r="D196" s="5"/>
+      <c r="C196" s="4">
+        <v>24</v>
+      </c>
+      <c r="D196" s="5">
+        <v>77589.94</v>
+      </c>
       <c r="E196" s="5">
-        <v>3232.91</v>
+        <f>IF(C196&gt;0,D196/C196,"")</f>
+        <v>3232.9141666666669</v>
       </c>
     </row>
     <row r="197">
@@ -6116,10 +6591,15 @@
           <t xml:space="preserve">TURRÓN DE MANÍ CON MIEL</t>
         </is>
       </c>
-      <c r="C206" s="4"/>
-      <c r="D206" s="5"/>
+      <c r="C206" s="4">
+        <v>12</v>
+      </c>
+      <c r="D206" s="5">
+        <v>40558.43</v>
+      </c>
       <c r="E206" s="5">
-        <v>3379.87</v>
+        <f>IF(C206&gt;0,D206/C206,"")</f>
+        <v>3379.8691666666668</v>
       </c>
     </row>
     <row r="207">
@@ -6131,10 +6611,15 @@
           <t xml:space="preserve">TABLETA CROCANTE DE FRUTOS SECOS 36x95gr</t>
         </is>
       </c>
-      <c r="C207" s="4"/>
-      <c r="D207" s="5"/>
+      <c r="C207" s="4">
+        <v>36</v>
+      </c>
+      <c r="D207" s="5">
+        <v>69948.65</v>
+      </c>
       <c r="E207" s="5">
-        <v>1943.02</v>
+        <f>IF(C207&gt;0,D207/C207,"")</f>
+        <v>1943.0180555555553</v>
       </c>
     </row>
     <row r="208">
@@ -6161,10 +6646,15 @@
           <t xml:space="preserve">CEREZAS AL RHUM CON CHOCOLATE 24x100gr</t>
         </is>
       </c>
-      <c r="C209" s="4"/>
-      <c r="D209" s="5"/>
+      <c r="C209" s="4">
+        <v>24</v>
+      </c>
+      <c r="D209" s="5">
+        <v>109914.66</v>
+      </c>
       <c r="E209" s="5">
-        <v>4579.78</v>
+        <f>IF(C209&gt;0,D209/C209,"")</f>
+        <v>4579.7775</v>
       </c>
     </row>
     <row r="210">
@@ -6191,10 +6681,15 @@
           <t xml:space="preserve">GARAPIÑADAS DE MANÍ 36X80GR</t>
         </is>
       </c>
-      <c r="C211" s="4"/>
-      <c r="D211" s="5"/>
+      <c r="C211" s="4">
+        <v>36</v>
+      </c>
+      <c r="D211" s="5">
+        <v>34850.18</v>
+      </c>
       <c r="E211" s="5">
-        <v>968.06</v>
+        <f>IF(C211&gt;0,D211/C211,"")</f>
+        <v>968.06055555555554</v>
       </c>
     </row>
     <row r="212">
@@ -6206,10 +6701,15 @@
           <t xml:space="preserve">GARAPIÑADAS DE MANÍ 36X100GR</t>
         </is>
       </c>
-      <c r="C212" s="4"/>
-      <c r="D212" s="5"/>
+      <c r="C212" s="4">
+        <v>36</v>
+      </c>
+      <c r="D212" s="5">
+        <v>42587.74</v>
+      </c>
       <c r="E212" s="5">
-        <v>1182.99</v>
+        <f>IF(C212&gt;0,D212/C212,"")</f>
+        <v>1182.9927777777777</v>
       </c>
     </row>
     <row r="213">
@@ -6221,10 +6721,15 @@
           <t xml:space="preserve">MANÍ CON CHOCOLATE 36X80GR</t>
         </is>
       </c>
-      <c r="C213" s="4"/>
-      <c r="D213" s="5"/>
+      <c r="C213" s="4">
+        <v>36</v>
+      </c>
+      <c r="D213" s="5">
+        <v>62217.62</v>
+      </c>
       <c r="E213" s="5">
-        <v>1728.27</v>
+        <f>IF(C213&gt;0,D213/C213,"")</f>
+        <v>1728.2672222222222</v>
       </c>
     </row>
     <row r="214">
@@ -6236,10 +6741,15 @@
           <t xml:space="preserve">MANÍ CON CHOCOLATE 24X120GR</t>
         </is>
       </c>
-      <c r="C214" s="4"/>
-      <c r="D214" s="5"/>
+      <c r="C214" s="4">
+        <v>24</v>
+      </c>
+      <c r="D214" s="5">
+        <v>59281.97</v>
+      </c>
       <c r="E214" s="5">
-        <v>2470.08</v>
+        <f>IF(C214&gt;0,D214/C214,"")</f>
+        <v>2470.0820833333332</v>
       </c>
     </row>
     <row r="215">
@@ -6266,10 +6776,15 @@
           <t xml:space="preserve">ALMENDRAS CON CHOCOLATE 24x80gr</t>
         </is>
       </c>
-      <c r="C216" s="4"/>
-      <c r="D216" s="5"/>
+      <c r="C216" s="4">
+        <v>24</v>
+      </c>
+      <c r="D216" s="5">
+        <v>67204.37</v>
+      </c>
       <c r="E216" s="5">
-        <v>2800.18</v>
+        <f>IF(C216&gt;0,D216/C216,"")</f>
+        <v>2800.1820833333331</v>
       </c>
     </row>
     <row r="217">
@@ -6281,10 +6796,15 @@
           <t xml:space="preserve">PASAS DE UVA CON CHOCOLATE</t>
         </is>
       </c>
-      <c r="C217" s="4"/>
-      <c r="D217" s="5"/>
+      <c r="C217" s="4">
+        <v>24</v>
+      </c>
+      <c r="D217" s="5">
+        <v>68355.51</v>
+      </c>
       <c r="E217" s="5">
-        <v>2848.15</v>
+        <f>IF(C217&gt;0,D217/C217,"")</f>
+        <v>2848.14625</v>
       </c>
     </row>
     <row r="218">
@@ -6326,10 +6846,15 @@
           <t xml:space="preserve">CONFITES DE MANÍ</t>
         </is>
       </c>
-      <c r="C220" s="4"/>
-      <c r="D220" s="5"/>
+      <c r="C220" s="4">
+        <v>36</v>
+      </c>
+      <c r="D220" s="5">
+        <v>45809.87</v>
+      </c>
       <c r="E220" s="5">
-        <v>1272.5</v>
+        <f>IF(C220&gt;0,D220/C220,"")</f>
+        <v>1272.496388888889</v>
       </c>
     </row>
     <row r="221">
@@ -6401,10 +6926,15 @@
           <t xml:space="preserve">PAN DULCE C/FRUTAS GEORGALOS 8x400gr</t>
         </is>
       </c>
-      <c r="C225" s="4"/>
-      <c r="D225" s="5"/>
+      <c r="C225" s="4">
+        <v>8</v>
+      </c>
+      <c r="D225" s="5">
+        <v>44823.24</v>
+      </c>
       <c r="E225" s="5">
-        <v>44823.24</v>
+        <f>IF(C225&gt;0,D225/C225,"")</f>
+        <v>5602.905</v>
       </c>
     </row>
     <row r="226">
@@ -6416,10 +6946,15 @@
           <t xml:space="preserve">GEORGALOS PAN DULCE SIN FRUTAS 8x400gr</t>
         </is>
       </c>
-      <c r="C226" s="4"/>
-      <c r="D226" s="5"/>
+      <c r="C226" s="4">
+        <v>8</v>
+      </c>
+      <c r="D226" s="5">
+        <v>37995.86</v>
+      </c>
       <c r="E226" s="5">
-        <v>37995.86</v>
+        <f>IF(C226&gt;0,D226/C226,"")</f>
+        <v>4749.4825</v>
       </c>
     </row>
     <row r="227">
@@ -6431,10 +6966,15 @@
           <t xml:space="preserve">MANTECOL CAFÉ 1X40X111GR</t>
         </is>
       </c>
-      <c r="C227" s="4"/>
-      <c r="D227" s="5"/>
+      <c r="C227" s="4">
+        <v>40</v>
+      </c>
+      <c r="D227" s="5">
+        <v>95469</v>
+      </c>
       <c r="E227" s="5">
-        <v>2386.72</v>
+        <f>IF(C227&gt;0,D227/C227,"")</f>
+        <v>2386.725</v>
       </c>
     </row>
     <row r="228">
@@ -6446,10 +6986,15 @@
           <t xml:space="preserve">MANTECOL COCO 1X40X111GR</t>
         </is>
       </c>
-      <c r="C228" s="4"/>
-      <c r="D228" s="5"/>
+      <c r="C228" s="4">
+        <v>40</v>
+      </c>
+      <c r="D228" s="5">
+        <v>95468.03</v>
+      </c>
       <c r="E228" s="5">
-        <v>2386.7</v>
+        <f>IF(C228&gt;0,D228/C228,"")</f>
+        <v>2386.70075</v>
       </c>
     </row>
     <row r="229">
@@ -6461,10 +7006,15 @@
           <t xml:space="preserve">MANTECOL SALTED CARAMEL 40X111GR</t>
         </is>
       </c>
-      <c r="C229" s="4"/>
-      <c r="D229" s="5"/>
+      <c r="C229" s="4">
+        <v>40</v>
+      </c>
+      <c r="D229" s="5">
+        <v>95469</v>
+      </c>
       <c r="E229" s="5">
-        <v>2386.72</v>
+        <f>IF(C229&gt;0,D229/C229,"")</f>
+        <v>2386.725</v>
       </c>
     </row>
     <row r="230">
@@ -6476,10 +7026,15 @@
           <t xml:space="preserve">P DE LA SELVA 12X660G</t>
         </is>
       </c>
-      <c r="C230" s="4"/>
-      <c r="D230" s="5"/>
+      <c r="C230" s="4">
+        <v>12</v>
+      </c>
+      <c r="D230" s="5">
+        <v>111441.87</v>
+      </c>
       <c r="E230" s="5">
-        <v>9286.82</v>
+        <f>IF(C230&gt;0,D230/C230,"")</f>
+        <v>9286.8225</v>
       </c>
     </row>
     <row r="231">
@@ -6491,10 +7046,15 @@
           <t xml:space="preserve">P DE LA SELVA 44X150G</t>
         </is>
       </c>
-      <c r="C231" s="4"/>
-      <c r="D231" s="5"/>
+      <c r="C231" s="4">
+        <v>44</v>
+      </c>
+      <c r="D231" s="5">
+        <v>92358.62</v>
+      </c>
       <c r="E231" s="5">
-        <v>2099.06</v>
+        <f>IF(C231&gt;0,D231/C231,"")</f>
+        <v>2099.0595454545455</v>
       </c>
     </row>
     <row r="232">
@@ -6506,10 +7066,15 @@
           <t xml:space="preserve">PALITO DE LA SELVA 12X480GR</t>
         </is>
       </c>
-      <c r="C232" s="4"/>
-      <c r="D232" s="5"/>
+      <c r="C232" s="4">
+        <v>12</v>
+      </c>
+      <c r="D232" s="5">
+        <v>6784.76</v>
+      </c>
       <c r="E232" s="5">
-        <v>6784.76</v>
+        <f>IF(C232&gt;0,D232/C232,"")</f>
+        <v>565.39666666666665</v>
       </c>
     </row>
     <row r="233">
@@ -6521,10 +7086,15 @@
           <t xml:space="preserve">PAL DE LA SELVA ANANA AC 1X44X150G</t>
         </is>
       </c>
-      <c r="C233" s="4"/>
-      <c r="D233" s="5"/>
+      <c r="C233" s="4">
+        <v>44</v>
+      </c>
+      <c r="D233" s="5">
+        <v>89668.41</v>
+      </c>
       <c r="E233" s="5">
-        <v>2037.92</v>
+        <f>IF(C233&gt;0,D233/C233,"")</f>
+        <v>2037.9184090909091</v>
       </c>
     </row>
     <row r="234">
@@ -6551,10 +7121,15 @@
           <t xml:space="preserve">P DE LA SELVA BLUEBERRY AC 1X44X150G</t>
         </is>
       </c>
-      <c r="C235" s="4"/>
-      <c r="D235" s="5"/>
+      <c r="C235" s="4">
+        <v>44</v>
+      </c>
+      <c r="D235" s="5">
+        <v>89668.41</v>
+      </c>
       <c r="E235" s="5">
-        <v>2037.92</v>
+        <f>IF(C235&gt;0,D235/C235,"")</f>
+        <v>2037.9184090909091</v>
       </c>
     </row>
     <row r="236">
@@ -6581,10 +7156,15 @@
           <t xml:space="preserve">PALITO DE LA SELVA MARSHMALLOW 12x24x12GR</t>
         </is>
       </c>
-      <c r="C237" s="4"/>
-      <c r="D237" s="5"/>
+      <c r="C237" s="4">
+        <v>24</v>
+      </c>
+      <c r="D237" s="5">
+        <v>219847.32</v>
+      </c>
       <c r="E237" s="5">
-        <v>9160.3</v>
+        <f>IF(C237&gt;0,D237/C237,"")</f>
+        <v>9160.305</v>
       </c>
     </row>
     <row r="238">
@@ -6596,10 +7176,15 @@
           <t xml:space="preserve">MANTECOL IMP B SOD 111GR</t>
         </is>
       </c>
-      <c r="C238" s="4"/>
-      <c r="D238" s="5"/>
+      <c r="C238" s="4">
+        <v>40</v>
+      </c>
+      <c r="D238" s="5">
+        <v>95468.52</v>
+      </c>
       <c r="E238" s="5">
-        <v>2386.71</v>
+        <f>IF(C238&gt;0,D238/C238,"")</f>
+        <v>2386.713</v>
       </c>
     </row>
     <row r="239">
@@ -6611,10 +7196,15 @@
           <t xml:space="preserve">MANTECOL MARMO B SOD 111GR</t>
         </is>
       </c>
-      <c r="C239" s="4"/>
-      <c r="D239" s="5"/>
+      <c r="C239" s="4">
+        <v>40</v>
+      </c>
+      <c r="D239" s="5">
+        <v>101689.37</v>
+      </c>
       <c r="E239" s="5">
-        <v>2542.23</v>
+        <f>IF(C239&gt;0,D239/C239,"")</f>
+        <v>2542.23425</v>
       </c>
     </row>
     <row r="240">
@@ -6626,10 +7216,15 @@
           <t xml:space="preserve">MANTECOL B SOD 253GR</t>
         </is>
       </c>
-      <c r="C240" s="4"/>
-      <c r="D240" s="5"/>
+      <c r="C240" s="4">
+        <v>36</v>
+      </c>
+      <c r="D240" s="5">
+        <v>174629.86</v>
+      </c>
       <c r="E240" s="5">
-        <v>4850.83</v>
+        <f>IF(C240&gt;0,D240/C240,"")</f>
+        <v>4850.8294444444437</v>
       </c>
     </row>
     <row r="241">
@@ -6641,10 +7236,15 @@
           <t xml:space="preserve">MANTECOL B SOD 404GR</t>
         </is>
       </c>
-      <c r="C241" s="4"/>
-      <c r="D241" s="5"/>
+      <c r="C241" s="4">
+        <v>24</v>
+      </c>
+      <c r="D241" s="5">
+        <v>166098.35</v>
+      </c>
       <c r="E241" s="5">
-        <v>6920.76</v>
+        <f>IF(C241&gt;0,D241/C241,"")</f>
+        <v>6920.7645833333336</v>
       </c>
     </row>
     <row r="242">
@@ -6656,10 +7256,15 @@
           <t xml:space="preserve">FLYNN PAFF CHUP TUTTI FRUTTI 18X18GR</t>
         </is>
       </c>
-      <c r="C242" s="4"/>
-      <c r="D242" s="5"/>
+      <c r="C242" s="4">
+        <v>18</v>
+      </c>
+      <c r="D242" s="5">
+        <v>89558.27</v>
+      </c>
       <c r="E242" s="5">
-        <v>4975.46</v>
+        <f>IF(C242&gt;0,D242/C242,"")</f>
+        <v>4975.4594444444447</v>
       </c>
     </row>
     <row r="243">
@@ -6746,10 +7351,15 @@
           <t xml:space="preserve">LENGUETAZO T FRUTTI  32X 13GR</t>
         </is>
       </c>
-      <c r="C248" s="4"/>
-      <c r="D248" s="5"/>
+      <c r="C248" s="4">
+        <v>32</v>
+      </c>
+      <c r="D248" s="5">
+        <v>229281.25</v>
+      </c>
       <c r="E248" s="5">
-        <v>7165.04</v>
+        <f>IF(C248&gt;0,D248/C248,"")</f>
+        <v>7165.0390625</v>
       </c>
     </row>
     <row r="249">
@@ -6776,10 +7386,15 @@
           <t xml:space="preserve">CARAM. FULLMINT CHERRY MENTA 24X12X28GR</t>
         </is>
       </c>
-      <c r="C250" s="4"/>
-      <c r="D250" s="5"/>
+      <c r="C250" s="4">
+        <v>24</v>
+      </c>
+      <c r="D250" s="5">
+        <v>78057.2</v>
+      </c>
       <c r="E250" s="5">
-        <v>3252.38</v>
+        <f>IF(C250&gt;0,D250/C250,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="251">
@@ -6791,10 +7406,15 @@
           <t xml:space="preserve">CARAM. FULLMINT CHOCO MENTA 24X12X28G</t>
         </is>
       </c>
-      <c r="C251" s="4"/>
-      <c r="D251" s="5"/>
+      <c r="C251" s="4">
+        <v>24</v>
+      </c>
+      <c r="D251" s="5">
+        <v>78057.2</v>
+      </c>
       <c r="E251" s="5">
-        <v>3252.38</v>
+        <f>IF(C251&gt;0,D251/C251,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="252">
@@ -6806,10 +7426,15 @@
           <t xml:space="preserve">CARAM. FULLMINT MENTA 24X12X28GR</t>
         </is>
       </c>
-      <c r="C252" s="4"/>
-      <c r="D252" s="5"/>
+      <c r="C252" s="4">
+        <v>24</v>
+      </c>
+      <c r="D252" s="5">
+        <v>78057.2</v>
+      </c>
       <c r="E252" s="5">
-        <v>3252.38</v>
+        <f>IF(C252&gt;0,D252/C252,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="253">
@@ -6821,10 +7446,15 @@
           <t xml:space="preserve">CARAM. FULLMINT MIEL MENTA 24X12X28GR</t>
         </is>
       </c>
-      <c r="C253" s="4"/>
-      <c r="D253" s="5"/>
+      <c r="C253" s="4">
+        <v>24</v>
+      </c>
+      <c r="D253" s="5">
+        <v>78057.2</v>
+      </c>
       <c r="E253" s="5">
-        <v>3252.38</v>
+        <f>IF(C253&gt;0,D253/C253,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="254">
@@ -6836,10 +7466,15 @@
           <t xml:space="preserve">CARAM. FULLMINT NARANJA Y MENTA 24X12X28G</t>
         </is>
       </c>
-      <c r="C254" s="4"/>
-      <c r="D254" s="5"/>
+      <c r="C254" s="4">
+        <v>24</v>
+      </c>
+      <c r="D254" s="5">
+        <v>78057.2</v>
+      </c>
       <c r="E254" s="5">
-        <v>3252.38</v>
+        <f>IF(C254&gt;0,D254/C254,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="255">
@@ -6851,10 +7486,15 @@
           <t xml:space="preserve">CARAM. FULLMINT MENTA STRONG 24X12X28G</t>
         </is>
       </c>
-      <c r="C255" s="4"/>
-      <c r="D255" s="5"/>
+      <c r="C255" s="4">
+        <v>24</v>
+      </c>
+      <c r="D255" s="5">
+        <v>78057.2</v>
+      </c>
       <c r="E255" s="5">
-        <v>3252.38</v>
+        <f>IF(C255&gt;0,D255/C255,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="256">
@@ -6866,10 +7506,15 @@
           <t xml:space="preserve">CARAM. FULLMINT MIX DE FRUTAS 24X12X28GR</t>
         </is>
       </c>
-      <c r="C256" s="4"/>
-      <c r="D256" s="5"/>
+      <c r="C256" s="4">
+        <v>12</v>
+      </c>
+      <c r="D256" s="5">
+        <v>39028.6</v>
+      </c>
       <c r="E256" s="5">
-        <v>3252.38</v>
+        <f>IF(C256&gt;0,D256/C256,"")</f>
+        <v>3252.3833333333332</v>
       </c>
     </row>
     <row r="257">
@@ -6881,10 +7526,15 @@
           <t xml:space="preserve">LENGUETAZO FRAMBUESA 18X32X13GR</t>
         </is>
       </c>
-      <c r="C257" s="4"/>
-      <c r="D257" s="5"/>
+      <c r="C257" s="4">
+        <v>32</v>
+      </c>
+      <c r="D257" s="5">
+        <v>229281.25</v>
+      </c>
       <c r="E257" s="5">
-        <v>7165.04</v>
+        <f>IF(C257&gt;0,D257/C257,"")</f>
+        <v>7165.0390625</v>
       </c>
     </row>
     <row r="258">
@@ -6896,10 +7546,15 @@
           <t xml:space="preserve">LENGUETAZO TROPICAL PUNCH 18X32X13GR</t>
         </is>
       </c>
-      <c r="C258" s="4"/>
-      <c r="D258" s="5"/>
+      <c r="C258" s="4">
+        <v>32</v>
+      </c>
+      <c r="D258" s="5">
+        <v>229281.25</v>
+      </c>
       <c r="E258" s="5">
-        <v>7165.04</v>
+        <f>IF(C258&gt;0,D258/C258,"")</f>
+        <v>7165.0390625</v>
       </c>
     </row>
     <row r="259">
@@ -6911,10 +7566,15 @@
           <t xml:space="preserve">TODDY CHOCOLATE AIREADO COMBINADO 6X10X50GR</t>
         </is>
       </c>
-      <c r="C259" s="4"/>
-      <c r="D259" s="5"/>
+      <c r="C259" s="4">
+        <v>10</v>
+      </c>
+      <c r="D259" s="5">
+        <v>16130.87</v>
+      </c>
       <c r="E259" s="5">
-        <v>1613.09</v>
+        <f>IF(C259&gt;0,D259/C259,"")</f>
+        <v>1613.087</v>
       </c>
     </row>
     <row r="260">
@@ -6926,10 +7586,15 @@
           <t xml:space="preserve">MANTECOL BOCADO B/SOD 26GR</t>
         </is>
       </c>
-      <c r="C260" s="4"/>
-      <c r="D260" s="5"/>
+      <c r="C260" s="4">
+        <v>8</v>
+      </c>
+      <c r="D260" s="5">
+        <v>100679.16</v>
+      </c>
       <c r="E260" s="5">
-        <v>12584.9</v>
+        <f>IF(C260&gt;0,D260/C260,"")</f>
+        <v>12584.895</v>
       </c>
     </row>
     <row r="261">
@@ -6941,10 +7606,15 @@
           <t xml:space="preserve">MANTECOL BAJO SOD 41GR</t>
         </is>
       </c>
-      <c r="C261" s="4"/>
-      <c r="D261" s="5"/>
+      <c r="C261" s="4">
+        <v>8</v>
+      </c>
+      <c r="D261" s="5">
+        <v>108968.15</v>
+      </c>
       <c r="E261" s="5">
-        <v>13621.02</v>
+        <f>IF(C261&gt;0,D261/C261,"")</f>
+        <v>13621.01875</v>
       </c>
     </row>
     <row r="262">
@@ -6956,10 +7626,15 @@
           <t xml:space="preserve">MANTECOL BARRA B SOD 64GR</t>
         </is>
       </c>
-      <c r="C262" s="4"/>
-      <c r="D262" s="5"/>
+      <c r="C262" s="4">
+        <v>8</v>
+      </c>
+      <c r="D262" s="5">
+        <v>95710.81</v>
+      </c>
       <c r="E262" s="5">
-        <v>11963.85</v>
+        <f>IF(C262&gt;0,D262/C262,"")</f>
+        <v>11963.85125</v>
       </c>
     </row>
     <row r="263">
@@ -7051,9 +7726,14 @@
           <t xml:space="preserve">MANTECA S/SAL Y S/VITAMINAS X 100G. ILOLAY</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5">
+        <v>29887</v>
+      </c>
       <c r="E4" s="5">
+        <f>IF(C4&gt;0,D4/C4,"")</f>
         <v>1494.35</v>
       </c>
     </row>
@@ -7066,10 +7746,15 @@
           <t xml:space="preserve">MANTECA S/SAL Y S/VITAMINAS X 200G. ILOLAY</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5">
+        <v>26898.66</v>
+      </c>
       <c r="E5" s="5">
-        <v>2689.87</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>2689.866</v>
       </c>
     </row>
     <row r="6">
@@ -7081,10 +7766,15 @@
           <t xml:space="preserve">MANTECA S/SAL Y S/VITAMINAS X 500G. ILOLAY</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5">
+        <v>77300.85</v>
+      </c>
       <c r="E6" s="5">
-        <v>6441.74</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>6441.7375</v>
       </c>
     </row>
     <row r="7">
@@ -7096,10 +7786,15 @@
           <t xml:space="preserve">CREMA DOBLE X 200ML. ILOLAY</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5">
+        <v>45114.51</v>
+      </c>
       <c r="E7" s="5">
-        <v>1879.77</v>
+        <f>IF(C7&gt;0,D7/C7,"")</f>
+        <v>1879.77125</v>
       </c>
     </row>
     <row r="8">
@@ -7111,10 +7806,15 @@
           <t xml:space="preserve">CREMA DOBLE X 350ML. ILOLAY</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>35964.01</v>
+      </c>
       <c r="E8" s="5">
-        <v>2997</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>2997.0008333333335</v>
       </c>
     </row>
     <row r="9">
@@ -7126,9 +7826,14 @@
           <t xml:space="preserve">CREMA SIMPLE X 200ML. ILOLAY</t>
         </is>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="4">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5">
+        <v>42137.04</v>
+      </c>
       <c r="E9" s="5">
+        <f>IF(C9&gt;0,D9/C9,"")</f>
         <v>1755.71</v>
       </c>
     </row>
@@ -7141,10 +7846,15 @@
           <t xml:space="preserve">CREMA SIMPLE X 350ML. ILOLAY</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="4">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5">
+        <v>38051.11</v>
+      </c>
       <c r="E10" s="5">
-        <v>3170.93</v>
+        <f>IF(C10&gt;0,D10/C10,"")</f>
+        <v>3170.9258333333332</v>
       </c>
     </row>
     <row r="11">
@@ -7261,10 +7971,15 @@
           <t xml:space="preserve">QUESO ILOLAY CREM CLASICO (NUEVO) 290gr</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="4">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5">
+        <v>28435.1</v>
+      </c>
       <c r="E18" s="5">
-        <v>2369.59</v>
+        <f>IF(C18&gt;0,D18/C18,"")</f>
+        <v>2369.5916666666667</v>
       </c>
     </row>
     <row r="19">
@@ -7276,10 +7991,15 @@
           <t xml:space="preserve">QUESO ILOLAY CREM BALANCE 290GR</t>
         </is>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="4">
+        <v>12</v>
+      </c>
+      <c r="D19" s="5">
+        <v>28435.1</v>
+      </c>
       <c r="E19" s="5">
-        <v>2369.59</v>
+        <f>IF(C19&gt;0,D19/C19,"")</f>
+        <v>2369.5916666666667</v>
       </c>
     </row>
     <row r="20">
@@ -7321,10 +8041,15 @@
           <t xml:space="preserve">QUESO UNTABLE CLASICO ILOLAY X 190GR</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="4">
+        <v>12</v>
+      </c>
+      <c r="D22" s="5">
+        <v>23248.12</v>
+      </c>
       <c r="E22" s="5">
-        <v>1937.34</v>
+        <f>IF(C22&gt;0,D22/C22,"")</f>
+        <v>1937.3433333333332</v>
       </c>
     </row>
     <row r="23">
@@ -7351,10 +8076,15 @@
           <t xml:space="preserve">QUESO UNTABLE JAMON ILOLAY 190GR</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4">
+        <v>12</v>
+      </c>
+      <c r="D24" s="5">
+        <v>23248.12</v>
+      </c>
       <c r="E24" s="5">
-        <v>1937.34</v>
+        <f>IF(C24&gt;0,D24/C24,"")</f>
+        <v>1937.3433333333332</v>
       </c>
     </row>
     <row r="25">
@@ -7381,10 +8111,15 @@
           <t xml:space="preserve">DISPLAY 20 QUESO RALLADO X 40G. ILOLAY</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>157905.15</v>
+      </c>
       <c r="E26" s="5">
-        <v>26317.52</v>
+        <f>IF(C26&gt;0,D26/C26,"")</f>
+        <v>26317.524999999998</v>
       </c>
     </row>
     <row r="27">
@@ -7396,10 +8131,15 @@
           <t xml:space="preserve">QUESO RALLADO X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4">
+        <v>40</v>
+      </c>
+      <c r="D27" s="5">
+        <v>145318.1</v>
+      </c>
       <c r="E27" s="5">
-        <v>3632.95</v>
+        <f>IF(C27&gt;0,D27/C27,"")</f>
+        <v>3632.9525000000003</v>
       </c>
     </row>
     <row r="28">
@@ -7411,10 +8151,15 @@
           <t xml:space="preserve">POSTRE VAINILLA X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4">
+        <v>20</v>
+      </c>
+      <c r="D28" s="5">
+        <v>24132.48</v>
+      </c>
       <c r="E28" s="5">
-        <v>1206.62</v>
+        <f>IF(C28&gt;0,D28/C28,"")</f>
+        <v>1206.624</v>
       </c>
     </row>
     <row r="29">
@@ -7426,10 +8171,15 @@
           <t xml:space="preserve">POSTRE CHOCOLATE X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="4">
+        <v>20</v>
+      </c>
+      <c r="D29" s="5">
+        <v>24132.48</v>
+      </c>
       <c r="E29" s="5">
-        <v>1206.62</v>
+        <f>IF(C29&gt;0,D29/C29,"")</f>
+        <v>1206.624</v>
       </c>
     </row>
     <row r="30">
@@ -7441,10 +8191,15 @@
           <t xml:space="preserve">POSTRE VAIN/DDL. X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4">
+        <v>20</v>
+      </c>
+      <c r="D30" s="5">
+        <v>24132.48</v>
+      </c>
       <c r="E30" s="5">
-        <v>1206.62</v>
+        <f>IF(C30&gt;0,D30/C30,"")</f>
+        <v>1206.624</v>
       </c>
     </row>
     <row r="31">
@@ -7456,10 +8211,15 @@
           <t xml:space="preserve">POSTRE DULCE DE LECHE X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4">
+        <v>20</v>
+      </c>
+      <c r="D31" s="5">
+        <v>24132.48</v>
+      </c>
       <c r="E31" s="5">
-        <v>1206.62</v>
+        <f>IF(C31&gt;0,D31/C31,"")</f>
+        <v>1206.624</v>
       </c>
     </row>
     <row r="32">
@@ -7471,10 +8231,15 @@
           <t xml:space="preserve">POSTRE VAIN. C/CONFITES X 110G. ILOLAY</t>
         </is>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="4">
+        <v>20</v>
+      </c>
+      <c r="D32" s="5">
+        <v>42480.92</v>
+      </c>
       <c r="E32" s="5">
-        <v>2124.05</v>
+        <f>IF(C32&gt;0,D32/C32,"")</f>
+        <v>2124.046</v>
       </c>
     </row>
     <row r="33">
@@ -7486,10 +8251,15 @@
           <t xml:space="preserve">FLAN VAIN. C/CARA Y DDL. X 110G. ILOLAY</t>
         </is>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
+      <c r="C33" s="4">
+        <v>20</v>
+      </c>
+      <c r="D33" s="5">
+        <v>23127.94</v>
+      </c>
       <c r="E33" s="5">
-        <v>1156.4</v>
+        <f>IF(C33&gt;0,D33/C33,"")</f>
+        <v>1156.397</v>
       </c>
     </row>
     <row r="34">
@@ -7501,10 +8271,15 @@
           <t xml:space="preserve">FLAN VAINILLA C/CARAMELO X 110G. ILOLAY</t>
         </is>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
+      <c r="C34" s="4">
+        <v>20</v>
+      </c>
+      <c r="D34" s="5">
+        <v>23127.94</v>
+      </c>
       <c r="E34" s="5">
-        <v>1156.4</v>
+        <f>IF(C34&gt;0,D34/C34,"")</f>
+        <v>1156.397</v>
       </c>
     </row>
     <row r="35">
@@ -7516,10 +8291,15 @@
           <t xml:space="preserve">YOG. CREMOSO ENT. FRUTILLA X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="4">
+        <v>24</v>
+      </c>
+      <c r="D35" s="5">
+        <v>18090.18</v>
+      </c>
       <c r="E35" s="5">
-        <v>753.76</v>
+        <f>IF(C35&gt;0,D35/C35,"")</f>
+        <v>753.7575</v>
       </c>
     </row>
     <row r="36">
@@ -7531,10 +8311,15 @@
           <t xml:space="preserve">YOG. CREMOSO ENT. VAINILLA X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
+      <c r="C36" s="4">
+        <v>24</v>
+      </c>
+      <c r="D36" s="5">
+        <v>18090.18</v>
+      </c>
       <c r="E36" s="5">
-        <v>753.76</v>
+        <f>IF(C36&gt;0,D36/C36,"")</f>
+        <v>753.7575</v>
       </c>
     </row>
     <row r="37">
@@ -7546,10 +8331,15 @@
           <t xml:space="preserve">YOGUR CREMOSO PD DESLAC FRUT 90GR ILOLAY</t>
         </is>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
+      <c r="C37" s="4">
+        <v>24</v>
+      </c>
+      <c r="D37" s="5">
+        <v>18206.05</v>
+      </c>
       <c r="E37" s="5">
-        <v>758.59</v>
+        <f>IF(C37&gt;0,D37/C37,"")</f>
+        <v>758.58541666666667</v>
       </c>
     </row>
     <row r="38">
@@ -7561,10 +8351,15 @@
           <t xml:space="preserve">YOGUR CREMOSO PD DESLAC VAI 90GR ILOLAY</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
+      <c r="C38" s="4">
+        <v>24</v>
+      </c>
+      <c r="D38" s="5">
+        <v>18206.05</v>
+      </c>
       <c r="E38" s="5">
-        <v>758.59</v>
+        <f>IF(C38&gt;0,D38/C38,"")</f>
+        <v>758.58541666666667</v>
       </c>
     </row>
     <row r="39">
@@ -7606,10 +8401,15 @@
           <t xml:space="preserve">YOG. FIRME ENT. FRUT.  X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="4">
+        <v>24</v>
+      </c>
+      <c r="D41" s="5">
+        <v>18090.18</v>
+      </c>
       <c r="E41" s="5">
-        <v>753.76</v>
+        <f>IF(C41&gt;0,D41/C41,"")</f>
+        <v>753.7575</v>
       </c>
     </row>
     <row r="42">
@@ -7621,10 +8421,15 @@
           <t xml:space="preserve">YOG. FIRME ENT. VAIN.  X 120G. ILOLAY</t>
         </is>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="4">
+        <v>24</v>
+      </c>
+      <c r="D42" s="5">
+        <v>18090.18</v>
+      </c>
       <c r="E42" s="5">
-        <v>753.76</v>
+        <f>IF(C42&gt;0,D42/C42,"")</f>
+        <v>753.7575</v>
       </c>
     </row>
     <row r="43">
@@ -7636,10 +8441,15 @@
           <t xml:space="preserve">YOGUR CON TROZOS FRUTILLA x150g ILOLAY</t>
         </is>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
+      <c r="C43" s="4">
+        <v>20</v>
+      </c>
+      <c r="D43" s="5">
+        <v>27107.63</v>
+      </c>
       <c r="E43" s="5">
-        <v>1355.38</v>
+        <f>IF(C43&gt;0,D43/C43,"")</f>
+        <v>1355.3815</v>
       </c>
     </row>
     <row r="44">
@@ -7651,10 +8461,15 @@
           <t xml:space="preserve">YOGUR CON TROZOS DURAZNO x150g ILOLAY</t>
         </is>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
+      <c r="C44" s="4">
+        <v>20</v>
+      </c>
+      <c r="D44" s="5">
+        <v>27107.63</v>
+      </c>
       <c r="E44" s="5">
-        <v>1355.38</v>
+        <f>IF(C44&gt;0,D44/C44,"")</f>
+        <v>1355.3815</v>
       </c>
     </row>
     <row r="45">
@@ -7666,9 +8481,14 @@
           <t xml:space="preserve">YOGUR CON TROZOS DE ARANDANOS x150g ILOLAY</t>
         </is>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
+      <c r="C45" s="4">
+        <v>20</v>
+      </c>
+      <c r="D45" s="5">
+        <v>26576.2</v>
+      </c>
       <c r="E45" s="5">
+        <f>IF(C45&gt;0,D45/C45,"")</f>
         <v>1328.81</v>
       </c>
     </row>
@@ -7711,10 +8531,15 @@
           <t xml:space="preserve">YOGUR NATURAL 140gr ILOLAY</t>
         </is>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="5"/>
+      <c r="C48" s="4">
+        <v>20</v>
+      </c>
+      <c r="D48" s="5">
+        <v>23391.24</v>
+      </c>
       <c r="E48" s="5">
-        <v>1169.56</v>
+        <f>IF(C48&gt;0,D48/C48,"")</f>
+        <v>1169.5620000000001</v>
       </c>
     </row>
     <row r="49">
@@ -7726,10 +8551,15 @@
           <t xml:space="preserve">YOGUR BATIDO PROTEINA FRUTILLA X 180GR ILOLAY</t>
         </is>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="5"/>
+      <c r="C49" s="4">
+        <v>20</v>
+      </c>
+      <c r="D49" s="5">
+        <v>45537.87</v>
+      </c>
       <c r="E49" s="5">
-        <v>2276.89</v>
+        <f>IF(C49&gt;0,D49/C49,"")</f>
+        <v>2276.8935</v>
       </c>
     </row>
     <row r="50">
@@ -7741,10 +8571,15 @@
           <t xml:space="preserve">YOGUR BATIDO PROTEINA VAINILLA X 180GR ILOLAY</t>
         </is>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="5"/>
+      <c r="C50" s="4">
+        <v>20</v>
+      </c>
+      <c r="D50" s="5">
+        <v>45537.87</v>
+      </c>
       <c r="E50" s="5">
-        <v>2276.89</v>
+        <f>IF(C50&gt;0,D50/C50,"")</f>
+        <v>2276.8935</v>
       </c>
     </row>
     <row r="51">
@@ -7756,10 +8591,15 @@
           <t xml:space="preserve">YOG.FIRME ENT. FRUT. POTE X 190G. ILOLAY</t>
         </is>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
+      <c r="C51" s="4">
+        <v>20</v>
+      </c>
+      <c r="D51" s="5">
+        <v>24788.79</v>
+      </c>
       <c r="E51" s="5">
-        <v>1239.44</v>
+        <f>IF(C51&gt;0,D51/C51,"")</f>
+        <v>1239.4395</v>
       </c>
     </row>
     <row r="52">
@@ -7771,10 +8611,15 @@
           <t xml:space="preserve">YOG.FIRME ENT. VAIN. POTE X 190G. ILOLAY</t>
         </is>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
+      <c r="C52" s="4">
+        <v>20</v>
+      </c>
+      <c r="D52" s="5">
+        <v>24788.79</v>
+      </c>
       <c r="E52" s="5">
-        <v>1239.44</v>
+        <f>IF(C52&gt;0,D52/C52,"")</f>
+        <v>1239.4395</v>
       </c>
     </row>
     <row r="53">
@@ -7831,10 +8676,15 @@
           <t xml:space="preserve">YOGUR NATURAL PD x 350 ILOLAY</t>
         </is>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="5"/>
+      <c r="C56" s="4">
+        <v>12</v>
+      </c>
+      <c r="D56" s="5">
+        <v>24424.24</v>
+      </c>
       <c r="E56" s="5">
-        <v>2035.35</v>
+        <f>IF(C56&gt;0,D56/C56,"")</f>
+        <v>2035.3533333333335</v>
       </c>
     </row>
     <row r="57">
@@ -7846,10 +8696,15 @@
           <t xml:space="preserve">YOG. C/ CEREAL. ENT. POTE X 165G. ILOLAY</t>
         </is>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
+      <c r="C57" s="4">
+        <v>20</v>
+      </c>
+      <c r="D57" s="5">
+        <v>34710.3</v>
+      </c>
       <c r="E57" s="5">
-        <v>1735.52</v>
+        <f>IF(C57&gt;0,D57/C57,"")</f>
+        <v>1735.515</v>
       </c>
     </row>
     <row r="58">
@@ -7876,10 +8731,15 @@
           <t xml:space="preserve">YOG. C/ CEREAL. DES. POTE X 160G. ILOLAY</t>
         </is>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
+      <c r="C59" s="4">
+        <v>20</v>
+      </c>
+      <c r="D59" s="5">
+        <v>33885.57</v>
+      </c>
       <c r="E59" s="5">
-        <v>1694.28</v>
+        <f>IF(C59&gt;0,D59/C59,"")</f>
+        <v>1694.2785</v>
       </c>
     </row>
     <row r="60">
@@ -7891,10 +8751,15 @@
           <t xml:space="preserve">YOG.BEB.ENT.FRUT. S. X 900GR. MULTVT</t>
         </is>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
+      <c r="C60" s="4">
+        <v>12</v>
+      </c>
+      <c r="D60" s="5">
+        <v>24982.82</v>
+      </c>
       <c r="E60" s="5">
-        <v>2081.9</v>
+        <f>IF(C60&gt;0,D60/C60,"")</f>
+        <v>2081.9016666666666</v>
       </c>
     </row>
     <row r="61">
@@ -7906,10 +8771,15 @@
           <t xml:space="preserve">YOG.BEB.ENT.VAIN. S. X 900GR. MULTVT</t>
         </is>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
+      <c r="C61" s="4">
+        <v>12</v>
+      </c>
+      <c r="D61" s="5">
+        <v>24982.82</v>
+      </c>
       <c r="E61" s="5">
-        <v>2081.9</v>
+        <f>IF(C61&gt;0,D61/C61,"")</f>
+        <v>2081.9016666666666</v>
       </c>
     </row>
     <row r="62">
@@ -7921,10 +8791,15 @@
           <t xml:space="preserve">YOG.BEB.ENT.DURAZ. S. X 900GR. MULTVT</t>
         </is>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
+      <c r="C62" s="4">
+        <v>12</v>
+      </c>
+      <c r="D62" s="5">
+        <v>25042.93</v>
+      </c>
       <c r="E62" s="5">
-        <v>2086.91</v>
+        <f>IF(C62&gt;0,D62/C62,"")</f>
+        <v>2086.9108333333334</v>
       </c>
     </row>
     <row r="63">
@@ -7981,10 +8856,15 @@
           <t xml:space="preserve">Yog. TTOP PD Frut. x 950 GRS. Ilolay</t>
         </is>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="5"/>
+      <c r="C66" s="4">
+        <v>8</v>
+      </c>
+      <c r="D66" s="5">
+        <v>20039.83</v>
+      </c>
       <c r="E66" s="5">
-        <v>2504.98</v>
+        <f>IF(C66&gt;0,D66/C66,"")</f>
+        <v>2504.97875</v>
       </c>
     </row>
     <row r="67">
@@ -7996,10 +8876,15 @@
           <t xml:space="preserve">Yog. TTOP PD Vai. x 950 GRS. Ilolay</t>
         </is>
       </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="5"/>
+      <c r="C67" s="4">
+        <v>8</v>
+      </c>
+      <c r="D67" s="5">
+        <v>20039.83</v>
+      </c>
       <c r="E67" s="5">
-        <v>2504.98</v>
+        <f>IF(C67&gt;0,D67/C67,"")</f>
+        <v>2504.97875</v>
       </c>
     </row>
     <row r="68">
@@ -8011,10 +8896,15 @@
           <t xml:space="preserve">Yog. TTOP PD Dur. x 950 GRS. Ilolay</t>
         </is>
       </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="5"/>
+      <c r="C68" s="4">
+        <v>8</v>
+      </c>
+      <c r="D68" s="5">
+        <v>20040.02</v>
+      </c>
       <c r="E68" s="5">
-        <v>2505</v>
+        <f>IF(C68&gt;0,D68/C68,"")</f>
+        <v>2505.0025</v>
       </c>
     </row>
     <row r="69">
@@ -8056,10 +8946,15 @@
           <t xml:space="preserve">TETRATOP PROTEINA FRUTILLA X950GR ILOLAY</t>
         </is>
       </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="5"/>
+      <c r="C71" s="4">
+        <v>8</v>
+      </c>
+      <c r="D71" s="5">
+        <v>38666.76</v>
+      </c>
       <c r="E71" s="5">
-        <v>4833.34</v>
+        <f>IF(C71&gt;0,D71/C71,"")</f>
+        <v>4833.345</v>
       </c>
     </row>
     <row r="72">
@@ -8071,10 +8966,15 @@
           <t xml:space="preserve">TETRATOP PROTEINA VAINILLA X950GR ILOLAY</t>
         </is>
       </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="5"/>
+      <c r="C72" s="4">
+        <v>8</v>
+      </c>
+      <c r="D72" s="5">
+        <v>38666.76</v>
+      </c>
       <c r="E72" s="5">
-        <v>4833.34</v>
+        <f>IF(C72&gt;0,D72/C72,"")</f>
+        <v>4833.345</v>
       </c>
     </row>
     <row r="73">
@@ -8146,10 +9046,15 @@
           <t xml:space="preserve">TETRATOP PROTEINA FRUTILLA X220GR ILOLAY</t>
         </is>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="5"/>
+      <c r="C77" s="4">
+        <v>24</v>
+      </c>
+      <c r="D77" s="5">
+        <v>54777.28</v>
+      </c>
       <c r="E77" s="5">
-        <v>2282.39</v>
+        <f>IF(C77&gt;0,D77/C77,"")</f>
+        <v>2282.3866666666668</v>
       </c>
     </row>
     <row r="78">
@@ -8311,10 +9216,15 @@
           <t xml:space="preserve">LECHE LARGA VIDA PROTEINAS X1L ILOLAY</t>
         </is>
       </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="5"/>
+      <c r="C87" s="4">
+        <v>12</v>
+      </c>
+      <c r="D87" s="5">
+        <v>28134.39</v>
+      </c>
       <c r="E87" s="5">
-        <v>2344.53</v>
+        <f>IF(C87&gt;0,D87/C87,"")</f>
+        <v>2344.5325</v>
       </c>
     </row>
     <row r="88">
@@ -8376,10 +9286,15 @@
           <t xml:space="preserve">LECHE CHOCOLATADA X 200ML. ILOLAY</t>
         </is>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="5"/>
+      <c r="C91" s="4">
+        <v>30</v>
+      </c>
+      <c r="D91" s="5">
+        <v>30108.67</v>
+      </c>
       <c r="E91" s="5">
-        <v>1003.62</v>
+        <f>IF(C91&gt;0,D91/C91,"")</f>
+        <v>1003.6223333333332</v>
       </c>
     </row>
     <row r="92">
@@ -8421,10 +9336,15 @@
           <t xml:space="preserve">DULCE DE LECHE CLÁSICO X 200G. ILOLAY</t>
         </is>
       </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="5"/>
+      <c r="C94" s="4">
+        <v>24</v>
+      </c>
+      <c r="D94" s="5">
+        <v>34264.3</v>
+      </c>
       <c r="E94" s="5">
-        <v>1427.68</v>
+        <f>IF(C94&gt;0,D94/C94,"")</f>
+        <v>1427.6791666666668</v>
       </c>
     </row>
     <row r="95">
@@ -8436,10 +9356,15 @@
           <t xml:space="preserve">DULCE DE LECHE CLÁSICO X 400G. ILOLAY</t>
         </is>
       </c>
-      <c r="C95" s="4"/>
-      <c r="D95" s="5"/>
+      <c r="C95" s="4">
+        <v>24</v>
+      </c>
+      <c r="D95" s="5">
+        <v>57468.13</v>
+      </c>
       <c r="E95" s="5">
-        <v>2394.51</v>
+        <f>IF(C95&gt;0,D95/C95,"")</f>
+        <v>2394.5054166666664</v>
       </c>
     </row>
     <row r="96">
@@ -8451,10 +9376,15 @@
           <t xml:space="preserve">DULCE DE LECHE CLÁSICO X 1KG. ILOLAY</t>
         </is>
       </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="5"/>
+      <c r="C96" s="4">
+        <v>12</v>
+      </c>
+      <c r="D96" s="5">
+        <v>76454.48</v>
+      </c>
       <c r="E96" s="5">
-        <v>6371.21</v>
+        <f>IF(C96&gt;0,D96/C96,"")</f>
+        <v>6371.206666666666</v>
       </c>
     </row>
     <row r="97">
@@ -8481,10 +9411,15 @@
           <t xml:space="preserve">DULCE DE LECHE REPOSTERO X 400G. ILOLAY</t>
         </is>
       </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="5"/>
+      <c r="C98" s="4">
+        <v>24</v>
+      </c>
+      <c r="D98" s="5">
+        <v>63213.98</v>
+      </c>
       <c r="E98" s="5">
-        <v>2633.92</v>
+        <f>IF(C98&gt;0,D98/C98,"")</f>
+        <v>2633.9158333333335</v>
       </c>
     </row>
     <row r="99">
@@ -8496,10 +9431,15 @@
           <t xml:space="preserve">DULCE DE LECHE REPOSTERO X 1KG. ILOLAY</t>
         </is>
       </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="5"/>
+      <c r="C99" s="4">
+        <v>12</v>
+      </c>
+      <c r="D99" s="5">
+        <v>84099.99</v>
+      </c>
       <c r="E99" s="5">
-        <v>7008.33</v>
+        <f>IF(C99&gt;0,D99/C99,"")</f>
+        <v>7008.3325</v>
       </c>
     </row>
     <row r="100">
@@ -8541,10 +9481,15 @@
           <t xml:space="preserve">LECHE EN POLVO DES. X 5G. ILOLAY</t>
         </is>
       </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="5"/>
+      <c r="C102" s="4">
+        <v>8</v>
+      </c>
+      <c r="D102" s="5">
+        <v>41727.29</v>
+      </c>
       <c r="E102" s="5">
-        <v>5215.91</v>
+        <f>IF(C102&gt;0,D102/C102,"")</f>
+        <v>5215.91125</v>
       </c>
     </row>
     <row r="103">
@@ -9271,10 +10216,15 @@
           <t xml:space="preserve">ATÚN DESMENUZADO AL NATURAL 48 X 170G</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>48</v>
+      </c>
+      <c r="D4" s="5">
+        <v>64694.15</v>
+      </c>
       <c r="E4" s="5">
-        <v>1347.79</v>
+        <f>IF(C4&gt;0,D4/C4,"")</f>
+        <v>1347.7947916666667</v>
       </c>
     </row>
     <row r="5">
@@ -9286,10 +10236,15 @@
           <t xml:space="preserve">ATÚN DESMENUZADO EN ACEITE Y AGUA 48 X 170G</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>48</v>
+      </c>
+      <c r="D5" s="5">
+        <v>71248.48</v>
+      </c>
       <c r="E5" s="5">
-        <v>1484.34</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>1484.3433333333332</v>
       </c>
     </row>
     <row r="6">
@@ -9301,10 +10256,15 @@
           <t xml:space="preserve">LOMITOS DE ATÚN AL NATURAL 48 X 160G</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>48</v>
+      </c>
+      <c r="D6" s="5">
+        <v>97173.07</v>
+      </c>
       <c r="E6" s="5">
-        <v>2024.44</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>2024.4389583333334</v>
       </c>
     </row>
     <row r="7">
@@ -9316,10 +10276,15 @@
           <t xml:space="preserve">LOMITOS DE ATÚN EN ACEITE Y AGUA 48 X 160G</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>48</v>
+      </c>
+      <c r="D7" s="5">
+        <v>103805.22</v>
+      </c>
       <c r="E7" s="5">
-        <v>2162.61</v>
+        <f>IF(C7&gt;0,D7/C7,"")</f>
+        <v>2162.60875</v>
       </c>
     </row>
     <row r="8">
@@ -9331,10 +10296,15 @@
           <t xml:space="preserve">Aceite TAYAL 1X16</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>99000.07</v>
+      </c>
       <c r="E8" s="5">
-        <v>6187.5</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>6187.504375</v>
       </c>
     </row>
     <row r="9">
@@ -9381,10 +10351,15 @@
           <t xml:space="preserve">Tomate Perita Entero 400GRS X24</t>
         </is>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="4">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5">
+        <v>16377.11</v>
+      </c>
       <c r="E11" s="5">
-        <v>682.38</v>
+        <f>IF(C11&gt;0,D11/C11,"")</f>
+        <v>682.37958333333336</v>
       </c>
     </row>
     <row r="12">
@@ -9396,10 +10371,15 @@
           <t xml:space="preserve">Tomate Perita Cubeteado 400GRS X24</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="4">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5">
+        <v>17315.1</v>
+      </c>
       <c r="E12" s="5">
-        <v>721.46</v>
+        <f>IF(C12&gt;0,D12/C12,"")</f>
+        <v>721.4625</v>
       </c>
     </row>
     <row r="13">
@@ -9441,9 +10421,14 @@
           <t xml:space="preserve">ACEITE EL GRAN JUICIO 500ml x16</t>
         </is>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="4">
+        <v>16</v>
+      </c>
+      <c r="D15" s="5">
+        <v>74775.68</v>
+      </c>
       <c r="E15" s="5">
+        <f>IF(C15&gt;0,D15/C15,"")</f>
         <v>4673.48</v>
       </c>
     </row>
@@ -9456,10 +10441,15 @@
           <t xml:space="preserve">Choclo GRANO AMARILLO TAYAL 300g x 24 u</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="4">
+        <v>24</v>
+      </c>
+      <c r="D16" s="5">
+        <v>23025.24</v>
+      </c>
       <c r="E16" s="5">
-        <v>959.38</v>
+        <f>IF(C16&gt;0,D16/C16,"")</f>
+        <v>959.3850000000001</v>
       </c>
     </row>
     <row r="17">
@@ -9471,10 +10461,15 @@
           <t xml:space="preserve">Lenteja TAYAL 300gr x 24</t>
         </is>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="4">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5">
+        <v>16543.8</v>
+      </c>
       <c r="E17" s="5">
-        <v>689.32</v>
+        <f>IF(C17&gt;0,D17/C17,"")</f>
+        <v>689.32499999999993</v>
       </c>
     </row>
     <row r="18">
@@ -9486,10 +10481,15 @@
           <t xml:space="preserve">Poroto TAYAL 300g x 24u</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="4">
+        <v>24</v>
+      </c>
+      <c r="D18" s="5">
+        <v>15175.43</v>
+      </c>
       <c r="E18" s="5">
-        <v>632.31</v>
+        <f>IF(C18&gt;0,D18/C18,"")</f>
+        <v>632.30958333333331</v>
       </c>
     </row>
     <row r="19">
@@ -9501,10 +10501,15 @@
           <t xml:space="preserve">Garbanzo TAYAL 300g x 24u</t>
         </is>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="4">
+        <v>24</v>
+      </c>
+      <c r="D19" s="5">
+        <v>13475.43</v>
+      </c>
       <c r="E19" s="5">
-        <v>561.48</v>
+        <f>IF(C19&gt;0,D19/C19,"")</f>
+        <v>561.47625</v>
       </c>
     </row>
     <row r="20">
@@ -9516,10 +10521,15 @@
           <t xml:space="preserve">Jardinera TAYAL 350g x 24u</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="4">
+        <v>24</v>
+      </c>
+      <c r="D20" s="5">
+        <v>14005.41</v>
+      </c>
       <c r="E20" s="5">
-        <v>583.56</v>
+        <f>IF(C20&gt;0,D20/C20,"")</f>
+        <v>583.55875</v>
       </c>
     </row>
     <row r="21">
@@ -9531,10 +10541,15 @@
           <t xml:space="preserve">Arveja TAYAL 300g x 24u</t>
         </is>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="4">
+        <v>24</v>
+      </c>
+      <c r="D21" s="5">
+        <v>11146.71</v>
+      </c>
       <c r="E21" s="5">
-        <v>464.45</v>
+        <f>IF(C21&gt;0,D21/C21,"")</f>
+        <v>464.44624999999996</v>
       </c>
     </row>
     <row r="22">
@@ -9546,10 +10561,15 @@
           <t xml:space="preserve">Choclo Crema Amar. TAYAL 300g x 24u</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="4">
+        <v>24</v>
+      </c>
+      <c r="D22" s="5">
+        <v>12052.47</v>
+      </c>
       <c r="E22" s="5">
-        <v>502.19</v>
+        <f>IF(C22&gt;0,D22/C22,"")</f>
+        <v>502.18625</v>
       </c>
     </row>
     <row r="23">
@@ -9641,10 +10661,15 @@
           <t xml:space="preserve">AZUC LED SEL RUB S/TACC 6X800GR</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8918.91</v>
+      </c>
       <c r="E4" s="5">
-        <v>8918.91</v>
+        <f>IF(C4&gt;0,D4/C4,"")</f>
+        <v>1486.485</v>
       </c>
     </row>
     <row r="5">
@@ -9656,10 +10681,15 @@
           <t xml:space="preserve">ENDU LED LIGHT BSUC 6X500GR</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9436.86</v>
+      </c>
       <c r="E5" s="5">
-        <v>9436.86</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>1572.8100000000002</v>
       </c>
     </row>
     <row r="6">
@@ -9671,10 +10701,15 @@
           <t xml:space="preserve">AZUCAR LEDESMA CLASICA 10X1KG</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>14247.02</v>
+      </c>
       <c r="E6" s="5">
-        <v>14247.02</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>1424.702</v>
       </c>
     </row>
     <row r="7">
@@ -9781,10 +10816,15 @@
           <t xml:space="preserve">ACETO BALSAMICO PET 12X250ML MENOYO</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5">
+        <v>25536.03</v>
+      </c>
       <c r="E4" s="5">
-        <v>2128</v>
+        <f>IF(C4&gt;0,D4/C4,"")</f>
+        <v>2128.0025</v>
       </c>
     </row>
     <row r="5">
@@ -9796,10 +10836,15 @@
           <t xml:space="preserve">MOSTAZA 4X30X60GR MENOYO</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>27140.93</v>
+      </c>
       <c r="E5" s="5">
-        <v>6785.23</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>6785.2325</v>
       </c>
     </row>
     <row r="6">
@@ -9811,10 +10856,15 @@
           <t xml:space="preserve">VINAGRE DE ALCOHOL 12X500ML MENOYO</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10850.94</v>
+      </c>
       <c r="E6" s="5">
-        <v>904.25</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>904.245</v>
       </c>
     </row>
     <row r="7">
@@ -9826,10 +10876,15 @@
           <t xml:space="preserve">MOSTAZA 30X60GR LIVIAN</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>30</v>
+      </c>
+      <c r="D7" s="5">
+        <v>262068.94</v>
+      </c>
       <c r="E7" s="5">
-        <v>8735.63</v>
+        <f>IF(C7&gt;0,D7/C7,"")</f>
+        <v>8735.6313333333328</v>
       </c>
     </row>
     <row r="8">
@@ -9841,10 +10896,15 @@
           <t xml:space="preserve">VINAGRE DE ALCOHOL 12X1L MENOYO</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>16237.28</v>
+      </c>
       <c r="E8" s="5">
-        <v>1353.11</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>1353.1066666666668</v>
       </c>
     </row>
     <row r="9">
@@ -9856,10 +10916,15 @@
           <t xml:space="preserve">MAYONESA ORIGINAL 4X20X100cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="4">
+        <v>20</v>
+      </c>
+      <c r="D9" s="5">
+        <v>10117.79</v>
+      </c>
       <c r="E9" s="5">
-        <v>10117.79</v>
+        <f>IF(C9&gt;0,D9/C9,"")</f>
+        <v>505.88950000000006</v>
       </c>
     </row>
     <row r="10">
@@ -9871,10 +10936,15 @@
           <t xml:space="preserve">ACEITE GIRASOL AEROSOL 6X120GR MENOYO</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5">
+        <v>24596.23</v>
+      </c>
       <c r="E10" s="5">
-        <v>4099.37</v>
+        <f>IF(C10&gt;0,D10/C10,"")</f>
+        <v>4099.3716666666669</v>
       </c>
     </row>
     <row r="11">
@@ -9886,10 +10956,15 @@
           <t xml:space="preserve">MAYONESA 12X250cm3 MENOYO</t>
         </is>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="4">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5">
+        <v>8545.31</v>
+      </c>
       <c r="E11" s="5">
-        <v>712.11</v>
+        <f>IF(C11&gt;0,D11/C11,"")</f>
+        <v>712.10916666666662</v>
       </c>
     </row>
     <row r="12">
@@ -9901,9 +10976,14 @@
           <t xml:space="preserve">MOSTAZA 12X250GR MENOYO</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="4">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8845.44</v>
+      </c>
       <c r="E12" s="5">
+        <f>IF(C12&gt;0,D12/C12,"")</f>
         <v>737.12</v>
       </c>
     </row>
@@ -9916,10 +10996,15 @@
           <t xml:space="preserve">MAYONESA ORIGINAL 12X250cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="4">
+        <v>12</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12293.94</v>
+      </c>
       <c r="E13" s="5">
-        <v>1024.49</v>
+        <f>IF(C13&gt;0,D13/C13,"")</f>
+        <v>1024.4950000000001</v>
       </c>
     </row>
     <row r="14">
@@ -9931,10 +11016,15 @@
           <t xml:space="preserve">JUGO DE LIMON 6X250ML MENOYO</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="4">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8181.44</v>
+      </c>
       <c r="E14" s="5">
-        <v>1363.57</v>
+        <f>IF(C14&gt;0,D14/C14,"")</f>
+        <v>1363.5733333333333</v>
       </c>
     </row>
     <row r="15">
@@ -9946,10 +11036,15 @@
           <t xml:space="preserve">JUGO DE LIMON 12X250ML MENOYO</t>
         </is>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="4">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5">
+        <v>16362.88</v>
+      </c>
       <c r="E15" s="5">
-        <v>1363.57</v>
+        <f>IF(C15&gt;0,D15/C15,"")</f>
+        <v>1363.5733333333333</v>
       </c>
     </row>
     <row r="16">
@@ -9961,10 +11056,15 @@
           <t xml:space="preserve">MAYONESA LIGHT 12X250cm3 MENOYO</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="4">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5">
+        <v>9423.33</v>
+      </c>
       <c r="E16" s="5">
-        <v>785.28</v>
+        <f>IF(C16&gt;0,D16/C16,"")</f>
+        <v>785.2775</v>
       </c>
     </row>
     <row r="17">
@@ -9976,10 +11076,15 @@
           <t xml:space="preserve">MAYONESA 4x20x100cm3 MENOYO</t>
         </is>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>29917.35</v>
+      </c>
       <c r="E17" s="5">
-        <v>7479.34</v>
+        <f>IF(C17&gt;0,D17/C17,"")</f>
+        <v>7479.3375</v>
       </c>
     </row>
     <row r="18">
@@ -9991,10 +11096,15 @@
           <t xml:space="preserve">BIDON VINAGRE DE ALCOHOL 4X5L MENOYO</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="D18" s="5">
+        <v>24797.69</v>
+      </c>
       <c r="E18" s="5">
-        <v>6199.42</v>
+        <f>IF(C18&gt;0,D18/C18,"")</f>
+        <v>6199.4225</v>
       </c>
     </row>
     <row r="19">
@@ -10006,10 +11116,15 @@
           <t xml:space="preserve">VINAGRE DE VINO 12X500ML MENOYO</t>
         </is>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="4">
+        <v>12</v>
+      </c>
+      <c r="D19" s="5">
+        <v>16801.82</v>
+      </c>
       <c r="E19" s="5">
-        <v>1400.15</v>
+        <f>IF(C19&gt;0,D19/C19,"")</f>
+        <v>1400.1516666666666</v>
       </c>
     </row>
     <row r="20">
@@ -10021,10 +11136,15 @@
           <t xml:space="preserve">VINAGRE DE MANZANA 12X500ML MENOYO</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="4">
+        <v>12</v>
+      </c>
+      <c r="D20" s="5">
+        <v>20231.3</v>
+      </c>
       <c r="E20" s="5">
-        <v>1685.94</v>
+        <f>IF(C20&gt;0,D20/C20,"")</f>
+        <v>1685.9416666666666</v>
       </c>
     </row>
     <row r="21">
@@ -10036,10 +11156,15 @@
           <t xml:space="preserve">MAYONESA 15X500cm3 MENOYO</t>
         </is>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="4">
+        <v>15</v>
+      </c>
+      <c r="D21" s="5">
+        <v>22466.8</v>
+      </c>
       <c r="E21" s="5">
-        <v>1497.79</v>
+        <f>IF(C21&gt;0,D21/C21,"")</f>
+        <v>1497.7866666666666</v>
       </c>
     </row>
     <row r="22">
@@ -10051,10 +11176,15 @@
           <t xml:space="preserve">MAYONESA LIGHT 15X500cm3 MENOYO</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="4">
+        <v>15</v>
+      </c>
+      <c r="D22" s="5">
+        <v>22920.91</v>
+      </c>
       <c r="E22" s="5">
-        <v>1528.06</v>
+        <f>IF(C22&gt;0,D22/C22,"")</f>
+        <v>1528.0606666666667</v>
       </c>
     </row>
     <row r="23">
@@ -10066,10 +11196,15 @@
           <t xml:space="preserve">VINAGRE DE ALCOHOL 12X500ML ALCAZAR</t>
         </is>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="4">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5">
+        <v>8681.22</v>
+      </c>
       <c r="E23" s="5">
-        <v>723.43</v>
+        <f>IF(C23&gt;0,D23/C23,"")</f>
+        <v>723.435</v>
       </c>
     </row>
     <row r="24">
@@ -10081,10 +11216,15 @@
           <t xml:space="preserve">JUGO DE LIMON 6X500ML MENOYO</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>12639.37</v>
+      </c>
       <c r="E24" s="5">
-        <v>2106.56</v>
+        <f>IF(C24&gt;0,D24/C24,"")</f>
+        <v>2106.561666666667</v>
       </c>
     </row>
     <row r="25">
@@ -10096,10 +11236,15 @@
           <t xml:space="preserve">VINAGRE DE VINO 12X500ML ALCAZAR</t>
         </is>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4">
+        <v>12</v>
+      </c>
+      <c r="D25" s="5">
+        <v>13441.45</v>
+      </c>
       <c r="E25" s="5">
-        <v>1120.12</v>
+        <f>IF(C25&gt;0,D25/C25,"")</f>
+        <v>1120.1208333333334</v>
       </c>
     </row>
     <row r="26">
@@ -10111,10 +11256,15 @@
           <t xml:space="preserve">VINAGRE DE MANZANA 12X500ML ALCAZAR</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4">
+        <v>12</v>
+      </c>
+      <c r="D26" s="5">
+        <v>16185.01</v>
+      </c>
       <c r="E26" s="5">
-        <v>1348.75</v>
+        <f>IF(C26&gt;0,D26/C26,"")</f>
+        <v>1348.7508333333333</v>
       </c>
     </row>
     <row r="27">
@@ -10126,10 +11276,15 @@
           <t xml:space="preserve">VINAGRE DE VINO 12X1L MENOYO</t>
         </is>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4">
+        <v>12</v>
+      </c>
+      <c r="D27" s="5">
+        <v>25661.05</v>
+      </c>
       <c r="E27" s="5">
-        <v>2138.42</v>
+        <f>IF(C27&gt;0,D27/C27,"")</f>
+        <v>2138.4208333333331</v>
       </c>
     </row>
     <row r="28">
@@ -10141,10 +11296,15 @@
           <t xml:space="preserve">JUGO DE LIMON 12X1L MENOYO</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4">
+        <v>12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>35743.74</v>
+      </c>
       <c r="E28" s="5">
-        <v>2978.64</v>
+        <f>IF(C28&gt;0,D28/C28,"")</f>
+        <v>2978.645</v>
       </c>
     </row>
     <row r="29">
@@ -10171,10 +11331,15 @@
           <t xml:space="preserve">MAYONESA LIGHT EQUIL 12X250cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4">
+        <v>12</v>
+      </c>
+      <c r="D30" s="5">
+        <v>12660.86</v>
+      </c>
       <c r="E30" s="5">
-        <v>1055.07</v>
+        <f>IF(C30&gt;0,D30/C30,"")</f>
+        <v>1055.0716666666667</v>
       </c>
     </row>
     <row r="31">
@@ -10186,10 +11351,15 @@
           <t xml:space="preserve">MAYONESA OLIVA 12X250cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4">
+        <v>12</v>
+      </c>
+      <c r="D31" s="5">
+        <v>21006.66</v>
+      </c>
       <c r="E31" s="5">
-        <v>1750.56</v>
+        <f>IF(C31&gt;0,D31/C31,"")</f>
+        <v>1750.555</v>
       </c>
     </row>
     <row r="32">
@@ -10201,10 +11371,15 @@
           <t xml:space="preserve">MAYONESA AHUMADA 12X250cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="4">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5">
+        <v>21006.66</v>
+      </c>
       <c r="E32" s="5">
-        <v>1750.56</v>
+        <f>IF(C32&gt;0,D32/C32,"")</f>
+        <v>1750.555</v>
       </c>
     </row>
     <row r="33">
@@ -10216,10 +11391,15 @@
           <t xml:space="preserve">MAYONESA SABOR AJO 12X250cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
+      <c r="C33" s="4">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5">
+        <v>21006.66</v>
+      </c>
       <c r="E33" s="5">
-        <v>1750.56</v>
+        <f>IF(C33&gt;0,D33/C33,"")</f>
+        <v>1750.555</v>
       </c>
     </row>
     <row r="34">
@@ -10231,9 +11411,14 @@
           <t xml:space="preserve">MOSTAZA 12X250GR LIVIAN</t>
         </is>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
+      <c r="C34" s="4">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5">
+        <v>10921.8</v>
+      </c>
       <c r="E34" s="5">
+        <f>IF(C34&gt;0,D34/C34,"")</f>
         <v>910.15</v>
       </c>
     </row>
@@ -10246,9 +11431,14 @@
           <t xml:space="preserve">SALSA DE SOJA 6X250ML MENOYO</t>
         </is>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="4">
+        <v>6</v>
+      </c>
+      <c r="D35" s="5">
+        <v>12579.84</v>
+      </c>
       <c r="E35" s="5">
+        <f>IF(C35&gt;0,D35/C35,"")</f>
         <v>2096.64</v>
       </c>
     </row>
@@ -10261,10 +11451,15 @@
           <t xml:space="preserve">MAYONESA LIGHT EQUIL 15X500cm3 LIVIAN</t>
         </is>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
+      <c r="C36" s="4">
+        <v>15</v>
+      </c>
+      <c r="D36" s="5">
+        <v>29082.11</v>
+      </c>
       <c r="E36" s="5">
-        <v>1938.81</v>
+        <f>IF(C36&gt;0,D36/C36,"")</f>
+        <v>1938.8073333333334</v>
       </c>
     </row>
     <row r="37">
@@ -10291,10 +11486,15 @@
           <t xml:space="preserve">VINAGRE DE MANZANA 12X1L MENOYO</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
+      <c r="C38" s="4">
+        <v>12</v>
+      </c>
+      <c r="D38" s="5">
+        <v>33911.61</v>
+      </c>
       <c r="E38" s="5">
-        <v>2825.97</v>
+        <f>IF(C38&gt;0,D38/C38,"")</f>
+        <v>2825.9675</v>
       </c>
     </row>
   </sheetData>
@@ -11346,10 +12546,15 @@
           <t xml:space="preserve">GIN RIVER NEGRO x 750 x 6u</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>750</v>
+      </c>
+      <c r="D8" s="5">
+        <v>11592005.7</v>
+      </c>
       <c r="E8" s="5">
-        <v>15456.01</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>15456.007599999999</v>
       </c>
     </row>
     <row r="9">
@@ -11391,10 +12596,15 @@
           <t xml:space="preserve">5243 Gin Merle LONDON DRY 750 ml</t>
         </is>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="4">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>51452.49</v>
+      </c>
       <c r="E11" s="5">
-        <v>8575.42</v>
+        <f>IF(C11&gt;0,D11/C11,"")</f>
+        <v>8575.4149999999991</v>
       </c>
     </row>
     <row r="12">
@@ -11451,9 +12661,14 @@
           <t xml:space="preserve">Merle RTD PINK x6 u x 335 ml</t>
         </is>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="4">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10014.66</v>
+      </c>
       <c r="E15" s="5">
+        <f>IF(C15&gt;0,D15/C15,"")</f>
         <v>1669.11</v>
       </c>
     </row>
@@ -14941,10 +16156,15 @@
           <t xml:space="preserve">Mani King spicy hot 15x80gr</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="4">
+        <v>15</v>
+      </c>
+      <c r="D14" s="5">
+        <v>12818.09</v>
+      </c>
       <c r="E14" s="5">
-        <v>12818.09</v>
+        <f>IF(C14&gt;0,D14/C14,"")</f>
+        <v>854.53933333333339</v>
       </c>
     </row>
     <row r="15">
@@ -14956,10 +16176,15 @@
           <t xml:space="preserve">Maní c Sal s/piel 100g x 15 u</t>
         </is>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="4">
+        <v>15</v>
+      </c>
+      <c r="D15" s="5">
+        <v>12574.27</v>
+      </c>
       <c r="E15" s="5">
-        <v>12574.27</v>
+        <f>IF(C15&gt;0,D15/C15,"")</f>
+        <v>838.28466666666668</v>
       </c>
     </row>
     <row r="16">
@@ -14971,10 +16196,15 @@
           <t xml:space="preserve">Maní Sal con Piel 100G X 15u</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="4">
+        <v>15</v>
+      </c>
+      <c r="D16" s="5">
+        <v>12574.27</v>
+      </c>
       <c r="E16" s="5">
-        <v>12574.27</v>
+        <f>IF(C16&gt;0,D16/C16,"")</f>
+        <v>838.28466666666668</v>
       </c>
     </row>
     <row r="17">
@@ -15076,10 +16306,15 @@
           <t xml:space="preserve">Mani con cascara 10x400 gr</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="4">
+        <v>10</v>
+      </c>
+      <c r="D22" s="5">
+        <v>22706.91</v>
+      </c>
       <c r="E22" s="5">
-        <v>22706.91</v>
+        <f>IF(C22&gt;0,D22/C22,"")</f>
+        <v>2270.691</v>
       </c>
     </row>
     <row r="23">
@@ -15141,10 +16376,15 @@
           <t xml:space="preserve">MANI TOSTADO MK SIN SAL 20X350 GRS</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4">
+        <v>20</v>
+      </c>
+      <c r="D26" s="5">
+        <v>55511.48</v>
+      </c>
       <c r="E26" s="5">
-        <v>55511.48</v>
+        <f>IF(C26&gt;0,D26/C26,"")</f>
+        <v>2775.574</v>
       </c>
     </row>
     <row r="27">
@@ -15206,10 +16446,15 @@
           <t xml:space="preserve">REDONDITOS CHOCOLATE  210 G 16U</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4">
+        <v>16</v>
+      </c>
+      <c r="D30" s="5">
+        <v>26992.68</v>
+      </c>
       <c r="E30" s="5">
-        <v>1687.04</v>
+        <f>IF(C30&gt;0,D30/C30,"")</f>
+        <v>1687.0425</v>
       </c>
     </row>
   </sheetData>
@@ -15396,10 +16641,15 @@
           <t xml:space="preserve">MEDALLON CV CONGEL.214 CLASIC.24X4U7680</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5">
+        <v>108134.22</v>
+      </c>
       <c r="E4" s="5">
-        <v>4505.59</v>
+        <f>IF(C4&gt;0,D4/C4,"")</f>
+        <v>4505.5925</v>
       </c>
     </row>
     <row r="5">
@@ -15411,10 +16661,15 @@
           <t xml:space="preserve">CAJA MEDALL.CONG.214 80G 30X2 U 4,800 K</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5">
+        <v>73463.94</v>
+      </c>
       <c r="E5" s="5">
-        <v>2448.8</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>2448.7980000000002</v>
       </c>
     </row>
     <row r="6">
@@ -15426,10 +16681,15 @@
           <t xml:space="preserve">MEDALLON CV CONGEL.CHAMPION 24X4U 5376G</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5">
+        <v>60171.46</v>
+      </c>
       <c r="E6" s="5">
-        <v>2507.14</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>2507.1441666666665</v>
       </c>
     </row>
     <row r="7">
@@ -15441,10 +16701,15 @@
           <t xml:space="preserve">CAJA 20 X 6 UN. SALCHICHAS 214 225 GRS.</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5">
+        <v>34259.21</v>
+      </c>
       <c r="E7" s="5">
-        <v>1712.96</v>
+        <f>IF(C7&gt;0,D7/C7,"")</f>
+        <v>1712.9605</v>
       </c>
     </row>
     <row r="8">
@@ -15456,10 +16721,15 @@
           <t xml:space="preserve">CAJA 10 X 12 UN. SALCHICHAS 214 450 GRS</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
+        <v>33818.05</v>
+      </c>
       <c r="E8" s="5">
-        <v>3381.8</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>3381.8050000000003</v>
       </c>
     </row>
     <row r="9">
@@ -15471,10 +16741,15 @@
           <t xml:space="preserve">SALCH.CHAMPIFIESTA S/PIEL CAJA 30X180 G</t>
         </is>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="4">
+        <v>30</v>
+      </c>
+      <c r="D9" s="5">
+        <v>37619.5</v>
+      </c>
       <c r="E9" s="5">
-        <v>1253.98</v>
+        <f>IF(C9&gt;0,D9/C9,"")</f>
+        <v>1253.9833333333333</v>
       </c>
     </row>
     <row r="10">
@@ -15486,10 +16761,15 @@
           <t xml:space="preserve">SALCH.COC.Y AHU.S/PIEL L/GLUTEN 10PAQX12</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="4">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5">
+        <v>30594.12</v>
+      </c>
       <c r="E10" s="5">
-        <v>3059.41</v>
+        <f>IF(C10&gt;0,D10/C10,"")</f>
+        <v>3059.412</v>
       </c>
     </row>
     <row r="11">
@@ -15501,10 +16781,15 @@
           <t xml:space="preserve">SALCH.COC.Y AHU.S/PIEL L/GLUTEN 20PAQX6</t>
         </is>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="4">
+        <v>20</v>
+      </c>
+      <c r="D11" s="5">
+        <v>30193.13</v>
+      </c>
       <c r="E11" s="5">
-        <v>1509.66</v>
+        <f>IF(C11&gt;0,D11/C11,"")</f>
+        <v>1509.6565</v>
       </c>
     </row>
   </sheetData>
@@ -15581,10 +16866,15 @@
           <t xml:space="preserve">BIC CONFORT2 F WOMEN AR x24u</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5">
+        <v>435377.55</v>
+      </c>
       <c r="E4" s="5">
-        <v>36281.46</v>
+        <f>IF(C4&gt;0,D4/C4,"")</f>
+        <v>36281.4625</v>
       </c>
     </row>
     <row r="5">
@@ -15596,10 +16886,15 @@
           <t xml:space="preserve">AF BIC COMFORT 3 BLU AR X12</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5">
+        <v>282643.13</v>
+      </c>
       <c r="E5" s="5">
-        <v>11776.8</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>11776.797083333333</v>
       </c>
     </row>
     <row r="6">
@@ -15611,10 +16906,15 @@
           <t xml:space="preserve">COMFORT3 SEN AR</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5">
+        <v>282643.13</v>
+      </c>
       <c r="E6" s="5">
-        <v>11776.8</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>11776.797083333333</v>
       </c>
     </row>
     <row r="7">
@@ -15626,10 +16926,15 @@
           <t xml:space="preserve">AF BIC COMFORT 3 ACTION BLACK NIGHT CTL 24X12X1</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5">
+        <v>282643.13</v>
+      </c>
       <c r="E7" s="5">
-        <v>11776.8</v>
+        <f>IF(C7&gt;0,D7/C7,"")</f>
+        <v>11776.797083333333</v>
       </c>
     </row>
     <row r="8">
@@ -15641,10 +16946,15 @@
           <t xml:space="preserve">AF BIC TWIN CONFORT SENSITIVE CTL X24</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>24</v>
+      </c>
+      <c r="D8" s="5">
+        <v>406797.55</v>
+      </c>
       <c r="E8" s="5">
-        <v>16949.9</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>16949.897916666665</v>
       </c>
     </row>
     <row r="9">
@@ -15656,10 +16966,15 @@
           <t xml:space="preserve">BOL OPACO AZ BX/50</t>
         </is>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="4">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5">
+        <v>606525.08</v>
+      </c>
       <c r="E9" s="5">
-        <v>25271.88</v>
+        <f>IF(C9&gt;0,D9/C9,"")</f>
+        <v>25271.87833333333</v>
       </c>
     </row>
     <row r="10">
@@ -15671,10 +16986,15 @@
           <t xml:space="preserve">BOL OPACO  ROJO  BX X50</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="4">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5">
+        <v>606525.08</v>
+      </c>
       <c r="E10" s="5">
-        <v>25271.88</v>
+        <f>IF(C10&gt;0,D10/C10,"")</f>
+        <v>25271.87833333333</v>
       </c>
     </row>
     <row r="11">
@@ -15701,9 +17021,14 @@
           <t xml:space="preserve">BIC SENSITIVE SHAVER CARTELA X24</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="4">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5">
+        <v>490398.48</v>
+      </c>
       <c r="E12" s="5">
+        <f>IF(C12&gt;0,D12/C12,"")</f>
         <v>20433.27</v>
       </c>
     </row>
@@ -15776,10 +17101,15 @@
           <t xml:space="preserve">ENCENDEDOR BX7 12X50U</t>
         </is>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="4">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5">
+        <v>501440.94</v>
+      </c>
       <c r="E17" s="5">
-        <v>41786.74</v>
+        <f>IF(C17&gt;0,D17/C17,"")</f>
+        <v>41786.745</v>
       </c>
     </row>
     <row r="18">
@@ -15821,10 +17151,15 @@
           <t xml:space="preserve">MAXI J6 CARD12</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="4">
+        <v>22</v>
+      </c>
+      <c r="D20" s="5">
+        <v>322399.61</v>
+      </c>
       <c r="E20" s="5">
-        <v>14654.53</v>
+        <f>IF(C20&gt;0,D20/C20,"")</f>
+        <v>14654.527727272727</v>
       </c>
     </row>
     <row r="21">
@@ -15836,10 +17171,15 @@
           <t xml:space="preserve">MINI BIC CTL 22X12 CX264 ARG</t>
         </is>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="4">
+        <v>22</v>
+      </c>
+      <c r="D21" s="5">
+        <v>222004.41</v>
+      </c>
       <c r="E21" s="5">
-        <v>10091.11</v>
+        <f>IF(C21&gt;0,D21/C21,"")</f>
+        <v>10091.109545454545</v>
       </c>
     </row>
     <row r="22">
@@ -15931,10 +17271,15 @@
           <t xml:space="preserve">1265 TALITAS CLASICAx13u</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5">
+        <v>13092.93</v>
+      </c>
       <c r="E4" s="5">
-        <v>13092.93</v>
+        <f>IF(C4&gt;0,D4/C4,"")</f>
+        <v>1007.1484615384616</v>
       </c>
     </row>
     <row r="5">
@@ -16146,10 +17491,15 @@
           <t xml:space="preserve">CJ X12 ACEITUNA VERDE X 180 DOY PACK</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5">
+        <v>12997.58</v>
+      </c>
       <c r="E5" s="5">
-        <v>1083.13</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>1083.1316666666667</v>
       </c>
     </row>
     <row r="6">
@@ -16161,10 +17511,15 @@
           <t xml:space="preserve">CJ X16 A VERDE X 100 DOY PACK</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5">
+        <v>13963.21</v>
+      </c>
       <c r="E6" s="5">
-        <v>872.7</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>872.700625</v>
       </c>
     </row>
     <row r="7">
@@ -16176,10 +17531,15 @@
           <t xml:space="preserve">CJ X 16 A VERDE AJO X 100 DP</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5">
+        <v>26747.97</v>
+      </c>
       <c r="E7" s="5">
-        <v>1671.75</v>
+        <f>IF(C7&gt;0,D7/C7,"")</f>
+        <v>1671.748125</v>
       </c>
     </row>
     <row r="8">
@@ -16191,9 +17551,14 @@
           <t xml:space="preserve">CJ X 16 A VERDE AHU X 100 DP</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>25969.12</v>
+      </c>
       <c r="E8" s="5">
+        <f>IF(C8&gt;0,D8/C8,"")</f>
         <v>1623.07</v>
       </c>
     </row>
@@ -16206,10 +17571,15 @@
           <t xml:space="preserve">CJ X12 ACEITUNA VERDE XL X170 DOY PACK</t>
         </is>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="4">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5">
+        <v>21769.26</v>
+      </c>
       <c r="E9" s="5">
-        <v>1814.1</v>
+        <f>IF(C9&gt;0,D9/C9,"")</f>
+        <v>1814.1049999999998</v>
       </c>
     </row>
     <row r="10">
@@ -16221,10 +17591,15 @@
           <t xml:space="preserve">CJ X12 ACEITUNA VERDE XL X160 DP</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="4">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5">
+        <v>29856.75</v>
+      </c>
       <c r="E10" s="5">
-        <v>2488.06</v>
+        <f>IF(C10&gt;0,D10/C10,"")</f>
+        <v>2488.0625</v>
       </c>
     </row>
     <row r="11">
@@ -16236,10 +17611,15 @@
           <t xml:space="preserve">CJ X16 A VERDE DESC X80 DOY PACK</t>
         </is>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="4">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5">
+        <v>14889.39</v>
+      </c>
       <c r="E11" s="5">
-        <v>930.59</v>
+        <f>IF(C11&gt;0,D11/C11,"")</f>
+        <v>930.586875</v>
       </c>
     </row>
     <row r="12">
@@ -16251,10 +17631,15 @@
           <t xml:space="preserve">CJ X12 ACEITUNA NEGRA X180 DOY PACK</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="4">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5">
+        <v>19677.94</v>
+      </c>
       <c r="E12" s="5">
-        <v>1639.83</v>
+        <f>IF(C12&gt;0,D12/C12,"")</f>
+        <v>1639.8283333333331</v>
       </c>
     </row>
     <row r="13">
@@ -16266,10 +17651,15 @@
           <t xml:space="preserve">CJ X16 A NEGRA X100 DOY PACK</t>
         </is>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="4">
+        <v>16</v>
+      </c>
+      <c r="D13" s="5">
+        <v>24152.57</v>
+      </c>
       <c r="E13" s="5">
-        <v>1509.54</v>
+        <f>IF(C13&gt;0,D13/C13,"")</f>
+        <v>1509.535625</v>
       </c>
     </row>
     <row r="14">
@@ -16281,10 +17671,15 @@
           <t xml:space="preserve">CJ X 12 PEPINITOS X 140 DP</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="4">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5">
+        <v>27917.6</v>
+      </c>
       <c r="E14" s="5">
-        <v>2326.47</v>
+        <f>IF(C14&gt;0,D14/C14,"")</f>
+        <v>2326.4666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -16311,10 +17706,15 @@
           <t xml:space="preserve">CJ X 12 A VERDE RELL X 180 DP</t>
         </is>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="4">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5">
+        <v>24255.66</v>
+      </c>
       <c r="E16" s="5">
-        <v>2021.3</v>
+        <f>IF(C16&gt;0,D16/C16,"")</f>
+        <v>2021.305</v>
       </c>
     </row>
     <row r="17">
@@ -16326,10 +17726,15 @@
           <t xml:space="preserve">CJ X16 A VERDE RELL X100 DOY PACK</t>
         </is>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="4">
+        <v>16</v>
+      </c>
+      <c r="D17" s="5">
+        <v>21749.41</v>
+      </c>
       <c r="E17" s="5">
-        <v>1359.34</v>
+        <f>IF(C17&gt;0,D17/C17,"")</f>
+        <v>1359.338125</v>
       </c>
     </row>
     <row r="18">
@@ -16341,10 +17746,15 @@
           <t xml:space="preserve">CJ X 12 A VERDE DESC PRX165 FRASCO DE VIDRIO</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="4">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5">
+        <v>55444.91</v>
+      </c>
       <c r="E18" s="5">
-        <v>4620.41</v>
+        <f>IF(C18&gt;0,D18/C18,"")</f>
+        <v>4620.4091666666673</v>
       </c>
     </row>
     <row r="19">
@@ -16356,10 +17766,15 @@
           <t xml:space="preserve">CJ X 12 A VERDE PREMIUM VIDRIO x190</t>
         </is>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="4">
+        <v>12</v>
+      </c>
+      <c r="D19" s="5">
+        <v>59701.01</v>
+      </c>
       <c r="E19" s="5">
-        <v>4975.08</v>
+        <f>IF(C19&gt;0,D19/C19,"")</f>
+        <v>4975.0841666666665</v>
       </c>
     </row>
     <row r="20">
@@ -16371,10 +17786,15 @@
           <t xml:space="preserve">CJ X12 ACEITUNA VERDE DESC X150 DOY PACK</t>
         </is>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="4">
+        <v>12</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15695.39</v>
+      </c>
       <c r="E20" s="5">
-        <v>1307.95</v>
+        <f>IF(C20&gt;0,D20/C20,"")</f>
+        <v>1307.9491666666665</v>
       </c>
     </row>
     <row r="21">
@@ -16386,10 +17806,15 @@
           <t xml:space="preserve">CJ X12 PICKLE X140 DOY PACK</t>
         </is>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="4">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5">
+        <v>16819.53</v>
+      </c>
       <c r="E21" s="5">
-        <v>1401.63</v>
+        <f>IF(C21&gt;0,D21/C21,"")</f>
+        <v>1401.6274999999998</v>
       </c>
     </row>
     <row r="22">
@@ -16401,10 +17826,15 @@
           <t xml:space="preserve">CJ X 12 A VERDE ROD X 150 DP</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="4">
+        <v>12</v>
+      </c>
+      <c r="D22" s="5">
+        <v>19433.86</v>
+      </c>
       <c r="E22" s="5">
-        <v>1619.49</v>
+        <f>IF(C22&gt;0,D22/C22,"")</f>
+        <v>1619.4883333333335</v>
       </c>
     </row>
     <row r="23">
@@ -16416,10 +17846,15 @@
           <t xml:space="preserve">CJ X 16 A VERDE ROD X80 DOYPACK</t>
         </is>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="4">
+        <v>16</v>
+      </c>
+      <c r="D23" s="5">
+        <v>16600.04</v>
+      </c>
       <c r="E23" s="5">
-        <v>1037.5</v>
+        <f>IF(C23&gt;0,D23/C23,"")</f>
+        <v>1037.5025</v>
       </c>
     </row>
   </sheetData>
@@ -18746,9 +20181,14 @@
           <t xml:space="preserve">COPOS NF AZUCAR FLAKES 24X400GR</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="4">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5">
+        <v>71089.92</v>
+      </c>
       <c r="E4" s="5">
+        <f>IF(C4&gt;0,D4/C4,"")</f>
         <v>2962.08</v>
       </c>
     </row>
@@ -18761,10 +20201,15 @@
           <t xml:space="preserve">AVENA INSTANTANEA NF 24X300G</t>
         </is>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5">
+        <v>49515.52</v>
+      </c>
       <c r="E5" s="5">
-        <v>2063.15</v>
+        <f>IF(C5&gt;0,D5/C5,"")</f>
+        <v>2063.1466666666665</v>
       </c>
     </row>
     <row r="6">
@@ -18776,10 +20221,15 @@
           <t xml:space="preserve">AVENA TRADICIONAL NF 24X300GR</t>
         </is>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="4">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5">
+        <v>36251.21</v>
+      </c>
       <c r="E6" s="5">
-        <v>1510.47</v>
+        <f>IF(C6&gt;0,D6/C6,"")</f>
+        <v>1510.4670833333332</v>
       </c>
     </row>
     <row r="7">
@@ -18791,9 +20241,14 @@
           <t xml:space="preserve">BOLITA DE CHOCO NUTRI CHOK 20X200GR</t>
         </is>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5">
+        <v>38115</v>
+      </c>
       <c r="E7" s="5">
+        <f>IF(C7&gt;0,D7/C7,"")</f>
         <v>1905.75</v>
       </c>
     </row>
@@ -18806,10 +20261,15 @@
           <t xml:space="preserve">ANILLO FRUTA NUTRI RING 20X160GR</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="4">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5">
+        <v>28979.26</v>
+      </c>
       <c r="E8" s="5">
-        <v>1448.96</v>
+        <f>IF(C8&gt;0,D8/C8,"")</f>
+        <v>1448.963</v>
       </c>
     </row>
     <row r="9">
@@ -18821,10 +20281,15 @@
           <t xml:space="preserve">COPO AZUC FLAKES NUTRIFO 20X200 A</t>
         </is>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="4">
+        <v>20</v>
+      </c>
+      <c r="D9" s="5">
+        <v>27689.16</v>
+      </c>
       <c r="E9" s="5">
-        <v>1384.46</v>
+        <f>IF(C9&gt;0,D9/C9,"")</f>
+        <v>1384.458</v>
       </c>
     </row>
     <row r="10">
@@ -18836,10 +20301,15 @@
           <t xml:space="preserve">COPOS DE MAIZ NF 20X150GR</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="4">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5">
+        <v>29886.52</v>
+      </c>
       <c r="E10" s="5">
-        <v>1494.33</v>
+        <f>IF(C10&gt;0,D10/C10,"")</f>
+        <v>1494.326</v>
       </c>
     </row>
   </sheetData>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -10776,7 +10776,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 01/10/2026</t>
+          <t xml:space="preserve">Vigencia: 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -11289,86 +11289,81 @@
     </row>
     <row r="28">
       <c r="A28" s="4">
-        <v>5410003</v>
+        <v>5410002</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUGO DE LIMON 12X1L MENOYO</t>
-        </is>
-      </c>
-      <c r="C28" s="4">
-        <v>12</v>
-      </c>
-      <c r="D28" s="5">
-        <v>35743.74</v>
-      </c>
+          <t xml:space="preserve">VINAGRE DE ALCOHOL 12X1L MENOYO</t>
+        </is>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="5">
-        <f>IF(C28&gt;0,D28/C28,"")</f>
-        <v>2978.645</v>
+        <v>15192.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4">
-        <v>5412061</v>
+        <v>5410003</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACEITE DE MANTECA AEROSOL 6X120GR MENOYO</t>
-        </is>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
+          <t xml:space="preserve">JUGO DE LIMON 12X1L MENOYO</t>
+        </is>
+      </c>
+      <c r="C29" s="4">
+        <v>12</v>
+      </c>
+      <c r="D29" s="5">
+        <v>35743.74</v>
+      </c>
       <c r="E29" s="5">
-        <v>4099.37</v>
+        <f>IF(C29&gt;0,D29/C29,"")</f>
+        <v>2978.645</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4">
-        <v>5425041</v>
+        <v>5412061</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYONESA LIGHT EQUIL 12X250cm3 LIVIAN</t>
-        </is>
-      </c>
-      <c r="C30" s="4">
-        <v>12</v>
-      </c>
-      <c r="D30" s="5">
-        <v>12660.86</v>
-      </c>
+          <t xml:space="preserve">ACEITE DE MANTECA AEROSOL 6X120GR MENOYO</t>
+        </is>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <f>IF(C30&gt;0,D30/C30,"")</f>
-        <v>1055.0716666666667</v>
+        <v>4099.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4">
-        <v>5425042</v>
+        <v>5425041</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYONESA OLIVA 12X250cm3 LIVIAN</t>
+          <t xml:space="preserve">MAYONESA LIGHT EQUIL 12X250cm3 LIVIAN</t>
         </is>
       </c>
       <c r="C31" s="4">
         <v>12</v>
       </c>
       <c r="D31" s="5">
-        <v>21006.66</v>
+        <v>12660.86</v>
       </c>
       <c r="E31" s="5">
         <f>IF(C31&gt;0,D31/C31,"")</f>
-        <v>1750.555</v>
+        <v>1055.0716666666667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4">
-        <v>5425043</v>
+        <v>5425042</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYONESA AHUMADA 12X250cm3 LIVIAN</t>
+          <t xml:space="preserve">MAYONESA OLIVA 12X250cm3 LIVIAN</t>
         </is>
       </c>
       <c r="C32" s="4">
@@ -11384,11 +11379,11 @@
     </row>
     <row r="33">
       <c r="A33" s="4">
-        <v>5425044</v>
+        <v>5425043</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYONESA SABOR AJO 12X250cm3 LIVIAN</t>
+          <t xml:space="preserve">MAYONESA AHUMADA 12X250cm3 LIVIAN</t>
         </is>
       </c>
       <c r="C33" s="4">
@@ -11404,96 +11399,116 @@
     </row>
     <row r="34">
       <c r="A34" s="4">
-        <v>5425045</v>
+        <v>5425044</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOSTAZA 12X250GR LIVIAN</t>
+          <t xml:space="preserve">MAYONESA SABOR AJO 12X250cm3 LIVIAN</t>
         </is>
       </c>
       <c r="C34" s="4">
         <v>12</v>
       </c>
       <c r="D34" s="5">
-        <v>10921.8</v>
+        <v>21006.66</v>
       </c>
       <c r="E34" s="5">
         <f>IF(C34&gt;0,D34/C34,"")</f>
-        <v>910.15</v>
+        <v>1750.555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4">
-        <v>5425062</v>
+        <v>5425045</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALSA DE SOJA 6X250ML MENOYO</t>
+          <t xml:space="preserve">MOSTAZA 12X250GR LIVIAN</t>
         </is>
       </c>
       <c r="C35" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D35" s="5">
-        <v>12579.84</v>
+        <v>10921.8</v>
       </c>
       <c r="E35" s="5">
         <f>IF(C35&gt;0,D35/C35,"")</f>
-        <v>2096.64</v>
+        <v>910.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4">
-        <v>5450041</v>
+        <v>5425062</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYONESA LIGHT EQUIL 15X500cm3 LIVIAN</t>
+          <t xml:space="preserve">SALSA DE SOJA 6X250ML MENOYO</t>
         </is>
       </c>
       <c r="C36" s="4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D36" s="5">
-        <v>29082.11</v>
+        <v>12579.84</v>
       </c>
       <c r="E36" s="5">
         <f>IF(C36&gt;0,D36/C36,"")</f>
-        <v>1938.8073333333334</v>
+        <v>2096.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4">
-        <v>5450061</v>
+        <v>5450041</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALSA DE SOJA 6X500ML MENOYO</t>
-        </is>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
+          <t xml:space="preserve">MAYONESA LIGHT EQUIL 15X500cm3 LIVIAN</t>
+        </is>
+      </c>
+      <c r="C37" s="4">
+        <v>15</v>
+      </c>
+      <c r="D37" s="5">
+        <v>29082.11</v>
+      </c>
       <c r="E37" s="5">
-        <v>4096.77</v>
+        <f>IF(C37&gt;0,D37/C37,"")</f>
+        <v>1938.8073333333334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4">
+        <v>5450061</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALSA DE SOJA 6X500ML MENOYO</t>
+        </is>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5">
+        <v>4096.77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4">
         <v>54510002</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">VINAGRE DE MANZANA 12X1L MENOYO</t>
         </is>
       </c>
-      <c r="C38" s="4">
-        <v>12</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C39" s="4">
+        <v>12</v>
+      </c>
+      <c r="D39" s="5">
         <v>33911.61</v>
       </c>
-      <c r="E38" s="5">
-        <f>IF(C38&gt;0,D38/C38,"")</f>
+      <c r="E39" s="5">
+        <f>IF(C39&gt;0,D39/C39,"")</f>
         <v>2825.9675</v>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -11486,10 +11486,15 @@
           <t xml:space="preserve">SALSA DE SOJA 6X500ML MENOYO</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
+      <c r="C38" s="4">
+        <v>6</v>
+      </c>
+      <c r="D38" s="5">
+        <v>24580.62</v>
+      </c>
       <c r="E38" s="5">
-        <v>4096.77</v>
+        <f>IF(C38&gt;0,D38/C38,"")</f>
+        <v>4096.7699999999995</v>
       </c>
     </row>
     <row r="39">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -22,8 +22,7 @@
     <sheet name="POLDITOS" sheetId="18" r:id="rId18"/>
     <sheet name="PORTA HNOS" sheetId="19" r:id="rId19"/>
     <sheet name="PRO DE MAN" sheetId="20" r:id="rId20"/>
-    <sheet name="REFINERIA  DE GRASAS SUDAMERICA" sheetId="21" r:id="rId21"/>
-    <sheet name="RIOSMA" sheetId="22" r:id="rId22"/>
+    <sheet name="RIOSMA" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,7 +66,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,12 +199,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF455A64"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -249,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -324,9 +317,6 @@
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16500,7 +16490,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LISTA DE PRECIOS REFINERIA  DE GRASAS SUDAMERICANA - OCTUBRE 2026 (LISTA 1 - PRECIOS CON IVA)</t>
+          <t xml:space="preserve">LISTA DE PRECIOS RIOSMA - OCTUBRE 2026 (LISTA 1 - PRECIOS CON IVA)</t>
         </is>
       </c>
       <c r="B1" s="1"/>
@@ -16537,116 +16527,6 @@
         </is>
       </c>
       <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Precio por unidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>450033001</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GRASA VACUNA HAL SACHET 10X500GR</t>
-        </is>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5">
-        <v>1539.97</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>450033015</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GRASA DE CERDO HAL SACHET 10X500GR</t>
-        </is>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5">
-        <v>1692.55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>45412033000</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRIMICIA PARA UNTAR POTES 250GR</t>
-        </is>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5">
-        <v>1554.12</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="13"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LISTA DE PRECIOS RIOSMA - OCTUBRE 2026 (LISTA 1 - PRECIOS CON IVA)</t>
-        </is>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vigencia: 01/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codigo</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Descripcion del producto</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cant. por bulto (unidades)</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Precio por bulto</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Precio por unidad</t>
         </is>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -10766,7 +10766,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 14/10/2026</t>
+          <t xml:space="preserve">Vigencia: 15/10/2026</t>
         </is>
       </c>
     </row>
@@ -10850,11 +10850,11 @@
         <v>12</v>
       </c>
       <c r="D6" s="5">
-        <v>10850.94</v>
+        <v>10850.65</v>
       </c>
       <c r="E6" s="5">
         <f>IF(C6&gt;0,D6/C6,"")</f>
-        <v>904.245</v>
+        <v>904.2208333333333</v>
       </c>
     </row>
     <row r="7">
@@ -10890,11 +10890,11 @@
         <v>12</v>
       </c>
       <c r="D8" s="5">
-        <v>16237.28</v>
+        <v>16236.99</v>
       </c>
       <c r="E8" s="5">
         <f>IF(C8&gt;0,D8/C8,"")</f>
-        <v>1353.1066666666668</v>
+        <v>1353.0825</v>
       </c>
     </row>
     <row r="9">
@@ -11190,11 +11190,11 @@
         <v>12</v>
       </c>
       <c r="D23" s="5">
-        <v>8681.22</v>
+        <v>8681.07</v>
       </c>
       <c r="E23" s="5">
         <f>IF(C23&gt;0,D23/C23,"")</f>
-        <v>723.435</v>
+        <v>723.4225</v>
       </c>
     </row>
     <row r="24">
@@ -11283,13 +11283,18 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINAGRE DE ALCOHOL 12X1L MENOYO</t>
-        </is>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+          <t xml:space="preserve">VINAGRE DE ALCOHOL 12X1L ALCAZAR</t>
+        </is>
+      </c>
+      <c r="C28" s="4">
+        <v>12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>12989.59</v>
+      </c>
       <c r="E28" s="5">
-        <v>15192.87</v>
+        <f>IF(C28&gt;0,D28/C28,"")</f>
+        <v>1082.4658333333334</v>
       </c>
     </row>
     <row r="29">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -9561,7 +9561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 14/10/2026</t>
+          <t xml:space="preserve">Vigencia: 15/10/2026</t>
         </is>
       </c>
     </row>
@@ -10130,6 +10130,126 @@
       <c r="E30" s="5">
         <f>IF(C30&gt;0,D30/C30,"")</f>
         <v>16661.396666666667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4">
+        <v>874513</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromat. Gatillo Ropa Limpia 250ML</t>
+        </is>
+      </c>
+      <c r="C31" s="4">
+        <v>12</v>
+      </c>
+      <c r="D31" s="5">
+        <v>30501.37</v>
+      </c>
+      <c r="E31" s="5">
+        <f>IF(C31&gt;0,D31/C31,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4">
+        <v>874520</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromat. Gatillo Cony Fresh 250ML</t>
+        </is>
+      </c>
+      <c r="C32" s="4">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5">
+        <v>30501.37</v>
+      </c>
+      <c r="E32" s="5">
+        <f>IF(C32&gt;0,D32/C32,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4">
+        <v>874612</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Ropa Limpia 500ml</t>
+        </is>
+      </c>
+      <c r="C33" s="4">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E33" s="5">
+        <f>IF(C33&gt;0,D33/C33,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4">
+        <v>874629</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Bubble Candy 500ml</t>
+        </is>
+      </c>
+      <c r="C34" s="4">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E34" s="5">
+        <f>IF(C34&gt;0,D34/C34,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4">
+        <v>874698</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Green Bamboo 500ml</t>
+        </is>
+      </c>
+      <c r="C35" s="4">
+        <v>12</v>
+      </c>
+      <c r="D35" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E35" s="5">
+        <f>IF(C35&gt;0,D35/C35,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4">
+        <v>874704</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Cony Fresh 500ml</t>
+        </is>
+      </c>
+      <c r="C36" s="4">
+        <v>12</v>
+      </c>
+      <c r="D36" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E36" s="5">
+        <f>IF(C36&gt;0,D36/C36,"")</f>
+        <v>4574.2316666666666</v>
       </c>
     </row>
   </sheetData>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -7676,7 +7676,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 01/10/2026</t>
+          <t xml:space="preserve">Vigencia: 16/10/2026</t>
         </is>
       </c>
     </row>
@@ -8801,10 +8801,15 @@
           <t xml:space="preserve">YOG.BEB.ENT.FRUT/KW. S. X 900GR. MULTVT</t>
         </is>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
+      <c r="C63" s="4">
+        <v>12</v>
+      </c>
+      <c r="D63" s="5">
+        <v>25042.93</v>
+      </c>
       <c r="E63" s="5">
-        <v>2086.91</v>
+        <f>IF(C63&gt;0,D63/C63,"")</f>
+        <v>2086.9108333333334</v>
       </c>
     </row>
     <row r="64">
@@ -9210,11 +9215,11 @@
         <v>12</v>
       </c>
       <c r="D87" s="5">
-        <v>28134.39</v>
+        <v>26379.06</v>
       </c>
       <c r="E87" s="5">
         <f>IF(C87&gt;0,D87/C87,"")</f>
-        <v>2344.5325</v>
+        <v>2198.255</v>
       </c>
     </row>
     <row r="88">
@@ -9561,7 +9566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 15/10/2026</t>
+          <t xml:space="preserve">Vigencia: 16/10/2026</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10143,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aromat. Gatillo Ropa Limpia 250ML</t>
+          <t xml:space="preserve">Aromatiz. Gat. Ropa Limpia 250ml</t>
         </is>
       </c>
       <c r="C31" s="4">
@@ -10158,7 +10163,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aromat. Gatillo Cony Fresh 250ML</t>
+          <t xml:space="preserve">Aromatiz. Gat. Cony Fresh 250ml</t>
         </is>
       </c>
       <c r="C32" s="4">
@@ -10174,81 +10179,361 @@
     </row>
     <row r="33">
       <c r="A33" s="4">
-        <v>874612</v>
+        <v>874537</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aromatiz. Gat. Ropa Limpia 500ml</t>
+          <t xml:space="preserve">Aromatiz. Gat. Bubble Candy 250ml</t>
         </is>
       </c>
       <c r="C33" s="4">
         <v>12</v>
       </c>
       <c r="D33" s="5">
-        <v>54890.78</v>
+        <v>30501.37</v>
       </c>
       <c r="E33" s="5">
         <f>IF(C33&gt;0,D33/C33,"")</f>
-        <v>4574.2316666666666</v>
+        <v>2541.7808333333332</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4">
-        <v>874629</v>
+        <v>874544</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aromatiz. Gat. Bubble Candy 500ml</t>
+          <t xml:space="preserve">Aromatiz. Gat. Green Bamboo 250ml</t>
         </is>
       </c>
       <c r="C34" s="4">
         <v>12</v>
       </c>
       <c r="D34" s="5">
-        <v>54890.78</v>
+        <v>30501.37</v>
       </c>
       <c r="E34" s="5">
         <f>IF(C34&gt;0,D34/C34,"")</f>
-        <v>4574.2316666666666</v>
+        <v>2541.7808333333332</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4">
-        <v>874698</v>
+        <v>874551</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aromatiz. Gat. Green Bamboo 500ml</t>
+          <t xml:space="preserve">Aromatiz. Gat. Coconut Grove 250ml</t>
         </is>
       </c>
       <c r="C35" s="4">
         <v>12</v>
       </c>
       <c r="D35" s="5">
-        <v>54890.78</v>
+        <v>30501.37</v>
       </c>
       <c r="E35" s="5">
         <f>IF(C35&gt;0,D35/C35,"")</f>
-        <v>4574.2316666666666</v>
+        <v>2541.7808333333332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4">
-        <v>874704</v>
+        <v>874568</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aromatiz. Gat. Cony Fresh 500ml</t>
+          <t xml:space="preserve">Aromatiz. Gat. Exotic Flower 250ml</t>
         </is>
       </c>
       <c r="C36" s="4">
         <v>12</v>
       </c>
       <c r="D36" s="5">
-        <v>54890.78</v>
+        <v>30501.37</v>
       </c>
       <c r="E36" s="5">
         <f>IF(C36&gt;0,D36/C36,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4">
+        <v>874575</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Mary Blossom 250ml</t>
+        </is>
+      </c>
+      <c r="C37" s="4">
+        <v>12</v>
+      </c>
+      <c r="D37" s="5">
+        <v>30501.37</v>
+      </c>
+      <c r="E37" s="5">
+        <f>IF(C37&gt;0,D37/C37,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4">
+        <v>874582</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Victus 250ml</t>
+        </is>
+      </c>
+      <c r="C38" s="4">
+        <v>12</v>
+      </c>
+      <c r="D38" s="5">
+        <v>30501.37</v>
+      </c>
+      <c r="E38" s="5">
+        <f>IF(C38&gt;0,D38/C38,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4">
+        <v>874599</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Santal 250ml</t>
+        </is>
+      </c>
+      <c r="C39" s="4">
+        <v>12</v>
+      </c>
+      <c r="D39" s="5">
+        <v>30501.37</v>
+      </c>
+      <c r="E39" s="5">
+        <f>IF(C39&gt;0,D39/C39,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4">
+        <v>874605</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. One Alma 250ml</t>
+        </is>
+      </c>
+      <c r="C40" s="4">
+        <v>12</v>
+      </c>
+      <c r="D40" s="5">
+        <v>30501.37</v>
+      </c>
+      <c r="E40" s="5">
+        <f>IF(C40&gt;0,D40/C40,"")</f>
+        <v>2541.7808333333332</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4">
+        <v>874612</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Ropa Limpia 500ml</t>
+        </is>
+      </c>
+      <c r="C41" s="4">
+        <v>12</v>
+      </c>
+      <c r="D41" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E41" s="5">
+        <f>IF(C41&gt;0,D41/C41,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4">
+        <v>874629</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Bubble Candy 500ml</t>
+        </is>
+      </c>
+      <c r="C42" s="4">
+        <v>12</v>
+      </c>
+      <c r="D42" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E42" s="5">
+        <f>IF(C42&gt;0,D42/C42,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4">
+        <v>874636</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Coconut Grove 500ml</t>
+        </is>
+      </c>
+      <c r="C43" s="4">
+        <v>12</v>
+      </c>
+      <c r="D43" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E43" s="5">
+        <f>IF(C43&gt;0,D43/C43,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4">
+        <v>874643</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Exotic Flower 500ml</t>
+        </is>
+      </c>
+      <c r="C44" s="4">
+        <v>12</v>
+      </c>
+      <c r="D44" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E44" s="5">
+        <f>IF(C44&gt;0,D44/C44,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4">
+        <v>874650</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Mary Blossom 500ml</t>
+        </is>
+      </c>
+      <c r="C45" s="4">
+        <v>12</v>
+      </c>
+      <c r="D45" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E45" s="5">
+        <f>IF(C45&gt;0,D45/C45,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4">
+        <v>874667</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Victus 500ml</t>
+        </is>
+      </c>
+      <c r="C46" s="4">
+        <v>12</v>
+      </c>
+      <c r="D46" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E46" s="5">
+        <f>IF(C46&gt;0,D46/C46,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4">
+        <v>874674</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Santal 500ml</t>
+        </is>
+      </c>
+      <c r="C47" s="4">
+        <v>12</v>
+      </c>
+      <c r="D47" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E47" s="5">
+        <f>IF(C47&gt;0,D47/C47,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4">
+        <v>874681</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. One Alma 500ml</t>
+        </is>
+      </c>
+      <c r="C48" s="4">
+        <v>12</v>
+      </c>
+      <c r="D48" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E48" s="5">
+        <f>IF(C48&gt;0,D48/C48,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4">
+        <v>874698</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Green Bamboo 500ml</t>
+        </is>
+      </c>
+      <c r="C49" s="4">
+        <v>12</v>
+      </c>
+      <c r="D49" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E49" s="5">
+        <f>IF(C49&gt;0,D49/C49,"")</f>
+        <v>4574.2316666666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4">
+        <v>874704</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aromatiz. Gat. Cony Fresh 500ml</t>
+        </is>
+      </c>
+      <c r="C50" s="4">
+        <v>12</v>
+      </c>
+      <c r="D50" s="5">
+        <v>54890.78</v>
+      </c>
+      <c r="E50" s="5">
+        <f>IF(C50&gt;0,D50/C50,"")</f>
         <v>4574.2316666666666</v>
       </c>
     </row>
@@ -11446,10 +11731,15 @@
           <t xml:space="preserve">ACEITE DE MANTECA AEROSOL 6X120GR MENOYO</t>
         </is>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5">
+        <v>24596.23</v>
+      </c>
       <c r="E30" s="5">
-        <v>4099.37</v>
+        <f>IF(C30&gt;0,D30/C30,"")</f>
+        <v>4099.3716666666669</v>
       </c>
     </row>
     <row r="31">
@@ -11485,11 +11775,11 @@
         <v>12</v>
       </c>
       <c r="D32" s="5">
-        <v>21006.66</v>
+        <v>1750.56</v>
       </c>
       <c r="E32" s="5">
         <f>IF(C32&gt;0,D32/C32,"")</f>
-        <v>1750.555</v>
+        <v>145.88</v>
       </c>
     </row>
     <row r="33">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -18206,7 +18206,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 01/10/2026</t>
+          <t xml:space="preserve">Vigencia: 19/10/2026</t>
         </is>
       </c>
     </row>
@@ -18270,11 +18270,11 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>52228.72</v>
+        <v>53795.58</v>
       </c>
       <c r="E5" s="5">
         <f>IF(C5&gt;0,D5/C5,"")</f>
-        <v>4352.3933333333334</v>
+        <v>4482.965</v>
       </c>
     </row>
     <row r="6">
@@ -18370,11 +18370,11 @@
         <v>6</v>
       </c>
       <c r="D10" s="5">
-        <v>51104.97</v>
+        <v>52127.08</v>
       </c>
       <c r="E10" s="5">
         <f>IF(C10&gt;0,D10/C10,"")</f>
-        <v>8517.495</v>
+        <v>8687.8466666666664</v>
       </c>
     </row>
     <row r="11">
@@ -18390,11 +18390,11 @@
         <v>6</v>
       </c>
       <c r="D11" s="5">
-        <v>33146.32</v>
+        <v>33809.24</v>
       </c>
       <c r="E11" s="5">
         <f>IF(C11&gt;0,D11/C11,"")</f>
-        <v>5524.3866666666663</v>
+        <v>5634.873333333333</v>
       </c>
     </row>
     <row r="12">
@@ -18430,11 +18430,11 @@
         <v>12</v>
       </c>
       <c r="D13" s="5">
-        <v>46427.75</v>
+        <v>47356.3</v>
       </c>
       <c r="E13" s="5">
         <f>IF(C13&gt;0,D13/C13,"")</f>
-        <v>3868.9791666666665</v>
+        <v>3946.3583333333336</v>
       </c>
     </row>
     <row r="14">
@@ -18450,11 +18450,11 @@
         <v>12</v>
       </c>
       <c r="D14" s="5">
-        <v>91430.83</v>
+        <v>93259.44</v>
       </c>
       <c r="E14" s="5">
         <f>IF(C14&gt;0,D14/C14,"")</f>
-        <v>7619.2358333333332</v>
+        <v>7771.62</v>
       </c>
     </row>
     <row r="15">
@@ -18470,11 +18470,11 @@
         <v>12</v>
       </c>
       <c r="D15" s="5">
-        <v>127610.75</v>
+        <v>130162.97</v>
       </c>
       <c r="E15" s="5">
         <f>IF(C15&gt;0,D15/C15,"")</f>
-        <v>10634.229166666666</v>
+        <v>10846.914166666667</v>
       </c>
     </row>
     <row r="16">
@@ -18490,11 +18490,11 @@
         <v>12</v>
       </c>
       <c r="D16" s="5">
-        <v>87748.96</v>
+        <v>89503.94</v>
       </c>
       <c r="E16" s="5">
         <f>IF(C16&gt;0,D16/C16,"")</f>
-        <v>7312.4133333333339</v>
+        <v>7458.6616666666669</v>
       </c>
     </row>
     <row r="17">
@@ -18570,11 +18570,11 @@
         <v>24</v>
       </c>
       <c r="D20" s="5">
-        <v>46125.2</v>
+        <v>47047.7</v>
       </c>
       <c r="E20" s="5">
         <f>IF(C20&gt;0,D20/C20,"")</f>
-        <v>1921.8833333333332</v>
+        <v>1960.3208333333332</v>
       </c>
     </row>
     <row r="21">
@@ -18590,11 +18590,11 @@
         <v>6</v>
       </c>
       <c r="D21" s="5">
-        <v>41084.91</v>
+        <v>47047.7</v>
       </c>
       <c r="E21" s="5">
         <f>IF(C21&gt;0,D21/C21,"")</f>
-        <v>6847.4850000000006</v>
+        <v>7841.2833333333328</v>
       </c>
     </row>
     <row r="22">
@@ -18610,11 +18610,11 @@
         <v>6</v>
       </c>
       <c r="D22" s="5">
-        <v>76142.37</v>
+        <v>77665.22</v>
       </c>
       <c r="E22" s="5">
         <f>IF(C22&gt;0,D22/C22,"")</f>
-        <v>12690.394999999999</v>
+        <v>12944.203333333333</v>
       </c>
     </row>
     <row r="23">
@@ -18630,11 +18630,11 @@
         <v>24</v>
       </c>
       <c r="D23" s="5">
-        <v>38938.8</v>
+        <v>39717.6</v>
       </c>
       <c r="E23" s="5">
         <f>IF(C23&gt;0,D23/C23,"")</f>
-        <v>1622.45</v>
+        <v>1654.8999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -18650,11 +18650,11 @@
         <v>6</v>
       </c>
       <c r="D24" s="5">
-        <v>57592.37</v>
+        <v>58744.22</v>
       </c>
       <c r="E24" s="5">
         <f>IF(C24&gt;0,D24/C24,"")</f>
-        <v>9598.7283333333344</v>
+        <v>9790.7033333333329</v>
       </c>
     </row>
     <row r="25">
@@ -18670,11 +18670,11 @@
         <v>12</v>
       </c>
       <c r="D25" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E25" s="5">
         <f>IF(C25&gt;0,D25/C25,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="26">
@@ -18690,11 +18690,11 @@
         <v>12</v>
       </c>
       <c r="D26" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E26" s="5">
         <f>IF(C26&gt;0,D26/C26,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="27">
@@ -18710,11 +18710,11 @@
         <v>12</v>
       </c>
       <c r="D27" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E27" s="5">
         <f>IF(C27&gt;0,D27/C27,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="28">
@@ -18730,11 +18730,11 @@
         <v>12</v>
       </c>
       <c r="D28" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E28" s="5">
         <f>IF(C28&gt;0,D28/C28,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="29">
@@ -18750,11 +18750,11 @@
         <v>12</v>
       </c>
       <c r="D29" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E29" s="5">
         <f>IF(C29&gt;0,D29/C29,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="30">
@@ -18770,11 +18770,11 @@
         <v>12</v>
       </c>
       <c r="D30" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E30" s="5">
         <f>IF(C30&gt;0,D30/C30,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="31">
@@ -18790,11 +18790,11 @@
         <v>12</v>
       </c>
       <c r="D31" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E31" s="5">
         <f>IF(C31&gt;0,D31/C31,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="32">
@@ -18810,11 +18810,11 @@
         <v>12</v>
       </c>
       <c r="D32" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E32" s="5">
         <f>IF(C32&gt;0,D32/C32,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="33">
@@ -18830,11 +18830,11 @@
         <v>12</v>
       </c>
       <c r="D33" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E33" s="5">
         <f>IF(C33&gt;0,D33/C33,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="34">
@@ -18850,11 +18850,11 @@
         <v>12</v>
       </c>
       <c r="D34" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E34" s="5">
         <f>IF(C34&gt;0,D34/C34,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="35">
@@ -18870,11 +18870,11 @@
         <v>12</v>
       </c>
       <c r="D35" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E35" s="5">
         <f>IF(C35&gt;0,D35/C35,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="36">
@@ -18890,11 +18890,11 @@
         <v>24</v>
       </c>
       <c r="D36" s="5">
-        <v>45849.9</v>
+        <v>46766.89</v>
       </c>
       <c r="E36" s="5">
         <f>IF(C36&gt;0,D36/C36,"")</f>
-        <v>1910.4125000000001</v>
+        <v>1948.6204166666666</v>
       </c>
     </row>
     <row r="37">
@@ -18910,11 +18910,11 @@
         <v>24</v>
       </c>
       <c r="D37" s="5">
-        <v>45849.9</v>
+        <v>46766.89</v>
       </c>
       <c r="E37" s="5">
         <f>IF(C37&gt;0,D37/C37,"")</f>
-        <v>1910.4125000000001</v>
+        <v>1948.6204166666666</v>
       </c>
     </row>
     <row r="38">
@@ -18930,11 +18930,11 @@
         <v>24</v>
       </c>
       <c r="D38" s="5">
-        <v>45849.9</v>
+        <v>46766.89</v>
       </c>
       <c r="E38" s="5">
         <f>IF(C38&gt;0,D38/C38,"")</f>
-        <v>1910.4125000000001</v>
+        <v>1948.6204166666666</v>
       </c>
     </row>
     <row r="39">
@@ -18950,11 +18950,11 @@
         <v>24</v>
       </c>
       <c r="D39" s="5">
-        <v>45849.9</v>
+        <v>46766.89</v>
       </c>
       <c r="E39" s="5">
         <f>IF(C39&gt;0,D39/C39,"")</f>
-        <v>1910.4125000000001</v>
+        <v>1948.6204166666666</v>
       </c>
     </row>
     <row r="40">
@@ -18970,11 +18970,11 @@
         <v>24</v>
       </c>
       <c r="D40" s="5">
-        <v>45849.9</v>
+        <v>46766.89</v>
       </c>
       <c r="E40" s="5">
         <f>IF(C40&gt;0,D40/C40,"")</f>
-        <v>1910.4125000000001</v>
+        <v>1948.6204166666666</v>
       </c>
     </row>
     <row r="41">
@@ -18990,11 +18990,11 @@
         <v>6</v>
       </c>
       <c r="D41" s="5">
-        <v>54460.01</v>
+        <v>55549.19</v>
       </c>
       <c r="E41" s="5">
         <f>IF(C41&gt;0,D41/C41,"")</f>
-        <v>9076.6683333333331</v>
+        <v>9258.1983333333337</v>
       </c>
     </row>
     <row r="42">
@@ -19010,11 +19010,11 @@
         <v>24</v>
       </c>
       <c r="D42" s="5">
-        <v>53484.23</v>
+        <v>54553.91</v>
       </c>
       <c r="E42" s="5">
         <f>IF(C42&gt;0,D42/C42,"")</f>
-        <v>2228.5095833333335</v>
+        <v>2273.0795833333336</v>
       </c>
     </row>
     <row r="43">
@@ -19030,11 +19030,11 @@
         <v>12</v>
       </c>
       <c r="D43" s="5">
-        <v>116887.69</v>
+        <v>119225.45</v>
       </c>
       <c r="E43" s="5">
         <f>IF(C43&gt;0,D43/C43,"")</f>
-        <v>9740.6408333333329</v>
+        <v>9935.4541666666664</v>
       </c>
     </row>
     <row r="44">
@@ -19050,11 +19050,11 @@
         <v>12</v>
       </c>
       <c r="D44" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E44" s="5">
         <f>IF(C44&gt;0,D44/C44,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="45">
@@ -19070,11 +19070,11 @@
         <v>12</v>
       </c>
       <c r="D45" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E45" s="5">
         <f>IF(C45&gt;0,D45/C45,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="46">
@@ -19090,11 +19090,11 @@
         <v>24</v>
       </c>
       <c r="D46" s="5">
-        <v>45849.9</v>
+        <v>46766.89</v>
       </c>
       <c r="E46" s="5">
         <f>IF(C46&gt;0,D46/C46,"")</f>
-        <v>1910.4125000000001</v>
+        <v>1948.6204166666666</v>
       </c>
     </row>
     <row r="47">
@@ -19110,11 +19110,11 @@
         <v>12</v>
       </c>
       <c r="D47" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E47" s="5">
         <f>IF(C47&gt;0,D47/C47,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="48">
@@ -19130,11 +19130,11 @@
         <v>12</v>
       </c>
       <c r="D48" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E48" s="5">
         <f>IF(C48&gt;0,D48/C48,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="49">
@@ -19150,11 +19150,11 @@
         <v>12</v>
       </c>
       <c r="D49" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E49" s="5">
         <f>IF(C49&gt;0,D49/C49,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="50">
@@ -19170,11 +19170,11 @@
         <v>12</v>
       </c>
       <c r="D50" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E50" s="5">
         <f>IF(C50&gt;0,D50/C50,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="51">
@@ -19190,11 +19190,11 @@
         <v>12</v>
       </c>
       <c r="D51" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E51" s="5">
         <f>IF(C51&gt;0,D51/C51,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="52">
@@ -19210,11 +19210,11 @@
         <v>12</v>
       </c>
       <c r="D52" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E52" s="5">
         <f>IF(C52&gt;0,D52/C52,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="53">
@@ -19230,11 +19230,11 @@
         <v>12</v>
       </c>
       <c r="D53" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E53" s="5">
         <f>IF(C53&gt;0,D53/C53,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="54">
@@ -19250,11 +19250,11 @@
         <v>12</v>
       </c>
       <c r="D54" s="5">
-        <v>23765.08</v>
+        <v>24240.38</v>
       </c>
       <c r="E54" s="5">
         <f>IF(C54&gt;0,D54/C54,"")</f>
-        <v>1980.4233333333334</v>
+        <v>2020.0316666666668</v>
       </c>
     </row>
     <row r="55">
@@ -19290,11 +19290,11 @@
         <v>12</v>
       </c>
       <c r="D56" s="5">
-        <v>35450.64</v>
+        <v>36159.65</v>
       </c>
       <c r="E56" s="5">
         <f>IF(C56&gt;0,D56/C56,"")</f>
-        <v>2954.22</v>
+        <v>3013.3041666666668</v>
       </c>
     </row>
     <row r="57">
@@ -19310,11 +19310,11 @@
         <v>12</v>
       </c>
       <c r="D57" s="5">
-        <v>14185.1</v>
+        <v>14468.8</v>
       </c>
       <c r="E57" s="5">
         <f>IF(C57&gt;0,D57/C57,"")</f>
-        <v>1182.0916666666667</v>
+        <v>1205.7333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -19330,11 +19330,11 @@
         <v>12</v>
       </c>
       <c r="D58" s="5">
-        <v>14185.1</v>
+        <v>14468.8</v>
       </c>
       <c r="E58" s="5">
         <f>IF(C58&gt;0,D58/C58,"")</f>
-        <v>1182.0916666666667</v>
+        <v>1205.7333333333333</v>
       </c>
     </row>
     <row r="59">
@@ -19350,11 +19350,11 @@
         <v>12</v>
       </c>
       <c r="D59" s="5">
-        <v>14185.1</v>
+        <v>14468.8</v>
       </c>
       <c r="E59" s="5">
         <f>IF(C59&gt;0,D59/C59,"")</f>
-        <v>1182.0916666666667</v>
+        <v>1205.7333333333333</v>
       </c>
     </row>
     <row r="60">
@@ -19370,11 +19370,11 @@
         <v>12</v>
       </c>
       <c r="D60" s="5">
-        <v>14185.1</v>
+        <v>14468.8</v>
       </c>
       <c r="E60" s="5">
         <f>IF(C60&gt;0,D60/C60,"")</f>
-        <v>1182.0916666666667</v>
+        <v>1205.7333333333333</v>
       </c>
     </row>
     <row r="61">
@@ -19390,11 +19390,11 @@
         <v>12</v>
       </c>
       <c r="D61" s="5">
-        <v>14185.1</v>
+        <v>14468.8</v>
       </c>
       <c r="E61" s="5">
         <f>IF(C61&gt;0,D61/C61,"")</f>
-        <v>1182.0916666666667</v>
+        <v>1205.7333333333333</v>
       </c>
     </row>
     <row r="62">
@@ -19430,11 +19430,11 @@
         <v>24</v>
       </c>
       <c r="D63" s="5">
-        <v>42118.81</v>
+        <v>42961.18</v>
       </c>
       <c r="E63" s="5">
         <f>IF(C63&gt;0,D63/C63,"")</f>
-        <v>1754.9504166666666</v>
+        <v>1790.0491666666667</v>
       </c>
     </row>
     <row r="64">
@@ -19470,11 +19470,11 @@
         <v>12</v>
       </c>
       <c r="D65" s="5">
-        <v>41089.19</v>
+        <v>41910.99</v>
       </c>
       <c r="E65" s="5">
         <f>IF(C65&gt;0,D65/C65,"")</f>
-        <v>3424.0991666666669</v>
+        <v>3492.5825</v>
       </c>
     </row>
     <row r="66">
@@ -19570,11 +19570,11 @@
         <v>12</v>
       </c>
       <c r="D70" s="5">
-        <v>91430.83</v>
+        <v>93259.44</v>
       </c>
       <c r="E70" s="5">
         <f>IF(C70&gt;0,D70/C70,"")</f>
-        <v>7619.2358333333332</v>
+        <v>7771.62</v>
       </c>
     </row>
   </sheetData>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -7676,7 +7676,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 16/10/2026</t>
+          <t xml:space="preserve">Vigencia: 19/10/2026</t>
         </is>
       </c>
     </row>
@@ -9155,11 +9155,11 @@
         <v>12</v>
       </c>
       <c r="D84" s="5">
-        <v>22179.3</v>
+        <v>20386.08</v>
       </c>
       <c r="E84" s="5">
         <f>IF(C84&gt;0,D84/C84,"")</f>
-        <v>1848.2749999999999</v>
+        <v>1698.8400000000001</v>
       </c>
     </row>
     <row r="85">
@@ -9175,11 +9175,11 @@
         <v>12</v>
       </c>
       <c r="D85" s="5">
-        <v>22179.3</v>
+        <v>20386.08</v>
       </c>
       <c r="E85" s="5">
         <f>IF(C85&gt;0,D85/C85,"")</f>
-        <v>1848.2749999999999</v>
+        <v>1698.8400000000001</v>
       </c>
     </row>
     <row r="86">
@@ -9195,11 +9195,11 @@
         <v>12</v>
       </c>
       <c r="D86" s="5">
-        <v>27804.63</v>
+        <v>22019.13</v>
       </c>
       <c r="E86" s="5">
         <f>IF(C86&gt;0,D86/C86,"")</f>
-        <v>2317.0525000000002</v>
+        <v>1834.9275</v>
       </c>
     </row>
     <row r="87">
@@ -9215,11 +9215,11 @@
         <v>12</v>
       </c>
       <c r="D87" s="5">
-        <v>26379.06</v>
+        <v>24232.43</v>
       </c>
       <c r="E87" s="5">
         <f>IF(C87&gt;0,D87/C87,"")</f>
-        <v>2198.255</v>
+        <v>2019.3691666666666</v>
       </c>
     </row>
     <row r="88">
@@ -9566,7 +9566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 16/10/2026</t>
+          <t xml:space="preserve">Vigencia: 19/10/2026</t>
         </is>
       </c>
     </row>
@@ -18587,14 +18587,14 @@
         </is>
       </c>
       <c r="C21" s="4">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D21" s="5">
         <v>47047.7</v>
       </c>
       <c r="E21" s="5">
         <f>IF(C21&gt;0,D21/C21,"")</f>
-        <v>7841.2833333333328</v>
+        <v>1960.3208333333332</v>
       </c>
     </row>
     <row r="22">
@@ -19499,81 +19499,21 @@
     </row>
     <row r="67">
       <c r="A67" s="4">
-        <v>39014866</v>
+        <v>39014996</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882 FERNET CON POMELO 7 473mlx6x4</t>
+          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
         </is>
       </c>
       <c r="C67" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D67" s="5">
-        <v>37989.09</v>
+        <v>93259.44</v>
       </c>
       <c r="E67" s="5">
         <f>IF(C67&gt;0,D67/C67,"")</f>
-        <v>1582.8787499999999</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4">
-        <v>39014882</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gancia LIMA LIMON ONE 4x6x473</t>
-        </is>
-      </c>
-      <c r="C68" s="4">
-        <v>24</v>
-      </c>
-      <c r="D68" s="5">
-        <v>51692.42</v>
-      </c>
-      <c r="E68" s="5">
-        <f>IF(C68&gt;0,D68/C68,"")</f>
-        <v>2153.8508333333334</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4">
-        <v>39014884</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DR LEMON RED BERRIES 5% 4x6x473</t>
-        </is>
-      </c>
-      <c r="C69" s="4">
-        <v>24</v>
-      </c>
-      <c r="D69" s="5">
-        <v>45849.9</v>
-      </c>
-      <c r="E69" s="5">
-        <f>IF(C69&gt;0,D69/C69,"")</f>
-        <v>1910.4125000000001</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4">
-        <v>39014996</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
-        </is>
-      </c>
-      <c r="C70" s="4">
-        <v>12</v>
-      </c>
-      <c r="D70" s="5">
-        <v>93259.44</v>
-      </c>
-      <c r="E70" s="5">
-        <f>IF(C70&gt;0,D70/C70,"")</f>
         <v>7771.62</v>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -351,7 +351,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 14/10/2026</t>
+          <t xml:space="preserve">Vigencia: 20/10/2026</t>
         </is>
       </c>
     </row>
@@ -2840,11 +2840,11 @@
         <v>54</v>
       </c>
       <c r="E111" s="5">
-        <v>55450.42</v>
+        <v>54222.36</v>
       </c>
       <c r="F111" s="5">
         <f>IF(D111&gt;0,E111/D111,"")</f>
-        <v>1026.8596296296296</v>
+        <v>1004.1177777777777</v>
       </c>
     </row>
     <row r="112">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -17371,10 +17371,15 @@
           <t xml:space="preserve">AF BIC SOLEIL CTL X12</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="4">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>391305.58</v>
+      </c>
       <c r="E14" s="5">
-        <v>16304.4</v>
+        <f>IF(C14&gt;0,D14/C14,"")</f>
+        <v>16304.399166666668</v>
       </c>
     </row>
     <row r="15">
@@ -18206,7 +18211,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 19/10/2026</t>
+          <t xml:space="preserve">Vigencia: 21/10/2026</t>
         </is>
       </c>
     </row>
@@ -19499,21 +19504,41 @@
     </row>
     <row r="67">
       <c r="A67" s="4">
-        <v>39014996</v>
+        <v>39014884</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
+          <t xml:space="preserve">DR LEMON RED BERRIES 5% 4x6x473</t>
         </is>
       </c>
       <c r="C67" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D67" s="5">
-        <v>93259.44</v>
+        <v>46766.89</v>
       </c>
       <c r="E67" s="5">
         <f>IF(C67&gt;0,D67/C67,"")</f>
+        <v>1948.6204166666666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4">
+        <v>39014996</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
+        </is>
+      </c>
+      <c r="C68" s="4">
+        <v>12</v>
+      </c>
+      <c r="D68" s="5">
+        <v>93259.44</v>
+      </c>
+      <c r="E68" s="5">
+        <f>IF(C68&gt;0,D68/C68,"")</f>
         <v>7771.62</v>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAPIÑADAS DE MANÍ</t>
+          <t xml:space="preserve">GARRAPIÑADAS DE MANÍ</t>
         </is>
       </c>
       <c r="C53" s="4"/>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAPIÑADA DE MANI NAMUR 36X60GR</t>
+          <t xml:space="preserve">GARRAPIÑADAS DE MANI NAMUR 36X60GR</t>
         </is>
       </c>
       <c r="C54" s="4">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAPIÑADAS DE MANÍ 36X80GR</t>
+          <t xml:space="preserve">GARRAPIÑADAS DE MANÍ 36X80GR</t>
         </is>
       </c>
       <c r="C211" s="4">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAPIÑADAS DE MANÍ 36X100GR</t>
+          <t xml:space="preserve">GARRAPIÑADAS DE MANÍ 36X100GR</t>
         </is>
       </c>
       <c r="C212" s="4">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAPIÑADAS DE ALMENDRAS</t>
+          <t xml:space="preserve">GARRAPIÑADAS DE ALMENDRAS</t>
         </is>
       </c>
       <c r="C215" s="4"/>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARAPIÑADAS DE MANÍ BAÑADA CON CHOCOLATE</t>
+          <t xml:space="preserve">GARRAPIÑADAS DE MANÍ BAÑADA CON CHOCOLATE</t>
         </is>
       </c>
       <c r="C219" s="4"/>
@@ -13326,7 +13326,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 01/10/2026</t>
+          <t xml:space="preserve">Vigencia: 21/10/2026</t>
         </is>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -11956,7 +11956,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 14/10/2026</t>
+          <t xml:space="preserve">Vigencia: 23/10/2026</t>
         </is>
       </c>
     </row>
@@ -12133,27 +12133,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARINA MASA MADRE S/GLUTE X 400 G</t>
+          <t xml:space="preserve">HARINA 000 MASA MADRE 10x1</t>
         </is>
       </c>
       <c r="C11" s="4">
         <v>10</v>
       </c>
       <c r="D11" s="5">
-        <v>19326.25</v>
+        <v>13357.93</v>
       </c>
       <c r="E11" s="5">
         <f>IF(C11&gt;0,D11/C11,"")</f>
-        <v>1932.625</v>
+        <v>1335.7930000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4">
-        <v>3626034</v>
+        <v>3626033</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREM PAN DE QUESO S/GLUTEN X 300 G</t>
+          <t xml:space="preserve">HARINA MASA MADRE S/GLUTE X 400 G</t>
         </is>
       </c>
       <c r="C12" s="4">
@@ -12169,21 +12169,41 @@
     </row>
     <row r="13">
       <c r="A13" s="4">
-        <v>3626040</v>
+        <v>3626034</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARINA 00 PIZZA NAPOLETANA 10 X 1  KG</t>
+          <t xml:space="preserve">PREM PAN DE QUESO S/GLUTEN X 300 G</t>
         </is>
       </c>
       <c r="C13" s="4">
         <v>10</v>
       </c>
       <c r="D13" s="5">
-        <v>25610.4</v>
+        <v>19326.25</v>
       </c>
       <c r="E13" s="5">
         <f>IF(C13&gt;0,D13/C13,"")</f>
+        <v>1932.625</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4">
+        <v>3626040</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HARINA 00 PIZZA NAPOLETANA 10 X 1  KG</t>
+        </is>
+      </c>
+      <c r="C14" s="4">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5">
+        <v>25610.4</v>
+      </c>
+      <c r="E14" s="5">
+        <f>IF(C14&gt;0,D14/C14,"")</f>
         <v>2561.04</v>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -8636,10 +8636,15 @@
           <t xml:space="preserve">YOG.FIRME DES. FRUT. POTE X 190G. ILOLAY</t>
         </is>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
+      <c r="C54" s="4">
+        <v>20</v>
+      </c>
+      <c r="D54" s="5">
+        <v>24788.79</v>
+      </c>
       <c r="E54" s="5">
-        <v>1239.44</v>
+        <f>IF(C54&gt;0,D54/C54,"")</f>
+        <v>1239.4395</v>
       </c>
     </row>
     <row r="55">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -9066,10 +9066,15 @@
           <t xml:space="preserve">TETRATOP PROTEINA VAINILLA X220GR ILOLAY</t>
         </is>
       </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="5"/>
+      <c r="C78" s="4">
+        <v>24</v>
+      </c>
+      <c r="D78" s="5">
+        <v>54777.28</v>
+      </c>
       <c r="E78" s="5">
-        <v>2282.39</v>
+        <f>IF(C78&gt;0,D78/C78,"")</f>
+        <v>2282.3866666666668</v>
       </c>
     </row>
     <row r="79">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -18241,7 +18241,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 21/10/2026</t>
+          <t xml:space="preserve">Vigencia: 27/10/2026</t>
         </is>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -5951,9 +5951,14 @@
           <t xml:space="preserve">FLYNN PAFF BOLSA SURTIDA 8X8GR</t>
         </is>
       </c>
-      <c r="C168" s="4"/>
-      <c r="D168" s="5"/>
+      <c r="C168" s="4">
+        <v>8</v>
+      </c>
+      <c r="D168" s="5">
+        <v>61993.04</v>
+      </c>
       <c r="E168" s="5">
+        <f>IF(C168&gt;0,D168/C168,"")</f>
         <v>7749.13</v>
       </c>
     </row>
@@ -18241,7 +18246,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 27/10/2026</t>
+          <t xml:space="preserve">Vigencia: 28/10/2026</t>
         </is>
       </c>
     </row>
@@ -19534,41 +19539,61 @@
     </row>
     <row r="67">
       <c r="A67" s="4">
-        <v>39014884</v>
+        <v>39014882</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DR LEMON RED BERRIES 5% 4x6x473</t>
+          <t xml:space="preserve">Gancia LIMA LIMON ONE 4x6x473</t>
         </is>
       </c>
       <c r="C67" s="4">
         <v>24</v>
       </c>
       <c r="D67" s="5">
-        <v>46766.89</v>
+        <v>42932.74</v>
       </c>
       <c r="E67" s="5">
         <f>IF(C67&gt;0,D67/C67,"")</f>
-        <v>1948.6204166666666</v>
+        <v>1788.8641666666665</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4">
-        <v>39014996</v>
+        <v>39014884</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
+          <t xml:space="preserve">DR LEMON RED BERRIES 5% 4x6x473</t>
         </is>
       </c>
       <c r="C68" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D68" s="5">
-        <v>93259.44</v>
+        <v>46766.89</v>
       </c>
       <c r="E68" s="5">
         <f>IF(C68&gt;0,D68/C68,"")</f>
+        <v>1948.6204166666666</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4">
+        <v>39014996</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
+        </is>
+      </c>
+      <c r="C69" s="4">
+        <v>12</v>
+      </c>
+      <c r="D69" s="5">
+        <v>93259.44</v>
+      </c>
+      <c r="E69" s="5">
+        <f>IF(C69&gt;0,D69/C69,"")</f>
         <v>7771.62</v>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -2460,78 +2460,74 @@
     </row>
     <row r="95">
       <c r="A95" s="4">
-        <v>1506523</v>
+        <v>1506286</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serv Elite Int Plus SH X250/72</t>
+          <t xml:space="preserve">Paños Maxwipe x70 Rollo x88/6</t>
         </is>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="E95" s="5">
-        <v>63234.6</v>
+        <v>18455.39</v>
       </c>
       <c r="F95" s="5">
         <f>IF(D95&gt;0,E95/D95,"")</f>
-        <v>878.25833333333333</v>
+        <v>3075.8983333333331</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4">
-        <v>1509232</v>
+        <v>1506385</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC NOBLE 40P x3/10</t>
-        </is>
-      </c>
-      <c r="C96" s="4">
-        <v>48</v>
-      </c>
+          <t xml:space="preserve">Paños Maxwipe 60 Q X50/12 Blanco</t>
+        </is>
+      </c>
+      <c r="C96" s="4"/>
       <c r="D96" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E96" s="5">
-        <v>15947.45</v>
+        <v>48228.18</v>
       </c>
       <c r="F96" s="5">
         <f>IF(D96&gt;0,E96/D96,"")</f>
-        <v>1594.7450000000001</v>
+        <v>4019.015</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4">
-        <v>1509243</v>
+        <v>1506523</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH NOBLE HS 30M X4/12</t>
-        </is>
-      </c>
-      <c r="C97" s="4">
-        <v>60</v>
-      </c>
+          <t xml:space="preserve">Serv Elite Int Plus SH X250/72</t>
+        </is>
+      </c>
+      <c r="C97" s="4"/>
       <c r="D97" s="4">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E97" s="5">
-        <v>21596.33</v>
+        <v>63234.6</v>
       </c>
       <c r="F97" s="5">
         <f>IF(D97&gt;0,E97/D97,"")</f>
-        <v>1799.6941666666669</v>
+        <v>878.25833333333333</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4">
-        <v>1509244</v>
+        <v>1509232</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH NOBLE HS 30X6</t>
+          <t xml:space="preserve">RC NOBLE 40P x3/10</t>
         </is>
       </c>
       <c r="C98" s="4">
@@ -2541,342 +2537,342 @@
         <v>10</v>
       </c>
       <c r="E98" s="5">
-        <v>26082.47</v>
+        <v>15947.45</v>
       </c>
       <c r="F98" s="5">
         <f>IF(D98&gt;0,E98/D98,"")</f>
-        <v>2608.2470000000003</v>
+        <v>1594.7450000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4">
-        <v>1509245</v>
+        <v>1509243</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH NOBLE DH 30x4/10</t>
+          <t xml:space="preserve">PH NOBLE HS 30M X4/12</t>
         </is>
       </c>
       <c r="C99" s="4">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D99" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E99" s="5">
-        <v>28089.53</v>
+        <v>21596.33</v>
       </c>
       <c r="F99" s="5">
         <f>IF(D99&gt;0,E99/D99,"")</f>
-        <v>2808.953</v>
+        <v>1799.6941666666669</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4">
-        <v>1509749</v>
+        <v>1509244</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PD ladysoft clasicos 20x30</t>
+          <t xml:space="preserve">PH NOBLE HS 30X6</t>
         </is>
       </c>
       <c r="C100" s="4">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D100" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E100" s="5">
-        <v>47205.4</v>
+        <v>26082.47</v>
       </c>
       <c r="F100" s="5">
         <f>IF(D100&gt;0,E100/D100,"")</f>
-        <v>1573.5133333333333</v>
+        <v>2608.2470000000003</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4">
-        <v>1509750</v>
+        <v>1509245</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PD LADYSOFT CLASICOS 56x10</t>
+          <t xml:space="preserve">PH NOBLE DH 30x4/10</t>
         </is>
       </c>
       <c r="C101" s="4">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D101" s="4">
         <v>10</v>
       </c>
       <c r="E101" s="5">
-        <v>41386.85</v>
+        <v>28089.53</v>
       </c>
       <c r="F101" s="5">
         <f>IF(D101&gt;0,E101/D101,"")</f>
-        <v>4138.6849999999995</v>
+        <v>2808.953</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4">
-        <v>1509755</v>
+        <v>1509749</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF UD T/SECA LADYSOFT ULTRA PROTECT 8</t>
+          <t xml:space="preserve">PD ladysoft clasicos 20x30</t>
         </is>
       </c>
       <c r="C102" s="4">
         <v>60</v>
       </c>
       <c r="D102" s="4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E102" s="5">
-        <v>58063.82</v>
+        <v>47205.4</v>
       </c>
       <c r="F102" s="5">
         <f>IF(D102&gt;0,E102/D102,"")</f>
-        <v>1451.5955</v>
+        <v>1573.5133333333333</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4">
-        <v>1509756</v>
+        <v>1509750</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF UD T/SECA LADYSOFT UL PRT 16u</t>
+          <t xml:space="preserve">PD LADYSOFT CLASICOS 56x10</t>
         </is>
       </c>
       <c r="C103" s="4">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D103" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E103" s="5">
-        <v>56475.9</v>
+        <v>41386.85</v>
       </c>
       <c r="F103" s="5">
         <f>IF(D103&gt;0,E103/D103,"")</f>
-        <v>2823.795</v>
+        <v>4138.6849999999995</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4">
-        <v>1509757</v>
+        <v>1509755</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF UD T/SECA LADYSOFT UL PTEC 24u</t>
+          <t xml:space="preserve">TF UD T/SECA LADYSOFT ULTRA PROTECT 8</t>
         </is>
       </c>
       <c r="C104" s="4">
         <v>60</v>
       </c>
       <c r="D104" s="4">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E104" s="5">
-        <v>60502.23</v>
+        <v>58063.82</v>
       </c>
       <c r="F104" s="5">
         <f>IF(D104&gt;0,E104/D104,"")</f>
-        <v>4033.4820000000004</v>
+        <v>1451.5955</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4">
-        <v>1509758</v>
+        <v>1509756</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF UD T/SUAVE EXT ALGO 8X40</t>
+          <t xml:space="preserve">TF UD T/SECA LADYSOFT UL PRT 16u</t>
         </is>
       </c>
       <c r="C105" s="4">
         <v>60</v>
       </c>
       <c r="D105" s="4">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E105" s="5">
-        <v>54001.88</v>
+        <v>56475.9</v>
       </c>
       <c r="F105" s="5">
         <f>IF(D105&gt;0,E105/D105,"")</f>
-        <v>1350.047</v>
+        <v>2823.795</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4">
-        <v>1509759</v>
+        <v>1509757</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF UD T/SUAVE EXT ALG 16x20</t>
+          <t xml:space="preserve">TF UD T/SECA LADYSOFT UL PTEC 24u</t>
         </is>
       </c>
       <c r="C106" s="4">
         <v>60</v>
       </c>
       <c r="D106" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E106" s="5">
-        <v>51563.15</v>
+        <v>60502.23</v>
       </c>
       <c r="F106" s="5">
         <f>IF(D106&gt;0,E106/D106,"")</f>
-        <v>2578.1575000000003</v>
+        <v>4033.4820000000004</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4">
-        <v>1509760</v>
+        <v>1509758</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TD UF T/Suave Ladysoft EXT ALGODÓN 24x15</t>
+          <t xml:space="preserve">TF UD T/SUAVE EXT ALGO 8X40</t>
         </is>
       </c>
       <c r="C107" s="4">
         <v>60</v>
       </c>
       <c r="D107" s="4">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E107" s="5">
-        <v>55018.2</v>
+        <v>54001.88</v>
       </c>
       <c r="F107" s="5">
         <f>IF(D107&gt;0,E107/D107,"")</f>
-        <v>3667.8799999999997</v>
+        <v>1350.047</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4">
-        <v>1509761</v>
+        <v>1509759</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF LADYSOFT COMFORT EXT ALGODON 8x54</t>
+          <t xml:space="preserve">TF UD T/SUAVE EXT ALG 16x20</t>
         </is>
       </c>
       <c r="C108" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D108" s="4">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="E108" s="5">
-        <v>51959.99</v>
+        <v>51563.15</v>
       </c>
       <c r="F108" s="5">
         <f>IF(D108&gt;0,E108/D108,"")</f>
-        <v>962.222037037037</v>
+        <v>2578.1575000000003</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4">
-        <v>1509762</v>
+        <v>1509760</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF NOCTUR EXT A 8x32</t>
+          <t xml:space="preserve">TD UF T/Suave Ladysoft EXT ALGODÓN 24x15</t>
         </is>
       </c>
       <c r="C109" s="4">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D109" s="4">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E109" s="5">
-        <v>45387.27</v>
+        <v>55018.2</v>
       </c>
       <c r="F109" s="5">
         <f>IF(D109&gt;0,E109/D109,"")</f>
-        <v>1418.3521875</v>
+        <v>3667.8799999999997</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4">
-        <v>1509763</v>
+        <v>1509761</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF Nocturna EXT ALGODON 16X16</t>
+          <t xml:space="preserve">TF LADYSOFT COMFORT EXT ALGODON 8x54</t>
         </is>
       </c>
       <c r="C110" s="4">
+        <v>50</v>
+      </c>
+      <c r="D110" s="4">
         <v>54</v>
       </c>
-      <c r="D110" s="4">
-        <v>16</v>
-      </c>
       <c r="E110" s="5">
-        <v>43851.46</v>
+        <v>51959.99</v>
       </c>
       <c r="F110" s="5">
         <f>IF(D110&gt;0,E110/D110,"")</f>
-        <v>2740.71625</v>
+        <v>962.222037037037</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4">
-        <v>1509764</v>
+        <v>1509762</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF NORMAL T/SUAVE EXT ALGODON 8x54</t>
+          <t xml:space="preserve">TF NOCTUR EXT A 8x32</t>
         </is>
       </c>
       <c r="C111" s="4">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D111" s="4">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E111" s="5">
-        <v>54222.36</v>
+        <v>45387.27</v>
       </c>
       <c r="F111" s="5">
         <f>IF(D111&gt;0,E111/D111,"")</f>
-        <v>1004.1177777777777</v>
+        <v>1418.3521875</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4">
-        <v>1509765</v>
+        <v>1509763</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF NORMALT/SUAVE EXT ALG 16x27</t>
+          <t xml:space="preserve">TF Nocturna EXT ALGODON 16X16</t>
         </is>
       </c>
       <c r="C112" s="4">
         <v>54</v>
       </c>
       <c r="D112" s="4">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E112" s="5">
-        <v>54303.52</v>
+        <v>43851.46</v>
       </c>
       <c r="F112" s="5">
         <f>IF(D112&gt;0,E112/D112,"")</f>
-        <v>2011.2414814814813</v>
+        <v>2740.71625</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4">
-        <v>1509766</v>
+        <v>1509764</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF T/SECA NORMAL MAS PROTECC 8x54</t>
+          <t xml:space="preserve">TF NORMAL T/SUAVE EXT ALGODON 8x54</t>
         </is>
       </c>
       <c r="C113" s="4">
@@ -2886,43 +2882,43 @@
         <v>54</v>
       </c>
       <c r="E113" s="5">
-        <v>59838.63</v>
+        <v>54222.36</v>
       </c>
       <c r="F113" s="5">
         <f>IF(D113&gt;0,E113/D113,"")</f>
-        <v>1108.1227777777776</v>
+        <v>1004.1177777777777</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4">
-        <v>1509767</v>
+        <v>1509765</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF UD TSUAVE ACTIVE 8X40</t>
+          <t xml:space="preserve">TF NORMALT/SUAVE EXT ALG 16x27</t>
         </is>
       </c>
       <c r="C114" s="4">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D114" s="4">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E114" s="5">
-        <v>65673.74</v>
+        <v>54303.52</v>
       </c>
       <c r="F114" s="5">
         <f>IF(D114&gt;0,E114/D114,"")</f>
-        <v>1641.8435000000002</v>
+        <v>2011.2414814814813</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4">
-        <v>1509768</v>
+        <v>1509766</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TF NORMAL T/SUAVE PIEL SENSIBLE 8x54</t>
+          <t xml:space="preserve">TF T/SECA NORMAL MAS PROTECC 8x54</t>
         </is>
       </c>
       <c r="C115" s="4">
@@ -2932,66 +2928,112 @@
         <v>54</v>
       </c>
       <c r="E115" s="5">
-        <v>63726.79</v>
+        <v>59838.63</v>
       </c>
       <c r="F115" s="5">
         <f>IF(D115&gt;0,E115/D115,"")</f>
-        <v>1180.1257407407409</v>
+        <v>1108.1227777777776</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4">
-        <v>1509769</v>
+        <v>1509767</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PD RESPIRABLES 100/12</t>
+          <t xml:space="preserve">TF UD TSUAVE ACTIVE 8X40</t>
         </is>
       </c>
       <c r="C116" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D116" s="4">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E116" s="5">
-        <v>76814.97</v>
+        <v>65673.74</v>
       </c>
       <c r="F116" s="5">
         <f>IF(D116&gt;0,E116/D116,"")</f>
-        <v>6401.2475</v>
+        <v>1641.8435000000002</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4">
-        <v>1509916</v>
+        <v>1509768</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PD LADYSOFT UD RESPIRABLE S/ALAS X20/30</t>
-        </is>
-      </c>
-      <c r="C117" s="4"/>
+          <t xml:space="preserve">TF NORMAL T/SUAVE PIEL SENSIBLE 8x54</t>
+        </is>
+      </c>
+      <c r="C117" s="4">
+        <v>54</v>
+      </c>
       <c r="D117" s="4">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E117" s="5">
-        <v>47622.19</v>
+        <v>63726.79</v>
       </c>
       <c r="F117" s="5">
         <f>IF(D117&gt;0,E117/D117,"")</f>
+        <v>1180.1257407407409</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4">
+        <v>1509769</v>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PD RESPIRABLES 100/12</t>
+        </is>
+      </c>
+      <c r="C118" s="4">
+        <v>50</v>
+      </c>
+      <c r="D118" s="4">
+        <v>12</v>
+      </c>
+      <c r="E118" s="5">
+        <v>76814.97</v>
+      </c>
+      <c r="F118" s="5">
+        <f>IF(D118&gt;0,E118/D118,"")</f>
+        <v>6401.2475</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4">
+        <v>1509916</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PD LADYSOFT UD RESPIRABLE S/ALAS X20/30</t>
+        </is>
+      </c>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4">
+        <v>30</v>
+      </c>
+      <c r="E119" s="5">
+        <v>47622.19</v>
+      </c>
+      <c r="F119" s="5">
+        <f>IF(D119&gt;0,E119/D119,"")</f>
         <v>1587.4063333333334</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">* 1503121 TH Babysec Premium 50/10: En el sistema el precio Pack figura 10 veces mas alto. Se toma el precio Unidad del sistema como precio del bulto.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">* 1504739 PL BABYSEC ULTRA M 26/8: El sistema lo carga con 6 por bulto; segun la tabla de logistica y la descripcion (26/8) son 8. Se toman 8.</t>
         </is>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -351,7 +351,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 20/10/2026</t>
+          <t xml:space="preserve">Vigencia: 29/10/2026</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 28/10/2026</t>
+          <t xml:space="preserve">Vigencia: 29/10/2026</t>
         </is>
       </c>
     </row>
@@ -19581,61 +19581,81 @@
     </row>
     <row r="67">
       <c r="A67" s="4">
-        <v>39014882</v>
+        <v>39014866</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gancia LIMA LIMON ONE 4x6x473</t>
+          <t xml:space="preserve">1882 FERNET CON POMELO 7 473mlx6x4</t>
         </is>
       </c>
       <c r="C67" s="4">
         <v>24</v>
       </c>
       <c r="D67" s="5">
-        <v>42932.74</v>
+        <v>40363.42</v>
       </c>
       <c r="E67" s="5">
         <f>IF(C67&gt;0,D67/C67,"")</f>
-        <v>1788.8641666666665</v>
+        <v>1681.8091666666667</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4">
-        <v>39014884</v>
+        <v>39014882</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DR LEMON RED BERRIES 5% 4x6x473</t>
+          <t xml:space="preserve">Gancia LIMA LIMON ONE 4x6x473</t>
         </is>
       </c>
       <c r="C68" s="4">
         <v>24</v>
       </c>
       <c r="D68" s="5">
-        <v>46766.89</v>
+        <v>42932.74</v>
       </c>
       <c r="E68" s="5">
         <f>IF(C68&gt;0,D68/C68,"")</f>
-        <v>1948.6204166666666</v>
+        <v>1788.8641666666665</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4">
-        <v>39014996</v>
+        <v>39014884</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
+          <t xml:space="preserve">DR LEMON RED BERRIES 5% 4x6x473</t>
         </is>
       </c>
       <c r="C69" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D69" s="5">
-        <v>93259.44</v>
+        <v>46766.89</v>
       </c>
       <c r="E69" s="5">
         <f>IF(C69&gt;0,D69/C69,"")</f>
+        <v>1948.6204166666666</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4">
+        <v>39014996</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martini Rosso 16° 12x995ml</t>
+        </is>
+      </c>
+      <c r="C70" s="4">
+        <v>12</v>
+      </c>
+      <c r="D70" s="5">
+        <v>93259.44</v>
+      </c>
+      <c r="E70" s="5">
+        <f>IF(C70&gt;0,D70/C70,"")</f>
         <v>7771.62</v>
       </c>
     </row>

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -7584,14 +7584,14 @@
         </is>
       </c>
       <c r="C258" s="4">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D258" s="5">
-        <v>229281.25</v>
+        <v>128970.71</v>
       </c>
       <c r="E258" s="5">
         <f>IF(C258&gt;0,D258/C258,"")</f>
-        <v>7165.0390625</v>
+        <v>7165.0394444444446</v>
       </c>
     </row>
     <row r="259">

--- a/Listas de precios LP - ELEBES.xlsx
+++ b/Listas de precios LP - ELEBES.xlsx
@@ -16448,7 +16448,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigencia: 06/10/2026</t>
+          <t xml:space="preserve">Vigencia: 31/10/2026</t>
         </is>
       </c>
     </row>
@@ -16671,31 +16671,26 @@
     </row>
     <row r="15">
       <c r="A15" s="4">
-        <v>4180154</v>
+        <v>4180153</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maní c Sal s/piel 100g x 15 u</t>
-        </is>
-      </c>
-      <c r="C15" s="4">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5">
-        <v>12574.27</v>
-      </c>
+          <t xml:space="preserve">Mani Chef Sabor Asado 15x80g</t>
+        </is>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="5">
-        <f>IF(C15&gt;0,D15/C15,"")</f>
-        <v>838.28466666666668</v>
+        <v>13394.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4">
-        <v>4180155</v>
+        <v>4180154</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maní Sal con Piel 100G X 15u</t>
+          <t xml:space="preserve">Maní c Sal s/piel 100g x 15 u</t>
         </is>
       </c>
       <c r="C16" s="4">
@@ -16711,251 +16706,286 @@
     </row>
     <row r="17">
       <c r="A17" s="4">
-        <v>4180203</v>
+        <v>4180155</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maní Tostado con Cáscara 175G</t>
-        </is>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
+          <t xml:space="preserve">Maní Sal con Piel 100G X 15u</t>
+        </is>
+      </c>
+      <c r="C17" s="4">
+        <v>15</v>
+      </c>
+      <c r="D17" s="5">
+        <v>12574.27</v>
+      </c>
       <c r="E17" s="5">
-        <v>18804.44</v>
+        <f>IF(C17&gt;0,D17/C17,"")</f>
+        <v>838.28466666666668</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4">
-        <v>41800103</v>
+        <v>4180169</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mani c chocolate 15 x 80 grs</t>
-        </is>
-      </c>
-      <c r="C18" s="4">
-        <v>15</v>
-      </c>
-      <c r="D18" s="5">
-        <v>21618.74</v>
-      </c>
+          <t xml:space="preserve">Mani Sal Marina 200g  x12u</t>
+        </is>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="5">
-        <f>IF(C18&gt;0,D18/C18,"")</f>
-        <v>1441.2493333333334</v>
+        <v>23866.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4">
-        <v>41800104</v>
+        <v>4180203</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GarrapiÑada 20 x 80 grs x 20 u</t>
-        </is>
-      </c>
-      <c r="C19" s="4">
-        <v>20</v>
-      </c>
-      <c r="D19" s="5">
-        <v>13117.49</v>
-      </c>
+          <t xml:space="preserve">Maní Tostado con Cáscara 175G</t>
+        </is>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="5">
-        <f>IF(C19&gt;0,D19/C19,"")</f>
-        <v>655.8745</v>
+        <v>18804.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4">
-        <v>41800131</v>
+        <v>41800103</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pasta de Mani cruchy  350x12gr</t>
+          <t xml:space="preserve">Mani c chocolate 15 x 80 grs</t>
         </is>
       </c>
       <c r="C20" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20" s="5">
-        <v>85078.8</v>
+        <v>21618.74</v>
       </c>
       <c r="E20" s="5">
         <f>IF(C20&gt;0,D20/C20,"")</f>
-        <v>7089.9000000000005</v>
+        <v>1441.2493333333334</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4">
-        <v>41800152</v>
+        <v>41800104</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mani Frito Mk  SIN PIEL 20 x350 gr</t>
-        </is>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
+          <t xml:space="preserve">GarrapiÑada 20 x 80 grs x 20 u</t>
+        </is>
+      </c>
+      <c r="C21" s="4">
+        <v>20</v>
+      </c>
+      <c r="D21" s="5">
+        <v>13117.49</v>
+      </c>
       <c r="E21" s="5">
-        <v>14454.47</v>
+        <f>IF(C21&gt;0,D21/C21,"")</f>
+        <v>655.8745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4">
-        <v>41800208</v>
+        <v>41800131</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mani con cascara 10x400 gr</t>
+          <t xml:space="preserve">Pasta de Mani cruchy  350x12gr</t>
         </is>
       </c>
       <c r="C22" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D22" s="5">
-        <v>22706.91</v>
+        <v>85078.8</v>
       </c>
       <c r="E22" s="5">
         <f>IF(C22&gt;0,D22/C22,"")</f>
-        <v>2270.691</v>
+        <v>7089.9000000000005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4">
-        <v>41800216</v>
+        <v>41800152</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mani c baño choco 15 x 80 grs</t>
-        </is>
-      </c>
-      <c r="C23" s="4">
-        <v>15</v>
-      </c>
-      <c r="D23" s="5">
-        <v>22110.08</v>
-      </c>
+          <t xml:space="preserve">Mani Frito Mk  SIN PIEL 20 x350 gr</t>
+        </is>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="5">
-        <f>IF(C23&gt;0,D23/C23,"")</f>
-        <v>1474.0053333333335</v>
+        <v>14454.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4">
-        <v>41810134</v>
+        <v>41800208</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANI FRITO MK 1KG X 9</t>
-        </is>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
+          <t xml:space="preserve">Mani con cascara 10x400 gr</t>
+        </is>
+      </c>
+      <c r="C24" s="4">
+        <v>10</v>
+      </c>
+      <c r="D24" s="5">
+        <v>22706.91</v>
+      </c>
       <c r="E24" s="5">
-        <v>54895.8</v>
+        <f>IF(C24&gt;0,D24/C24,"")</f>
+        <v>2270.691</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4">
-        <v>41810153</v>
+        <v>41800216</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANI FRITO C/ PIEL MK 20X350 GR</t>
-        </is>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
+          <t xml:space="preserve">Mani c baño choco 15 x 80 grs</t>
+        </is>
+      </c>
+      <c r="C25" s="4">
+        <v>15</v>
+      </c>
+      <c r="D25" s="5">
+        <v>22110.08</v>
+      </c>
       <c r="E25" s="5">
-        <v>55511.5</v>
+        <f>IF(C25&gt;0,D25/C25,"")</f>
+        <v>1474.0053333333335</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4">
-        <v>41820115</v>
+        <v>41810134</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANI TOSTADO MK SIN SAL 20X350 GRS</t>
-        </is>
-      </c>
-      <c r="C26" s="4">
-        <v>20</v>
-      </c>
-      <c r="D26" s="5">
-        <v>55511.48</v>
-      </c>
+          <t xml:space="preserve">MANI FRITO MK 1KG X 9</t>
+        </is>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
       <c r="E26" s="5">
-        <f>IF(C26&gt;0,D26/C26,"")</f>
-        <v>2775.574</v>
+        <v>54895.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4">
-        <v>41820116</v>
+        <v>41810153</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maní Tostado s/ Piel s/ Sal  100GR</t>
+          <t xml:space="preserve">MANI FRITO C/ PIEL MK 20X350 GR</t>
         </is>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
-        <v>12574.27</v>
+        <v>55511.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4">
-        <v>41820122</v>
+        <v>41820115</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANI TOSTADO 1KG X 9</t>
-        </is>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+          <t xml:space="preserve">MANI TOSTADO MK SIN SAL 20X350 GRS</t>
+        </is>
+      </c>
+      <c r="C28" s="4">
+        <v>20</v>
+      </c>
+      <c r="D28" s="5">
+        <v>55511.48</v>
+      </c>
       <c r="E28" s="5">
-        <v>54895.8</v>
+        <f>IF(C28&gt;0,D28/C28,"")</f>
+        <v>2775.574</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4">
-        <v>41860118</v>
+        <v>41820116</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASTA DE MANI MK NAT 6X1 KG</t>
-        </is>
-      </c>
-      <c r="C29" s="4">
-        <v>6</v>
-      </c>
-      <c r="D29" s="5">
-        <v>30562.08</v>
-      </c>
+          <t xml:space="preserve">Maní Tostado s/ Piel s/ Sal  100GR</t>
+        </is>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <f>IF(C29&gt;0,D29/C29,"")</f>
-        <v>5093.68</v>
+        <v>12574.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4">
+        <v>41820122</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANI TOSTADO 1KG X 9</t>
+        </is>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5">
+        <v>54895.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4">
+        <v>41860118</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASTA DE MANI MK NAT 6X1 KG</t>
+        </is>
+      </c>
+      <c r="C31" s="4">
+        <v>6</v>
+      </c>
+      <c r="D31" s="5">
+        <v>30562.08</v>
+      </c>
+      <c r="E31" s="5">
+        <f>IF(C31&gt;0,D31/C31,"")</f>
+        <v>5093.68</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4">
         <v>44834210</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">REDONDITOS CHOCOLATE  210 G 16U</t>
         </is>
       </c>
-      <c r="C30" s="4">
+      <c r="C32" s="4">
         <v>16</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D32" s="5">
         <v>26992.68</v>
       </c>
-      <c r="E30" s="5">
-        <f>IF(C30&gt;0,D30/C30,"")</f>
+      <c r="E32" s="5">
+        <f>IF(C32&gt;0,D32/C32,"")</f>
         <v>1687.0425</v>
       </c>
     </row>
